--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="472">
   <si>
     <t>الفرز</t>
   </si>
@@ -301,1099 +301,1102 @@
     <t>الجناح</t>
   </si>
   <si>
-    <t>جودي بوشي - شھد دباغ - ندوى صقال</t>
+    <t>جودي بوشي - شهد دباغ - ندوى صقال</t>
   </si>
   <si>
     <t>رشواني - مريم - رشا</t>
   </si>
   <si>
+    <t>هيا - لينا</t>
+  </si>
+  <si>
+    <t>العناية</t>
+  </si>
+  <si>
+    <t>سدرة</t>
+  </si>
+  <si>
+    <t>خديجة</t>
+  </si>
+  <si>
+    <t>المتوسطة</t>
+  </si>
+  <si>
+    <t>شهد حمدان - رفيدة فرمان - أحمد المحمد - علاء العلي</t>
+  </si>
+  <si>
+    <t>فرواتي - أشرفي - عبدالله - كردية - كجان</t>
+  </si>
+  <si>
+    <t>منار - نجار - كوثر</t>
+  </si>
+  <si>
+    <t>الأورام</t>
+  </si>
+  <si>
+    <t>بازركان</t>
+  </si>
+  <si>
+    <t>التوليد</t>
+  </si>
+  <si>
+    <t>رنيم ضبيط - روان عبس - روان جنيدي</t>
+  </si>
+  <si>
+    <t>ريم ماضي - راما - عائشة</t>
+  </si>
+  <si>
+    <t>تسنيم - هبة</t>
+  </si>
+  <si>
+    <t>المؤقتة</t>
+  </si>
+  <si>
+    <t>ويس</t>
+  </si>
+  <si>
+    <t>الإسعاف</t>
+  </si>
+  <si>
+    <t>روضة صباغ - اسراء الجاويش - محمد الصالح - نور كحيل</t>
+  </si>
+  <si>
+    <t>آمنة - هيا - علا خلوف - رؤى</t>
+  </si>
+  <si>
+    <t>الخميس</t>
+  </si>
+  <si>
+    <t>شاميران - ميسم طاحوش - خالد</t>
+  </si>
+  <si>
+    <t>سالي - زين - عدن</t>
+  </si>
+  <si>
+    <t>رفاعي - فاتن</t>
+  </si>
+  <si>
+    <t>تسنيم باكير</t>
+  </si>
+  <si>
+    <t>حرح</t>
+  </si>
+  <si>
+    <t>ساكت</t>
+  </si>
+  <si>
+    <t>راما مشلح - فاضلة محمد - فدى قصاص</t>
+  </si>
+  <si>
+    <t>ميسم - مكيس - همسة - محي الدين - حسن</t>
+  </si>
+  <si>
+    <t>روشان - تيما - فرح</t>
+  </si>
+  <si>
+    <t>وتي</t>
+  </si>
+  <si>
+    <t>علي عبد الرزاق - نور قلعجي - فاطمة قلعية</t>
+  </si>
+  <si>
+    <t>يمنى - براءة - بتول</t>
+  </si>
+  <si>
+    <t>دندل - نور</t>
+  </si>
+  <si>
+    <t>علا اليوسف</t>
+  </si>
+  <si>
+    <t>ماريا آغا - شهد كريمش - لانا صباغ - أريج الخطيب</t>
+  </si>
+  <si>
+    <t>اسلام - منصور - نجار - علي</t>
+  </si>
+  <si>
+    <t>الجمعة</t>
+  </si>
+  <si>
+    <t>محمد حج ابراهيم - رؤى عطار - بانة شحرور</t>
+  </si>
+  <si>
+    <t>أنس - خالد - بانة</t>
+  </si>
+  <si>
+    <t>تمو - إنجي</t>
+  </si>
+  <si>
+    <t>مها عيسى</t>
+  </si>
+  <si>
+    <t>تسنيم - أمل</t>
+  </si>
+  <si>
+    <t>عبدالو</t>
+  </si>
+  <si>
+    <t>روان بطل - رامي سليمان - أمامة الخليفة</t>
+  </si>
+  <si>
+    <t>سارة - فرواتي - مهندس - دليفان - علا بكري</t>
+  </si>
+  <si>
+    <t>كبب - إسماعيل - حمادية</t>
+  </si>
+  <si>
+    <t>ليندا</t>
+  </si>
+  <si>
+    <t>مصطفى جورية - سارة السعيد - براءة أحمد</t>
+  </si>
+  <si>
+    <t>شهابي - آية خلوف - ريما</t>
+  </si>
+  <si>
+    <t>مكانسي - مركن</t>
+  </si>
+  <si>
+    <t>لانا</t>
+  </si>
+  <si>
+    <t>رؤى النبشة - بتول هنداوي - آية فتال - رند كيالي</t>
+  </si>
+  <si>
+    <t>جميلي - نتالي - قمر - ويس</t>
+  </si>
+  <si>
+    <t>السبت</t>
+  </si>
+  <si>
+    <t>هيفا محمد - سهام وعري - لارا النعسان</t>
+  </si>
+  <si>
+    <t>آمنة - هيا - فاطمة</t>
+  </si>
+  <si>
+    <t>أريج - أماني</t>
+  </si>
+  <si>
+    <t>آية حايك - مجيدة</t>
+  </si>
+  <si>
+    <t>غرام - عائشة</t>
+  </si>
+  <si>
+    <t>أحمد</t>
+  </si>
+  <si>
+    <t>ريم حمادة - سنا مسلاتي - سلام قدور</t>
+  </si>
+  <si>
+    <t>خديجة - رحاب - همسة - أشرفي - منصور</t>
+  </si>
+  <si>
+    <t>إيلاف - شيماء - ديمة</t>
+  </si>
+  <si>
+    <t>ايمان</t>
+  </si>
+  <si>
+    <t>أمنية عدلة - سارة عرابي - هاجر صيادي</t>
+  </si>
+  <si>
+    <t>رشا - شهد - بازركان</t>
+  </si>
+  <si>
+    <t>سيد علي - أروى</t>
+  </si>
+  <si>
+    <t>علي</t>
+  </si>
+  <si>
+    <t>محمد نور - بيان قبسيز - محمد الصالح - شهد مخللاتي</t>
+  </si>
+  <si>
+    <t>ريم ماضي - راما - مريم - سدرة</t>
+  </si>
+  <si>
+    <t>الأحد</t>
+  </si>
+  <si>
+    <t>روان جنيدي - روان عبس - بلال صبحان - حسين</t>
+  </si>
+  <si>
+    <t>علا خلوف - رشواني - وتي</t>
+  </si>
+  <si>
+    <t>زين الدين - روان</t>
+  </si>
+  <si>
+    <t>زيلان علي - راما أبري</t>
+  </si>
+  <si>
+    <t>عدن</t>
+  </si>
+  <si>
+    <t>لين</t>
+  </si>
+  <si>
+    <t>أسماء قلعجي - رفيدة - فاضلة - روضة - هديل قناعة</t>
+  </si>
+  <si>
+    <t>دليفان - رؤى - سلام عرب - محي الدين - مكيس</t>
+  </si>
+  <si>
+    <t>قطنجي - كابرييل - دياب</t>
+  </si>
+  <si>
+    <t>نور كحيل</t>
+  </si>
+  <si>
+    <t>سنا ديب - ندوى - شهد دباغ - لانا صباغ</t>
+  </si>
+  <si>
+    <t>قمر - طاهر - زين</t>
+  </si>
+  <si>
+    <t>سنا - روابي</t>
+  </si>
+  <si>
+    <t>تسنيم</t>
+  </si>
+  <si>
+    <t>بتول</t>
+  </si>
+  <si>
+    <t>حور - علاء - سمر سرماني - رنيم ضبيط - نور علاف</t>
+  </si>
+  <si>
+    <t>أنس - حسن - علا اليوسف - لانا</t>
+  </si>
+  <si>
+    <t>الإثنين</t>
+  </si>
+  <si>
+    <t>جودي بلال - جودي بوشي - فاطمة قلعية - براءة أحمد</t>
+  </si>
+  <si>
+    <t>نتالي - ايمان - حرح</t>
+  </si>
+  <si>
+    <t>نور - بركات</t>
+  </si>
+  <si>
+    <t>زهيدة - فدى قصاص</t>
+  </si>
+  <si>
+    <t>بانة</t>
+  </si>
+  <si>
+    <t>سفانة</t>
+  </si>
+  <si>
+    <t>ميسم</t>
+  </si>
+  <si>
+    <t>راما مشلح - رامي - أمامة - بيان بيطار - نور قلعجي</t>
+  </si>
+  <si>
+    <t>فرواتي - مهندس - سدرة - غرام - تسنيم</t>
+  </si>
+  <si>
+    <t>حمادية - روشان - جودي</t>
+  </si>
+  <si>
+    <t>اسراء</t>
+  </si>
+  <si>
+    <t>جميلي</t>
+  </si>
+  <si>
+    <t>كريمش - مها عيسى - مصطفى - حسان</t>
+  </si>
+  <si>
+    <t>يمنى - براءة - أمل</t>
+  </si>
+  <si>
     <t>لينا - هيا</t>
   </si>
   <si>
-    <t>العناية</t>
-  </si>
-  <si>
-    <t>سدرة</t>
-  </si>
-  <si>
-    <t>خديجة</t>
-  </si>
-  <si>
-    <t>المتوسطة</t>
-  </si>
-  <si>
-    <t>فرواتي</t>
-  </si>
-  <si>
-    <t>شھد حمدان - رفیدة فرمان - أحمد المحمد - علاء العلي</t>
-  </si>
-  <si>
-    <t>أشرفي - عبدالله - كردية - كجان</t>
-  </si>
-  <si>
-    <t>كوثر - نجار - منار</t>
-  </si>
-  <si>
-    <t>الأورام</t>
-  </si>
-  <si>
-    <t>بازركان</t>
-  </si>
-  <si>
-    <t>التوليد</t>
-  </si>
-  <si>
-    <t>رنیم ضبیط - روان عبس - روان جنیدي</t>
-  </si>
-  <si>
-    <t>ريم ماضي - راما - عائشة</t>
-  </si>
-  <si>
-    <t>هبة - تسنيم</t>
-  </si>
-  <si>
-    <t>المؤقتة</t>
-  </si>
-  <si>
-    <t>ويس</t>
-  </si>
-  <si>
-    <t>الإسعاف</t>
-  </si>
-  <si>
-    <t>روضة صباغ - اسراء الجاویش - محمد الصالح - نور كحیل</t>
-  </si>
-  <si>
-    <t>آمنة - هيا - علا خلوف - رؤى</t>
-  </si>
-  <si>
-    <t>الخميس</t>
-  </si>
-  <si>
-    <t>شامیران - میسم طاحوش - خالد</t>
-  </si>
-  <si>
-    <t>سالي - زين - عدن</t>
-  </si>
-  <si>
-    <t>فاتن - رفاعي</t>
-  </si>
-  <si>
-    <t>تسنیم باكیر</t>
-  </si>
-  <si>
-    <t>حرح</t>
-  </si>
-  <si>
-    <t>ساكت</t>
-  </si>
-  <si>
-    <t>ميسم</t>
-  </si>
-  <si>
-    <t>راما مشلح - فاضلة محمد - فدى قصاص</t>
-  </si>
-  <si>
-    <t>مكيس - همسة - محي الدين - حسن</t>
-  </si>
-  <si>
-    <t>فرح - تيما - روشان</t>
-  </si>
-  <si>
-    <t>وتي</t>
-  </si>
-  <si>
-    <t>علي عبد الرزاق - نور قلعجي - فاطمة قلعیة</t>
-  </si>
-  <si>
-    <t>يمنى - براءة - بتول</t>
-  </si>
-  <si>
-    <t>نور - دندل</t>
-  </si>
-  <si>
-    <t>علا اليوسف</t>
-  </si>
-  <si>
-    <t>ماریا آغا - شھد كریمش - لانا صباغ - أریج الخطیب</t>
-  </si>
-  <si>
-    <t>اسلام - منصور - نجار - علي</t>
-  </si>
-  <si>
-    <t>الجمعة</t>
-  </si>
-  <si>
-    <t>محمد حج ابراھیم - رؤى عطار - بانة شحرور</t>
-  </si>
-  <si>
-    <t>أنس - خالد - بانة</t>
-  </si>
-  <si>
-    <t>انجي - تمو</t>
-  </si>
-  <si>
-    <t>مھا عیسى</t>
-  </si>
-  <si>
-    <t>تسنيم</t>
-  </si>
-  <si>
-    <t>عبدالو</t>
+    <t>رند كيالي</t>
+  </si>
+  <si>
+    <t>اسلام</t>
+  </si>
+  <si>
+    <t>روليان مصطفى - تسنيم ترك - علي - أحمد - سارة سعيد</t>
+  </si>
+  <si>
+    <t>ريما - رحاب - شهابي - خديجة</t>
+  </si>
+  <si>
+    <t>الثلاثاء</t>
+  </si>
+  <si>
+    <t>بتول هنداوي - آية فتال - سارة عرابي - رؤى عطار</t>
+  </si>
+  <si>
+    <t>ريم ماضي - عائشة - سلام عرب</t>
+  </si>
+  <si>
+    <t>هاجر - شاميران</t>
+  </si>
+  <si>
+    <t>فاطمة</t>
+  </si>
+  <si>
+    <t>سلات</t>
+  </si>
+  <si>
+    <t>بانة شحرور</t>
+  </si>
+  <si>
+    <t>سنا مسلاتي - ريم حمادة - محمد ح ابراهيم - محمد الصالح - بيان قبسيز</t>
+  </si>
+  <si>
+    <t>سارة - ميسم - بازركان - لانا - ليندا</t>
+  </si>
+  <si>
+    <t>سلمان - قاسم - شيماء</t>
+  </si>
+  <si>
+    <t>سوسن</t>
+  </si>
+  <si>
+    <t>آمنة</t>
+  </si>
+  <si>
+    <t>تسنيم فاضل - مجيدة - لارا النعسان - رؤى النبشة</t>
+  </si>
+  <si>
+    <t>وتي - ويس - عدن</t>
+  </si>
+  <si>
+    <t>سدرة - حريري</t>
+  </si>
+  <si>
+    <t>روان بطل</t>
+  </si>
+  <si>
+    <t>آية خلوف</t>
+  </si>
+  <si>
+    <t>بلال - بتول شكوا - خالد - ماريا - شهد حمدان</t>
+  </si>
+  <si>
+    <t>عبدالله - كردية - كجان - نجار</t>
+  </si>
+  <si>
+    <t>شهد مخللاتي - سلام - سمر سرماني - نور علاف</t>
+  </si>
+  <si>
+    <t>خديجة - ريما - شهابي</t>
+  </si>
+  <si>
+    <t>لينا - أماني</t>
+  </si>
+  <si>
+    <t>روان عبس - سنا ديب</t>
+  </si>
+  <si>
+    <t>حسن</t>
+  </si>
+  <si>
+    <t>هيا</t>
+  </si>
+  <si>
+    <t>غفران جزار</t>
+  </si>
+  <si>
+    <t>فاضلة - رفيدة - أسماء قلعجي - ندوى - رنيم</t>
+  </si>
+  <si>
+    <t>مهندس - أشرفي - رشواني - شهد - زين</t>
+  </si>
+  <si>
+    <t>خديجة - رؤى - فرح</t>
+  </si>
+  <si>
+    <t>راما ابري</t>
+  </si>
+  <si>
+    <t>هيفا - علاء - محمد نور - حسين</t>
+  </si>
+  <si>
+    <t>هيا - علا خلوف - رشا</t>
+  </si>
+  <si>
+    <t>ساكت - دندل</t>
+  </si>
+  <si>
+    <t>حور</t>
   </si>
   <si>
     <t>أمل</t>
   </si>
   <si>
-    <t>روان بطل - رامي سلیمان - أمامة الخلیفة</t>
-  </si>
-  <si>
-    <t>سارة - فرواتي - مهندس - دليفان</t>
-  </si>
-  <si>
-    <t>حمادية - اسماعيل - كبب</t>
+    <t>نور كحيل - روضة - سهام وعري - أمنية عدلة - آية حايك</t>
+  </si>
+  <si>
+    <t>راما - ايمان - قمر - علا بكري</t>
+  </si>
+  <si>
+    <t>زهيدة - جودي بلال - جودي بوشي - حسان</t>
+  </si>
+  <si>
+    <t>اسلام - منصور - علي</t>
+  </si>
+  <si>
+    <t>أحمد - أمل</t>
+  </si>
+  <si>
+    <t>براءة - أحمد</t>
+  </si>
+  <si>
+    <t>خالد</t>
+  </si>
+  <si>
+    <t>أريج</t>
+  </si>
+  <si>
+    <t>اسراء جاويش</t>
+  </si>
+  <si>
+    <t>راما مشلح - رامي - أمامة - تسنيم بخصو - تسنيم باكير</t>
+  </si>
+  <si>
+    <t>حرح - مكيس - همسة - محي الدين - آمنة</t>
+  </si>
+  <si>
+    <t>تيما - منار - كبب</t>
+  </si>
+  <si>
+    <t>فدى</t>
+  </si>
+  <si>
+    <t>دليفان</t>
+  </si>
+  <si>
+    <t>بيان بيطار - شهد دباغ - لانا صباغ - فاطمة سليمان</t>
+  </si>
+  <si>
+    <t>مريم - تسنيم - سدرة</t>
+  </si>
+  <si>
+    <t>عبدالو - إنجي</t>
+  </si>
+  <si>
+    <t>كريمش</t>
+  </si>
+  <si>
+    <t>نور قلعجي - فاطمة قلعية - روان جنيدي - مها عيسى - زيلان</t>
+  </si>
+  <si>
+    <t>يمنى - براءة - سالي - طاهر</t>
+  </si>
+  <si>
+    <t>رؤى النبشة - خالد - روان بطل - سارة السعيد</t>
+  </si>
+  <si>
+    <t>كجان - أنس - نجار</t>
+  </si>
+  <si>
+    <t>سفانة - قطنجي</t>
+  </si>
+  <si>
+    <t>علي - ميسم</t>
+  </si>
+  <si>
+    <t>عبدالله - كردية</t>
+  </si>
+  <si>
+    <t>زين الدين</t>
+  </si>
+  <si>
+    <t>تسنيم ترك</t>
+  </si>
+  <si>
+    <t>سنا مسلاتي - ريم حمادة - رغد الأفندي - سارة عرابي - حلا سعيد - رند كيالي</t>
+  </si>
+  <si>
+    <t>سارة - ميسم - أشرفي - بتول - آية خلوف</t>
+  </si>
+  <si>
+    <t>كابرييل - تمو - هبة</t>
+  </si>
+  <si>
+    <t>بتول هنداوي</t>
+  </si>
+  <si>
+    <t>عائشة</t>
+  </si>
+  <si>
+    <t>محمد ح ابراهيم - روليان مصطفى - هديل قناعة - ماريا آغا</t>
+  </si>
+  <si>
+    <t>عدن - ويس - وتي</t>
+  </si>
+  <si>
+    <t>فاتن - نور</t>
+  </si>
+  <si>
+    <t>لارا النعسان</t>
+  </si>
+  <si>
+    <t>غرام</t>
+  </si>
+  <si>
+    <t>تسنيم فاضل - مجيدة - محمد الصالح - شاميران - خديجة بكار</t>
+  </si>
+  <si>
+    <t>سلام عرب - بانة - زين - نتالي</t>
+  </si>
+  <si>
+    <t>أمنية عدلة - بانة شحرور - ندوى - شهد حمدان</t>
+  </si>
+  <si>
+    <t>ريما - رحاب - شهابي</t>
+  </si>
+  <si>
+    <t>روابي - خديجة</t>
+  </si>
+  <si>
+    <t>حور - سوسن</t>
+  </si>
+  <si>
+    <t>خديجة - ايمان</t>
+  </si>
+  <si>
+    <t>رؤى</t>
+  </si>
+  <si>
+    <t>سمر سرماني</t>
+  </si>
+  <si>
+    <t>رؤى عطار - سهام وعري - فاضلة - أسماء قلعجي - روضة - رنيم</t>
+  </si>
+  <si>
+    <t>فرواتي - مهندس - أمل - علا بكري - فاطمة</t>
+  </si>
+  <si>
+    <t>فرح - لينا - هيا</t>
+  </si>
+  <si>
+    <t>بيان قبسيز</t>
+  </si>
+  <si>
+    <t>رشا</t>
+  </si>
+  <si>
+    <t>آية حايك - شهد مخللاتي - راما أبري - بلال</t>
+  </si>
+  <si>
+    <t>حسن - خالد - جميلي</t>
+  </si>
+  <si>
+    <t>لين - روان</t>
+  </si>
+  <si>
+    <t>مصطفى</t>
+  </si>
+  <si>
+    <t>روان عبس - هيفا محمد - هاجر - سنا ديب - آية فتال</t>
+  </si>
+  <si>
+    <t>رشواني - بازركان - رؤى - علا اليوسف</t>
+  </si>
+  <si>
+    <t>مريم - تسنيم - بتول</t>
+  </si>
+  <si>
+    <t>سدرة - زين الدين</t>
+  </si>
+  <si>
+    <t>حريري</t>
+  </si>
+  <si>
+    <t>علا خلوف - هيا - همسة - أشرفي - قمر</t>
+  </si>
+  <si>
+    <t>ديمة - شيماء - إيلاف</t>
+  </si>
+  <si>
+    <t>جودي - روشان</t>
+  </si>
+  <si>
+    <t>ليندا - براءة - يمنى - سالي</t>
+  </si>
+  <si>
+    <t>شهد - زين - طاهر</t>
+  </si>
+  <si>
+    <t>ساكت - فاتن</t>
+  </si>
+  <si>
+    <t>مهندس</t>
+  </si>
+  <si>
+    <t>دندل</t>
+  </si>
+  <si>
+    <t>عبدالله - كردية - كجان - نجار - مكيس</t>
+  </si>
+  <si>
+    <t>كبب - سلمان - قاسم</t>
+  </si>
+  <si>
+    <t>سلام عرب - نتالي - آية خلوف</t>
+  </si>
+  <si>
+    <t>عدن - راما - ريم ماضي - عائشة</t>
+  </si>
+  <si>
+    <t>بازركان - رؤى - علا بكري</t>
+  </si>
+  <si>
+    <t>علا - تمو</t>
+  </si>
+  <si>
+    <t>غزال</t>
+  </si>
+  <si>
+    <t>فرواتي - محي الدين - سالي - رشا - أنس</t>
+  </si>
+  <si>
+    <t>منار - إسماعيل - حمادية</t>
+  </si>
+  <si>
+    <t>ليندا - لانا - جميلي</t>
+  </si>
+  <si>
+    <t>حسن - خالد - قمر - ايمان</t>
+  </si>
+  <si>
+    <t>مريم - تسنيم - هيا</t>
+  </si>
+  <si>
+    <t>رفاعي - سفانة</t>
+  </si>
+  <si>
+    <t>علا خلوف</t>
+  </si>
+  <si>
+    <t>روان</t>
+  </si>
+  <si>
+    <t>سارة - ميسم - همسة - يمنى - براءة</t>
+  </si>
+  <si>
+    <t>لين - كوثر - فرح</t>
+  </si>
+  <si>
+    <t>نجار - رشواني - غرام</t>
+  </si>
+  <si>
+    <t>بركات - روابي</t>
+  </si>
+  <si>
+    <t>ريم ماضي - راما - أمل</t>
+  </si>
+  <si>
+    <t>أريج - عبدالو</t>
+  </si>
+  <si>
+    <t>إنجي</t>
+  </si>
+  <si>
+    <t>فرواتي - مهندس - أشرفي - بتول - آية خلوف</t>
+  </si>
+  <si>
+    <t>سيد علي - دياب - كابرييل</t>
+  </si>
+  <si>
+    <t>أماني - أحمد</t>
+  </si>
+  <si>
+    <t>عبدالله - كردية - كجان - أنس</t>
+  </si>
+  <si>
+    <t>خديجة - رؤى</t>
+  </si>
+  <si>
+    <t>حسن - خالد</t>
+  </si>
+  <si>
+    <t>روشان</t>
+  </si>
+  <si>
+    <t>مكيس - جميلي - علا اليوسف - محي الدين - همسة</t>
+  </si>
+  <si>
+    <t>منار - تسنيم - إسماعيل</t>
   </si>
   <si>
     <t>علا بكري</t>
   </si>
   <si>
-    <t>مصطفى جوریة - سارة السعید - براءة أحمد</t>
-  </si>
-  <si>
-    <t>ليندا - شهابي - آية خلوف</t>
-  </si>
-  <si>
-    <t>مركن - مكانسي</t>
+    <t>سلام عرب - قمر - نتالي</t>
+  </si>
+  <si>
+    <t>ساكت - لينا</t>
+  </si>
+  <si>
+    <t>عدن - ويس - وتي - هيا</t>
+  </si>
+  <si>
+    <t>ريما - شهابي - خديجة</t>
+  </si>
+  <si>
+    <t>غزال - مركن</t>
+  </si>
+  <si>
+    <t>رحاب - نجار</t>
+  </si>
+  <si>
+    <t>مكانسي</t>
+  </si>
+  <si>
+    <t>سارة - ميسم - سالي - مريم - تسنيم</t>
+  </si>
+  <si>
+    <t>فرح - كوثر - كبب</t>
+  </si>
+  <si>
+    <t>رشا - علا خلوف - لانا</t>
+  </si>
+  <si>
+    <t>دندل - فاتن</t>
+  </si>
+  <si>
+    <t>يمنى - براءة - آمنة - رؤى</t>
+  </si>
+  <si>
+    <t>ايمان - سدرة - أمل</t>
+  </si>
+  <si>
+    <t>جودي</t>
+  </si>
+  <si>
+    <t>زين - طاهر - شهد - رشواني - محي الدين</t>
+  </si>
+  <si>
+    <t>ديمة - إيلاف - شيماء</t>
+  </si>
+  <si>
+    <t>عبدلله - كجان - أشرفي</t>
+  </si>
+  <si>
+    <t>زين الدين - قطنجي</t>
+  </si>
+  <si>
+    <t>حرح - ريم ماضي - راما - بتول</t>
+  </si>
+  <si>
+    <t>جميلي - نتالي - رؤى</t>
+  </si>
+  <si>
+    <t>سفانة - غزال</t>
+  </si>
+  <si>
+    <t>رفاعي</t>
+  </si>
+  <si>
+    <t>سارة - ميسم - علا اليوسف - سلام عرب - بانة</t>
+  </si>
+  <si>
+    <t>حمادية - سلمان - قاسم</t>
+  </si>
+  <si>
+    <t>خديجة - شهابي - رحاب</t>
+  </si>
+  <si>
+    <t>تمو - علا</t>
+  </si>
+  <si>
+    <t>اسلام - منصور - علي - خالد</t>
+  </si>
+  <si>
+    <t>يمنى - براءة - سدرة</t>
+  </si>
+  <si>
+    <t>سيد علي - حريري</t>
+  </si>
+  <si>
+    <t>أروى</t>
+  </si>
+  <si>
+    <t>سالي - مكيس - همسة - آمنة - نجار</t>
+  </si>
+  <si>
+    <t>منار - كابرييل - دياب</t>
   </si>
   <si>
     <t>ريما</t>
   </si>
   <si>
-    <t>رؤى النبشة - بتول ھنداوي - آیة فتال - رند كیالي</t>
-  </si>
-  <si>
-    <t>لانا - جمیلی - نتالي - قمر - ويس</t>
-  </si>
-  <si>
-    <t>السبت</t>
-  </si>
-  <si>
-    <t>ھیفا محمد - سھام وعري - لارا النعسان</t>
-  </si>
-  <si>
-    <t>آمنة - هيا - فاطمة</t>
-  </si>
-  <si>
-    <t>اماني - اريج</t>
-  </si>
-  <si>
-    <t>آیة حایك</t>
-  </si>
-  <si>
-    <t>غرام</t>
-  </si>
-  <si>
-    <t>احمد</t>
-  </si>
-  <si>
-    <t>مجیدة</t>
-  </si>
-  <si>
-    <t>عائشة</t>
-  </si>
-  <si>
-    <t>ریم حمادة - سنا مسلاتي - سلام قدور</t>
-  </si>
-  <si>
-    <t>خديجة - رحاب - همسة - أشرفي</t>
-  </si>
-  <si>
-    <t>ديمة - شيماء - ايلاف</t>
-  </si>
-  <si>
-    <t>منصور</t>
-  </si>
-  <si>
-    <t>أمنیة عدلة - سارة عرابي - ھاجر صیادي</t>
-  </si>
-  <si>
-    <t>ايمان - رشا - شهد</t>
-  </si>
-  <si>
-    <t>اروى - سيد علي</t>
-  </si>
-  <si>
-    <t>محمد نور - بیان قبسیز - محمد الصالح - شھد مخللاتي</t>
-  </si>
-  <si>
-    <t>علي - ريم ماضي - راما - مريم - سدرة</t>
-  </si>
-  <si>
-    <t>الأحد</t>
-  </si>
-  <si>
-    <t>روان جنیدي - روان عبس - بلال صبحان - حسین</t>
-  </si>
-  <si>
-    <t>علا خلوف - رشواني - وتي</t>
-  </si>
-  <si>
-    <t>روان - زين الدين</t>
-  </si>
-  <si>
-    <t>زیلان علي</t>
-  </si>
-  <si>
-    <t>عدن</t>
-  </si>
-  <si>
-    <t>لين</t>
-  </si>
-  <si>
-    <t>راما أبري</t>
-  </si>
-  <si>
-    <t>دليفان</t>
-  </si>
-  <si>
-    <t>أسماء قلعجي - رفیدة - فاضلة - روضة</t>
-  </si>
-  <si>
-    <t>رؤى - سلام عرب - محي الدين - مكيس</t>
-  </si>
-  <si>
-    <t>دياب - كابرئيل - قطنجي</t>
-  </si>
-  <si>
-    <t>ھدیل قناعة</t>
-  </si>
-  <si>
-    <t>ليندا</t>
-  </si>
-  <si>
-    <t>نور كحیل - سنا دیب - ندوى</t>
-  </si>
-  <si>
-    <t>قمر - طاهر - زين</t>
-  </si>
-  <si>
-    <t>روابي - سنا</t>
-  </si>
-  <si>
-    <t>شھد دباغ</t>
-  </si>
-  <si>
-    <t>بتول</t>
-  </si>
-  <si>
-    <t>لانا صباغ - تسنیم - حور - علاء - سمر سرماني - رنیم ضبیط - نور علاف</t>
-  </si>
-  <si>
-    <t>أنس - حسن - علا خلوف - لانا</t>
-  </si>
-  <si>
-    <t>الإثنين</t>
-  </si>
-  <si>
-    <t>جودي بلال - جودي بوشي - فاطمة قلعیة - براءة أحمد</t>
-  </si>
-  <si>
-    <t>نتالي - ايمان - حرح</t>
-  </si>
-  <si>
-    <t>بركات - نور</t>
-  </si>
-  <si>
-    <t>زھیدة</t>
-  </si>
-  <si>
-    <t>بانة</t>
-  </si>
-  <si>
-    <t>سفانة</t>
-  </si>
-  <si>
-    <t>فدى قصاص</t>
-  </si>
-  <si>
-    <t>میسم - راما مشلح - رامي - أمامة</t>
-  </si>
-  <si>
-    <t>مهندس - سدرة - غرام - تسنيم</t>
-  </si>
-  <si>
-    <t>جودي - روشان - حمادية</t>
-  </si>
-  <si>
-    <t>بیان بیطار</t>
-  </si>
-  <si>
-    <t>جمیلی</t>
-  </si>
-  <si>
-    <t>نور قلعجي - اسراء - كریمش</t>
-  </si>
-  <si>
-    <t>يمنى - براءة - أمل</t>
-  </si>
-  <si>
-    <t>هيا - لينا</t>
-  </si>
-  <si>
-    <t>اسلام</t>
-  </si>
-  <si>
-    <t>مصطفى - حسان - رند كیالي - رولیان مصطفى - تسنیم ترك - علي - أحمد - سارة سعید</t>
-  </si>
-  <si>
-    <t>ريما - رحاب - شهابي - خديجة</t>
-  </si>
-  <si>
-    <t>الثلاثاء</t>
-  </si>
-  <si>
-    <t>بتول ھنداوي - آیة فتال - سارة عرابي - رؤى عطار</t>
-  </si>
-  <si>
-    <t>ريم ماضي - عائشة - سلام عرب</t>
-  </si>
-  <si>
-    <t>ھاجر</t>
-  </si>
-  <si>
-    <t>فاطمة</t>
-  </si>
-  <si>
-    <t>سلات</t>
-  </si>
-  <si>
-    <t>شامیران</t>
-  </si>
-  <si>
-    <t>سارة</t>
-  </si>
-  <si>
-    <t>بانة شحرور - سنا مسلاتي - ریم حمادة - محمد ح ابراھیم</t>
-  </si>
-  <si>
-    <t>ميسم - بازركان - لانا - ليندا</t>
-  </si>
-  <si>
-    <t>شيماء - قاسم - سلمان</t>
-  </si>
-  <si>
-    <t>محمد الصالح</t>
-  </si>
-  <si>
-    <t>آمنة</t>
-  </si>
-  <si>
-    <t>بیان قبسیز - سوسن - تسنیم فاضل</t>
-  </si>
-  <si>
-    <t>وتي - ويس - عدن</t>
-  </si>
-  <si>
-    <t>حريري - سدرة</t>
-  </si>
-  <si>
-    <t>آية خلوف</t>
-  </si>
-  <si>
-    <t>لارا النعسان - رؤى النبشة - روان بطل - بلال - بتول شكوا - خالد - ماریا - شھد حمدان</t>
-  </si>
-  <si>
-    <t>عبدالله - كردية - كجان - نجار</t>
-  </si>
-  <si>
-    <t>شھد مخللاتي - سلام - سمر سرماني - نور علاف</t>
-  </si>
-  <si>
-    <t>خديجة - ريما - شهابي</t>
-  </si>
-  <si>
-    <t>اماني - لينا</t>
-  </si>
-  <si>
-    <t>روان عبس</t>
-  </si>
-  <si>
-    <t>حسن</t>
-  </si>
-  <si>
-    <t>هيا</t>
-  </si>
-  <si>
-    <t>سنا دیب</t>
-  </si>
-  <si>
-    <t>مهندس</t>
-  </si>
-  <si>
-    <t>غفران جزار - فاضلة - رفیدة - أسماء قلعجي</t>
-  </si>
-  <si>
-    <t>أشرفي - رشواني - شهد - زين</t>
-  </si>
-  <si>
-    <t>فرح - رؤى - خديجة</t>
-  </si>
-  <si>
-    <t>ندوى</t>
-  </si>
-  <si>
-    <t>رنیم - راما ابري - ھیفا</t>
-  </si>
-  <si>
-    <t>هيا - علا خلوف - رشا</t>
-  </si>
-  <si>
-    <t>دندل - ساكت</t>
-  </si>
-  <si>
-    <t>علاء</t>
-  </si>
-  <si>
-    <t>محمد نور - حسین - حور - نور كحیل - روضة - سھام وعري - أمنیة عدلة - آیة حایك</t>
-  </si>
-  <si>
-    <t>راما - ايمان - قمر - علا بكري</t>
-  </si>
-  <si>
-    <t>زھیدة - جودي بلال - جودي بوشي - حسان</t>
-  </si>
-  <si>
-    <t>اسلام - منصور - علي</t>
-  </si>
-  <si>
-    <t>امل - احمد</t>
-  </si>
-  <si>
-    <t>براءة</t>
-  </si>
-  <si>
-    <t>خالد</t>
-  </si>
-  <si>
-    <t>اريج</t>
-  </si>
-  <si>
-    <t>أحمد</t>
-  </si>
-  <si>
-    <t>اسراء جاویش - راما مشلح - رامي - أمامة</t>
-  </si>
-  <si>
-    <t>مكيس - همسة - محي الدين - آمنة</t>
-  </si>
-  <si>
-    <t>كبب - منار - تيما</t>
-  </si>
-  <si>
-    <t>تسنیم بخصو</t>
-  </si>
-  <si>
-    <t>تسنیم باكیر - فدى - بیان بیطار</t>
-  </si>
-  <si>
-    <t>مريم - تسنيم - سدرة</t>
-  </si>
-  <si>
-    <t>انجي - عبدالو</t>
-  </si>
-  <si>
-    <t>لانا صباغ - فاطمة سلیمان - كریمش - نور قلعجي - فاطمة قلعیة - روان جنیدي - مھا عیسى - زیلان</t>
-  </si>
-  <si>
-    <t>يمنى - براءة - سالي - طاهر</t>
-  </si>
-  <si>
-    <t>رؤى النبشة - خالد - روان بطل - سارة السعید</t>
-  </si>
-  <si>
-    <t>كجان - أنس - نجار</t>
-  </si>
-  <si>
-    <t>قطنجي - سفانة</t>
-  </si>
-  <si>
-    <t>علي</t>
-  </si>
-  <si>
-    <t>عبدالله</t>
-  </si>
-  <si>
-    <t>زين الدين</t>
-  </si>
-  <si>
-    <t>میسم</t>
+    <t>مريم - تسنيم - علا بكري</t>
+  </si>
+  <si>
+    <t>سلات - سدرة</t>
+  </si>
+  <si>
+    <t>لانا - عدن - ويس - وتي</t>
+  </si>
+  <si>
+    <t>آية خلوف - أمل - علا اليوسف</t>
+  </si>
+  <si>
+    <t>لين - دندل</t>
+  </si>
+  <si>
+    <t>فاتن</t>
+  </si>
+  <si>
+    <t>فرواتي - سارة - محي الدين - ريم ماضي - راما</t>
+  </si>
+  <si>
+    <t>تيما - فرح - كوثر</t>
+  </si>
+  <si>
+    <t>قمر</t>
+  </si>
+  <si>
+    <t>عبدالله - كردية - كجان</t>
+  </si>
+  <si>
+    <t>أنس</t>
+  </si>
+  <si>
+    <t>شهد - طاهر - علا خلوف - هيا</t>
+  </si>
+  <si>
+    <t>حسن - خالد - حرح</t>
+  </si>
+  <si>
+    <t>مكانسي - تسنيم</t>
+  </si>
+  <si>
+    <t>رشواني</t>
+  </si>
+  <si>
+    <t>مركن</t>
+  </si>
+  <si>
+    <t>سالي - ميسم - اسلام - منصور - علي</t>
+  </si>
+  <si>
+    <t>غزال - هبة - كبب</t>
+  </si>
+  <si>
+    <t>سلام عرب - بانة - بازركان</t>
+  </si>
+  <si>
+    <t>أحمد - أماني</t>
+  </si>
+  <si>
+    <t>علا بكري - عائشة - غرام - جميلي</t>
+  </si>
+  <si>
+    <t>بتول - وتي - تسنيم</t>
+  </si>
+  <si>
+    <t>نجار - رفاعي</t>
+  </si>
+  <si>
+    <t>مريم - آمنة</t>
+  </si>
+  <si>
+    <t>قطنجي</t>
+  </si>
+  <si>
+    <t>مكيس - همسة - ويس - محي الدين - نتالي</t>
+  </si>
+  <si>
+    <t>زين الدين - علا - أمل</t>
+  </si>
+  <si>
+    <t>نجار</t>
+  </si>
+  <si>
+    <t>رؤى - سدرة - ايمان</t>
+  </si>
+  <si>
+    <t>دياب - كابرييل</t>
+  </si>
+  <si>
+    <t>ليندا - لانا - يمنى - براءة</t>
+  </si>
+  <si>
+    <t>سدرة - غزال</t>
+  </si>
+  <si>
+    <t>سالي - آية خلوف</t>
+  </si>
+  <si>
+    <t>روابي</t>
+  </si>
+  <si>
+    <t>علا خلوف - فرواتي - أشرفي - ريم ماضي - راما</t>
+  </si>
+  <si>
+    <t>روان - قاسم - سلمان</t>
   </si>
   <si>
     <t>كردية</t>
   </si>
   <si>
-    <t>تسنیم ترك - سنا مسلاتي - ریم حمادة - رغد الأفندي</t>
-  </si>
-  <si>
-    <t>سارة - ميسم - أشرفي - بتول</t>
-  </si>
-  <si>
-    <t>هبة - تمو - كابرئيل</t>
-  </si>
-  <si>
-    <t>سارة عرابي</t>
-  </si>
-  <si>
-    <t>حلا سعید - رند كیالي - بتول ھنداوي</t>
-  </si>
-  <si>
-    <t>عائشة - عدن - ويس</t>
-  </si>
-  <si>
-    <t>نور - فاتن</t>
-  </si>
-  <si>
-    <t>محمد ح ابراھیم</t>
-  </si>
-  <si>
-    <t>رولیان مصطفى - ھدیل - ماریا آغا - لارا النعسان - تسنیم فاضل - مجیدة - محمد الصالح - شامیران - خدیجة بكار</t>
-  </si>
-  <si>
-    <t>غرام - سلام عرب - بانة - زين - نتالي</t>
-  </si>
-  <si>
-    <t>أمنیة عدلة - بانة شحرور - ندوى - شھد حمدان</t>
-  </si>
-  <si>
-    <t>ريما - رحاب - شهابي</t>
-  </si>
-  <si>
-    <t>خديجة - روابي</t>
-  </si>
-  <si>
-    <t>حور</t>
-  </si>
-  <si>
-    <t>رؤى</t>
-  </si>
-  <si>
-    <t>سوسن</t>
-  </si>
-  <si>
-    <t>ايمان</t>
-  </si>
-  <si>
-    <t>سمر سرماني - رؤى عطار - سھام وعري - فاضلة</t>
-  </si>
-  <si>
-    <t>فرواتي - مهندس - أمل - علا بكري</t>
-  </si>
-  <si>
-    <t>هيا - لينا - فرح</t>
-  </si>
-  <si>
-    <t>أسماء قلعجي</t>
-  </si>
-  <si>
-    <t>روضة - رنیم - بیان قبسیز</t>
-  </si>
-  <si>
-    <t>رشا - حسن - خالد</t>
-  </si>
-  <si>
-    <t>روان - لين</t>
-  </si>
-  <si>
-    <t>شھد مخللاتي - راما أبري - بلال - مصطفى - روان عبس - ھیفا محمد - ھاجر - سنا دیب</t>
-  </si>
-  <si>
-    <t>حرح - رشواني - بازركان - رؤى - علا اليوسف</t>
-  </si>
-  <si>
-    <t>مريم - تسنيم - بتول</t>
-  </si>
-  <si>
-    <t>زين الدين - سدرة</t>
-  </si>
-  <si>
-    <t>حريري</t>
-  </si>
-  <si>
-    <t>علا خلوف</t>
-  </si>
-  <si>
-    <t>هيا - همسة - أشرفي - قمر</t>
-  </si>
-  <si>
-    <t>ايلاف - شيماء - ديمة</t>
+    <t>قمر - علا اليوسف - حرح</t>
+  </si>
+  <si>
+    <t>عبدالله - كجان - اسلام - منصور</t>
+  </si>
+  <si>
+    <t>بازركان - رؤى - سلام عرب</t>
+  </si>
+  <si>
+    <t>كبب - أروى</t>
+  </si>
+  <si>
+    <t>نتالي</t>
+  </si>
+  <si>
+    <t>سيد علي</t>
+  </si>
+  <si>
+    <t>سارة - ميسم - ويس - بانة - عائشة</t>
+  </si>
+  <si>
+    <t>شيماء - إيلاف - ديمة</t>
+  </si>
+  <si>
+    <t>حسن - خالد - أنس</t>
+  </si>
+  <si>
+    <t>أمل - غرام - ليندا - لانا</t>
+  </si>
+  <si>
+    <t>علا خلوف - آمنة - جميلي</t>
+  </si>
+  <si>
+    <t>نجار - أحمد</t>
+  </si>
+  <si>
+    <t>أماني</t>
+  </si>
+  <si>
+    <t>ايمان - رشا - مهندس - محي الدين - همسة</t>
+  </si>
+  <si>
+    <t>منار - تيما - كوثر</t>
+  </si>
+  <si>
+    <t>مريم</t>
+  </si>
+  <si>
+    <t>يمنى - براءة - رشواني</t>
+  </si>
+  <si>
+    <t>خديجة - أريج</t>
+  </si>
+  <si>
+    <t>حرح - سدرة - علا اليوسف</t>
+  </si>
+  <si>
+    <t>سنا - سلات</t>
+  </si>
+  <si>
+    <t>بركات</t>
+  </si>
+  <si>
+    <t>سارة - مكيس - لانا - ليندا - عدن</t>
+  </si>
+  <si>
+    <t>سفانة - إسماعيل - حمادية</t>
+  </si>
+  <si>
+    <t>راما</t>
+  </si>
+  <si>
+    <t>منصور - نجار - علي</t>
+  </si>
+  <si>
+    <t>علا - أمل</t>
+  </si>
+  <si>
+    <t>أشرفي</t>
+  </si>
+  <si>
+    <t>شهد - زين - طاهر - آية خلوف</t>
+  </si>
+  <si>
+    <t>ويس - غرام - علا بكري</t>
   </si>
   <si>
     <t>روشان - جودي</t>
   </si>
   <si>
-    <t>لانا</t>
-  </si>
-  <si>
-    <t>ليندا - براءة - يمنى - سالي</t>
-  </si>
-  <si>
-    <t>شهد - زين - طاهر</t>
-  </si>
-  <si>
-    <t>فاتن - ساكت</t>
-  </si>
-  <si>
-    <t>دندل</t>
-  </si>
-  <si>
-    <t>كردية - كجان - نجار - مكيس</t>
-  </si>
-  <si>
-    <t>قاسم - سلمان - كبب</t>
-  </si>
-  <si>
-    <t>سلام عرب - نتالي - آية خلوف</t>
-  </si>
-  <si>
-    <t>عدن - راما - ريم ماضي - عائشة</t>
-  </si>
-  <si>
-    <t>بازركان - رؤى - علا بكري</t>
-  </si>
-  <si>
-    <t>تمو - علا</t>
-  </si>
-  <si>
-    <t>غزال</t>
-  </si>
-  <si>
-    <t>محي الدين - سالي - رشا - أنس</t>
-  </si>
-  <si>
-    <t>حمادية - اسماعيل - منار</t>
-  </si>
-  <si>
-    <t>ليندا - لانا - جمیلی</t>
-  </si>
-  <si>
-    <t>حسن - خالد - قمر - ايمان</t>
-  </si>
-  <si>
-    <t>مريم - تسنيم - هيا</t>
-  </si>
-  <si>
-    <t>سفانة - رفاعي</t>
-  </si>
-  <si>
-    <t>روان</t>
-  </si>
-  <si>
-    <t>ميسم - همسة - يمنى - براءة</t>
-  </si>
-  <si>
-    <t>فرح - كوثر - لين</t>
-  </si>
-  <si>
-    <t>نجار - رشواني - غرام</t>
-  </si>
-  <si>
-    <t>روابي - بركات</t>
-  </si>
-  <si>
-    <t>ريم ماضي - راما - أمل</t>
-  </si>
-  <si>
-    <t>عبدالو - اريج</t>
-  </si>
-  <si>
-    <t>انجي</t>
-  </si>
-  <si>
-    <t>مهندس - أشرفي - بتول - آية خلوف</t>
-  </si>
-  <si>
-    <t>كابرئيل - دياب - سيد علي</t>
-  </si>
-  <si>
-    <t>احمد - اماني</t>
-  </si>
-  <si>
-    <t>عبدالله - كردية - كجان - أنس</t>
-  </si>
-  <si>
-    <t>رؤى - خديجة</t>
-  </si>
-  <si>
-    <t>روشان</t>
-  </si>
-  <si>
-    <t>مكيس - جمیلی - علا اليوسف - محي الدين</t>
-  </si>
-  <si>
-    <t>اسماعيل - تسنيم - منار</t>
-  </si>
-  <si>
-    <t>همسة</t>
-  </si>
-  <si>
-    <t>علا بكري - سلام عرب - قمر</t>
-  </si>
-  <si>
-    <t>لينا - ساكت</t>
-  </si>
-  <si>
-    <t>نتالي</t>
-  </si>
-  <si>
-    <t>بازركان - عدن - ويس - وتي - هيا</t>
-  </si>
-  <si>
-    <t>ريما - شهابي - خديجة</t>
-  </si>
-  <si>
-    <t>مركن - غزال</t>
-  </si>
-  <si>
-    <t>رحاب</t>
-  </si>
-  <si>
-    <t>مكانسي</t>
-  </si>
-  <si>
-    <t>نجار</t>
-  </si>
-  <si>
-    <t>سارة - ميسم - سالي - مريم</t>
-  </si>
-  <si>
-    <t>كبب - كوثر - فرح</t>
-  </si>
-  <si>
-    <t>دليفان - رشا - علا خلوف</t>
-  </si>
-  <si>
-    <t>فاتن - دندل</t>
-  </si>
-  <si>
-    <t>ليندا - يمنى - براءة - آمنة - رؤى</t>
-  </si>
-  <si>
-    <t>ايمان - سدرة - أمل</t>
-  </si>
-  <si>
-    <t>جودي</t>
-  </si>
-  <si>
-    <t>زين</t>
-  </si>
-  <si>
-    <t>طاهر - شهد - رشواني - محي الدين</t>
-  </si>
-  <si>
-    <t>شيماء - ايلاف - ديمة</t>
-  </si>
-  <si>
-    <t>عبدالله - كجان - أشرفي</t>
-  </si>
-  <si>
-    <t>قطنجي - زين الدين</t>
-  </si>
-  <si>
-    <t>حرح - ريم ماضي - راما - بتول</t>
-  </si>
-  <si>
-    <t>جمیلی - نتالي - رؤى</t>
-  </si>
-  <si>
-    <t>غزال - سفانة</t>
-  </si>
-  <si>
-    <t>رفاعي</t>
-  </si>
-  <si>
-    <t>ميسم - علا اليوسف - سلام عرب - بانة</t>
-  </si>
-  <si>
-    <t>قاسم - سلمان - حمادية</t>
-  </si>
-  <si>
-    <t>خديجة - شهابي - رحاب</t>
-  </si>
-  <si>
-    <t>علا - تمو</t>
-  </si>
-  <si>
-    <t>اسلام - منصور - علي - خالد</t>
-  </si>
-  <si>
-    <t>يمنى - براءة - سدرة</t>
-  </si>
-  <si>
-    <t>حريري - سيد علي</t>
-  </si>
-  <si>
-    <t>اروى</t>
-  </si>
-  <si>
-    <t>سالي</t>
-  </si>
-  <si>
-    <t>مكيس - همسة - آمنة - نجار</t>
-  </si>
-  <si>
-    <t>دياب - كابرئيل - منار</t>
-  </si>
-  <si>
-    <t>مريم - تسنيم - علا بكري</t>
-  </si>
-  <si>
-    <t>سدرة - سلات</t>
-  </si>
-  <si>
-    <t>لانا - عدن - ويس - وتي</t>
-  </si>
-  <si>
-    <t>آية خلوف - أمل - علا اليوسف</t>
-  </si>
-  <si>
-    <t>دندل - لين</t>
-  </si>
-  <si>
-    <t>فاتن</t>
-  </si>
-  <si>
-    <t>سارة - محي الدين - ريم ماضي - راما</t>
-  </si>
-  <si>
-    <t>كوثر - فرح - تيما</t>
-  </si>
-  <si>
-    <t>قمر</t>
-  </si>
-  <si>
-    <t>عبدالله - كردية - كجان</t>
-  </si>
-  <si>
-    <t>أنس</t>
-  </si>
-  <si>
-    <t>شهد - طاهر - علا خلوف - هيا</t>
-  </si>
-  <si>
-    <t>حسن - خالد - حرح</t>
-  </si>
-  <si>
-    <t>تسنيم - مكانسي</t>
-  </si>
-  <si>
-    <t>رشواني</t>
-  </si>
-  <si>
-    <t>مركن</t>
-  </si>
-  <si>
-    <t>ميسم - اسلام - منصور - علي</t>
-  </si>
-  <si>
-    <t>كبب - هبة - غزال</t>
-  </si>
-  <si>
-    <t>رشا</t>
-  </si>
-  <si>
-    <t>سلام عرب - بانة - بازركان</t>
-  </si>
-  <si>
-    <t>اماني - احمد</t>
-  </si>
-  <si>
-    <t>علا بكري - عائشة - غرام - جمیلی</t>
-  </si>
-  <si>
-    <t>بتول - وتي - تسنيم</t>
+    <t>فرواتي - ميسم - عبدالله - كردية - كجان</t>
+  </si>
+  <si>
+    <t>سلمان - دندل - قاسم</t>
+  </si>
+  <si>
+    <t>رشا - سلام عرب - هيا - بازركان</t>
+  </si>
+  <si>
+    <t>ريما - رحاب - خديجة</t>
+  </si>
+  <si>
+    <t>إنجي - أمل</t>
+  </si>
+  <si>
+    <t>علا</t>
+  </si>
+  <si>
+    <t>سارة - همسة - أشرفي - سدرة - شهابي</t>
+  </si>
+  <si>
+    <t>عبدالو - كابرييل - دياب</t>
+  </si>
+  <si>
+    <t>آمنة - قمر - تسنيم</t>
   </si>
   <si>
     <t>رفاعي - نجار</t>
   </si>
   <si>
-    <t>مريم</t>
-  </si>
-  <si>
-    <t>قطنجي</t>
-  </si>
-  <si>
-    <t>مكيس - همسة - ويس - محي الدين</t>
-  </si>
-  <si>
-    <t>امل - علا - زين الدين</t>
-  </si>
-  <si>
-    <t>نجار - رؤى - سدرة</t>
-  </si>
-  <si>
-    <t>كابرئيل - دياب</t>
-  </si>
-  <si>
-    <t>هيا - ليندا - لانا - يمنى - براءة</t>
-  </si>
-  <si>
-    <t>غزال - سدرة</t>
-  </si>
-  <si>
-    <t>روابي</t>
-  </si>
-  <si>
-    <t>علا خلوف - فرواتي - أشرفي - ريم ماضي</t>
-  </si>
-  <si>
-    <t>سلمان - قاسم - روان</t>
-  </si>
-  <si>
-    <t>راما</t>
-  </si>
-  <si>
-    <t>كردية - قمر - علا اليوسف</t>
-  </si>
-  <si>
-    <t>علي - عبدالله - كجان - اسلام - منصور</t>
-  </si>
-  <si>
-    <t>بازركان - رؤى - سلام عرب</t>
-  </si>
-  <si>
-    <t>اروى - كبب</t>
-  </si>
-  <si>
-    <t>سيد علي</t>
-  </si>
-  <si>
-    <t>ميسم - ويس - بانة - عائشة</t>
-  </si>
-  <si>
-    <t>ديمة - ايلاف - شيماء</t>
-  </si>
-  <si>
-    <t>حسن - خالد - أنس</t>
-  </si>
-  <si>
-    <t>أمل - غرام - ليندا - لانا</t>
-  </si>
-  <si>
-    <t>علا خلوف - آمنة - جمیلی</t>
-  </si>
-  <si>
-    <t>احمد - نجار</t>
-  </si>
-  <si>
-    <t>اماني</t>
-  </si>
-  <si>
-    <t>رشا - مهندس - محي الدين - همسة</t>
-  </si>
-  <si>
-    <t>كوثر - تيما - منار</t>
-  </si>
-  <si>
-    <t>يمنى - براءة - رشواني</t>
-  </si>
-  <si>
-    <t>اريج - خديجة</t>
-  </si>
-  <si>
-    <t>حرح - سدرة - علا اليوسف</t>
-  </si>
-  <si>
-    <t>سلات - سنا</t>
-  </si>
-  <si>
-    <t>بركات</t>
-  </si>
-  <si>
-    <t>مكيس - لانا - ليندا - عدن</t>
-  </si>
-  <si>
-    <t>حمادية - اسماعيل - سفانة</t>
-  </si>
-  <si>
-    <t>منصور - نجار - علي</t>
-  </si>
-  <si>
-    <t>امل - علا</t>
-  </si>
-  <si>
-    <t>أشرفي</t>
-  </si>
-  <si>
-    <t>شهد - زين - طاهر - آية خلوف</t>
-  </si>
-  <si>
-    <t>ويس - غرام - علا بكري</t>
-  </si>
-  <si>
-    <t>جودي - روشان</t>
-  </si>
-  <si>
-    <t>ميسم - عبدالله - كردية - كجان</t>
-  </si>
-  <si>
-    <t>قاسم - دندل - سلمان</t>
-  </si>
-  <si>
-    <t>رشا - سلام عرب - هيا - بازركان</t>
-  </si>
-  <si>
-    <t>ريما - رحاب - خديجة</t>
-  </si>
-  <si>
-    <t>امل - انجي</t>
-  </si>
-  <si>
-    <t>علا</t>
-  </si>
-  <si>
-    <t>همسة - أشرفي - سدرة - شهابي</t>
-  </si>
-  <si>
-    <t>دياب - كابرئيل - عبدالو</t>
-  </si>
-  <si>
-    <t>آمنة - قمر - تسنيم</t>
-  </si>
-  <si>
-    <t>نجار - رفاعي</t>
-  </si>
-  <si>
     <t>بانة - رؤى - علا خلوف - نتالي</t>
   </si>
   <si>
     <t>عائشة - رشواني - عدن</t>
   </si>
   <si>
-    <t>بركات - فاتن</t>
-  </si>
-  <si>
-    <t>يمنى</t>
+    <t>فاتن - بركات</t>
+  </si>
+  <si>
+    <t>يمنى - برءة</t>
   </si>
   <si>
     <t>سنا</t>
   </si>
   <si>
-    <t>مكيس - محي الدين - شهد - زين</t>
-  </si>
-  <si>
-    <t>اماني - تيما - كوثر</t>
-  </si>
-  <si>
-    <t>طاهر</t>
-  </si>
-  <si>
-    <t>سلام عرب - ريم ماضي - راما</t>
-  </si>
-  <si>
-    <t>سدرة - خديجة</t>
-  </si>
-  <si>
-    <t>غرام - أنس - اسلام - بتول - حرح</t>
+    <t>مكيس - محي الدين - شهد - زين - طاهر</t>
+  </si>
+  <si>
+    <t>كوثر - تيما - أماني</t>
+  </si>
+  <si>
+    <t>سلام عرب</t>
+  </si>
+  <si>
+    <t>ريم ماضي - راما - ايمان</t>
+  </si>
+  <si>
+    <t>خديجة - سدرة</t>
+  </si>
+  <si>
+    <t>أنس - اسلام - بتول - حرح</t>
   </si>
   <si>
     <t>الإعداد</t>
@@ -1471,7 +1474,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1495,6 +1498,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1505,14 +1511,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font/>
       <fill>
@@ -1543,13 +1542,6 @@
     <dxf>
       <font/>
       <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF2DBDB"/>
           <bgColor rgb="FFF2DBDB"/>
@@ -1557,29 +1549,22 @@
       </fill>
       <border/>
     </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
-    </dxf>
   </dxfs>
   <tableStyles count="3">
     <tableStyle count="3" pivot="0" name="idari-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement type="headerRow"/>
+      <tableStyleElement dxfId="1" type="firstRowStripe"/>
+      <tableStyleElement dxfId="2" type="secondRowStripe"/>
     </tableStyle>
     <tableStyle count="3" pivot="0" name="mnaobat-style">
-      <tableStyleElement dxfId="4" type="headerRow"/>
-      <tableStyleElement dxfId="5" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement type="headerRow"/>
+      <tableStyleElement dxfId="3" type="firstRowStripe"/>
+      <tableStyleElement dxfId="2" type="secondRowStripe"/>
     </tableStyle>
     <tableStyle count="3" pivot="0" name="settings-style">
-      <tableStyleElement dxfId="6" type="headerRow"/>
-      <tableStyleElement dxfId="3" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="2" type="secondRowStripe"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -3486,9 +3471,7 @@
         <v>100</v>
       </c>
       <c r="E4" s="7"/>
-      <c r="F4" s="5" t="s">
-        <v>101</v>
-      </c>
+      <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="I4" s="6"/>
@@ -3509,13 +3492,13 @@
         <v>45</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>104</v>
       </c>
       <c r="H5" s="7"/>
       <c r="I5" s="6"/>
@@ -3533,11 +3516,11 @@
         <v>92</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
@@ -3556,16 +3539,16 @@
         <v>92</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>110</v>
       </c>
       <c r="H7" s="7"/>
       <c r="I7" s="6"/>
@@ -3583,11 +3566,11 @@
         <v>92</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
@@ -3606,13 +3589,13 @@
         <v>92</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>115</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
@@ -3628,19 +3611,19 @@
         <v>46205.0</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E10" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>119</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="6"/>
@@ -3655,19 +3638,19 @@
         <v>46205.0</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E11" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="G11" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="H11" s="7"/>
       <c r="I11" s="6"/>
@@ -3682,15 +3665,13 @@
         <v>46205.0</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E12" s="7"/>
-      <c r="F12" s="5" t="s">
-        <v>123</v>
-      </c>
+      <c r="F12" s="7"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="6"/>
@@ -3705,19 +3686,19 @@
         <v>46205.0</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E13" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>124</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>126</v>
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="6"/>
@@ -3732,14 +3713,14 @@
         <v>46205.0</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
@@ -3755,19 +3736,19 @@
         <v>46205.0</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E15" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>130</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="6"/>
@@ -3782,14 +3763,14 @@
         <v>46205.0</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -3805,16 +3786,16 @@
         <v>46205.0</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -3830,19 +3811,19 @@
         <v>46206.0</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E18" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>137</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="6"/>
@@ -3857,19 +3838,19 @@
         <v>46206.0</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E19" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>138</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>140</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="6"/>
@@ -3884,15 +3865,13 @@
         <v>46206.0</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E20" s="7"/>
-      <c r="F20" s="5" t="s">
-        <v>141</v>
-      </c>
+      <c r="F20" s="7"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
       <c r="I20" s="6"/>
@@ -3907,19 +3886,19 @@
         <v>46206.0</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="6"/>
@@ -3934,14 +3913,14 @@
         <v>46206.0</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E22" s="7"/>
       <c r="F22" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
@@ -3957,19 +3936,19 @@
         <v>46206.0</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="6"/>
@@ -3984,14 +3963,14 @@
         <v>46206.0</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
@@ -4007,16 +3986,16 @@
         <v>46206.0</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
@@ -4032,19 +4011,19 @@
         <v>46207.0</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="6"/>
@@ -4059,19 +4038,19 @@
         <v>46207.0</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="6"/>
@@ -4086,17 +4065,13 @@
         <v>46207.0</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>160</v>
-      </c>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
       <c r="I28" s="6"/>
@@ -4111,19 +4086,19 @@
         <v>46207.0</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="6"/>
@@ -4138,14 +4113,14 @@
         <v>46207.0</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" s="5" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
@@ -4161,19 +4136,19 @@
         <v>46207.0</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="6"/>
@@ -4188,14 +4163,14 @@
         <v>46207.0</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="5" t="s">
-        <v>106</v>
+        <v>163</v>
       </c>
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
@@ -4211,16 +4186,16 @@
         <v>46207.0</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
@@ -4236,19 +4211,19 @@
         <v>46208.0</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="6"/>
@@ -4263,19 +4238,19 @@
         <v>46208.0</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="H35" s="7"/>
       <c r="I35" s="6"/>
@@ -4290,17 +4265,13 @@
         <v>46208.0</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E36" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>178</v>
-      </c>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
       <c r="I36" s="6"/>
@@ -4315,19 +4286,19 @@
         <v>46208.0</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="H37" s="7"/>
       <c r="I37" s="6"/>
@@ -4342,16 +4313,16 @@
         <v>46208.0</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>183</v>
+        <v>142</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
@@ -4367,19 +4338,19 @@
         <v>46208.0</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="H39" s="7"/>
       <c r="I39" s="6"/>
@@ -4394,16 +4365,16 @@
         <v>46208.0</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
@@ -4419,16 +4390,16 @@
         <v>46208.0</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
@@ -4444,19 +4415,19 @@
         <v>46209.0</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="H42" s="7"/>
       <c r="I42" s="6"/>
@@ -4471,19 +4442,19 @@
         <v>46209.0</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="H43" s="7"/>
       <c r="I43" s="6"/>
@@ -4498,17 +4469,15 @@
         <v>46209.0</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>101</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="F44" s="7"/>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
       <c r="I44" s="6"/>
@@ -4523,19 +4492,19 @@
         <v>46209.0</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="H45" s="7"/>
       <c r="I45" s="6"/>
@@ -4550,16 +4519,16 @@
         <v>46209.0</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
@@ -4575,19 +4544,19 @@
         <v>46209.0</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="H47" s="7"/>
       <c r="I47" s="6"/>
@@ -4602,16 +4571,16 @@
         <v>46209.0</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>138</v>
+        <v>200</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
@@ -4627,16 +4596,16 @@
         <v>46209.0</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="G49" s="7"/>
       <c r="H49" s="7"/>
@@ -4652,19 +4621,19 @@
         <v>46210.0</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H50" s="7"/>
       <c r="I50" s="6"/>
@@ -4679,19 +4648,19 @@
         <v>46210.0</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="H51" s="7"/>
       <c r="I51" s="6"/>
@@ -4706,17 +4675,15 @@
         <v>46210.0</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>217</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="F52" s="7"/>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
       <c r="I52" s="6"/>
@@ -4731,19 +4698,19 @@
         <v>46210.0</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="H53" s="7"/>
       <c r="I53" s="6"/>
@@ -4758,16 +4725,16 @@
         <v>46210.0</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
@@ -4783,19 +4750,19 @@
         <v>46210.0</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="H55" s="7"/>
       <c r="I55" s="6"/>
@@ -4810,16 +4777,16 @@
         <v>46210.0</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>159</v>
+        <v>219</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
@@ -4835,16 +4802,16 @@
         <v>46210.0</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
@@ -4866,13 +4833,13 @@
         <v>93</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="H58" s="7"/>
       <c r="I58" s="6"/>
@@ -4893,13 +4860,13 @@
         <v>97</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="H59" s="7"/>
       <c r="I59" s="6"/>
@@ -4920,11 +4887,9 @@
         <v>100</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>236</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="F60" s="7"/>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
       <c r="I60" s="6"/>
@@ -4945,13 +4910,13 @@
         <v>45</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="H61" s="7"/>
       <c r="I61" s="6"/>
@@ -4969,13 +4934,13 @@
         <v>92</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
@@ -4994,16 +4959,16 @@
         <v>92</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="H63" s="7"/>
       <c r="I63" s="6"/>
@@ -5021,13 +4986,13 @@
         <v>92</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>141</v>
+        <v>238</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
@@ -5046,13 +5011,13 @@
         <v>92</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
@@ -5068,19 +5033,19 @@
         <v>46212.0</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="H66" s="7"/>
       <c r="I66" s="6"/>
@@ -5095,19 +5060,19 @@
         <v>46212.0</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="H67" s="7"/>
       <c r="I67" s="6"/>
@@ -5122,17 +5087,15 @@
         <v>46212.0</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>121</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="F68" s="7"/>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
       <c r="I68" s="6"/>
@@ -5147,19 +5110,19 @@
         <v>46212.0</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="H69" s="7"/>
       <c r="I69" s="6"/>
@@ -5174,16 +5137,16 @@
         <v>46212.0</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>178</v>
+        <v>252</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
@@ -5199,19 +5162,19 @@
         <v>46212.0</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="H71" s="7"/>
       <c r="I71" s="6"/>
@@ -5226,16 +5189,16 @@
         <v>46212.0</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>187</v>
+        <v>256</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
@@ -5251,16 +5214,16 @@
         <v>46212.0</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="7"/>
@@ -5276,19 +5239,19 @@
         <v>46213.0</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="H74" s="7"/>
       <c r="I74" s="6"/>
@@ -5303,19 +5266,19 @@
         <v>46213.0</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="H75" s="7"/>
       <c r="I75" s="6"/>
@@ -5330,17 +5293,15 @@
         <v>46213.0</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>270</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="F76" s="7"/>
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
       <c r="I76" s="6"/>
@@ -5355,19 +5316,19 @@
         <v>46213.0</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="H77" s="7"/>
       <c r="I77" s="6"/>
@@ -5382,16 +5343,16 @@
         <v>46213.0</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>226</v>
+        <v>270</v>
       </c>
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
@@ -5407,19 +5368,19 @@
         <v>46213.0</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="H79" s="7"/>
       <c r="I79" s="6"/>
@@ -5434,16 +5395,16 @@
         <v>46213.0</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>127</v>
+        <v>275</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
@@ -5459,16 +5420,16 @@
         <v>46213.0</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
@@ -5484,19 +5445,19 @@
         <v>46214.0</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D82" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="H82" s="7"/>
       <c r="I82" s="6"/>
@@ -5511,19 +5472,19 @@
         <v>46214.0</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>99</v>
+        <v>282</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H83" s="7"/>
       <c r="I83" s="6"/>
@@ -5538,17 +5499,15 @@
         <v>46214.0</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D84" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>287</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="F84" s="7"/>
       <c r="G84" s="7"/>
       <c r="H84" s="7"/>
       <c r="I84" s="6"/>
@@ -5563,19 +5522,19 @@
         <v>46214.0</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H85" s="7"/>
       <c r="I85" s="6"/>
@@ -5590,16 +5549,16 @@
         <v>46214.0</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>214</v>
+        <v>289</v>
       </c>
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
@@ -5615,19 +5574,19 @@
         <v>46214.0</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E87" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="G87" s="5" t="s">
         <v>292</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="G87" s="5" t="s">
-        <v>294</v>
       </c>
       <c r="H87" s="7"/>
       <c r="I87" s="6"/>
@@ -5642,16 +5601,16 @@
         <v>46214.0</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>156</v>
+        <v>293</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>203</v>
+        <v>120</v>
       </c>
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
@@ -5667,16 +5626,16 @@
         <v>46214.0</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E89" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="F89" s="5" t="s">
         <v>295</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>296</v>
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
@@ -5692,17 +5651,17 @@
         <v>46215.0</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E90" s="7"/>
       <c r="F90" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="G90" s="5" t="s">
         <v>297</v>
-      </c>
-      <c r="G90" s="5" t="s">
-        <v>298</v>
       </c>
       <c r="H90" s="7"/>
       <c r="I90" s="6"/>
@@ -5717,17 +5676,17 @@
         <v>46215.0</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E91" s="7"/>
       <c r="F91" s="5" t="s">
-        <v>178</v>
+        <v>252</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H91" s="7"/>
       <c r="I91" s="6"/>
@@ -5742,15 +5701,13 @@
         <v>46215.0</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E92" s="7"/>
-      <c r="F92" s="5" t="s">
-        <v>300</v>
-      </c>
+      <c r="F92" s="7"/>
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
       <c r="I92" s="6"/>
@@ -5765,17 +5722,17 @@
         <v>46215.0</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E93" s="7"/>
       <c r="F93" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H93" s="7"/>
       <c r="I93" s="6"/>
@@ -5790,14 +5747,14 @@
         <v>46215.0</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E94" s="7"/>
       <c r="F94" s="5" t="s">
-        <v>157</v>
+        <v>275</v>
       </c>
       <c r="G94" s="7"/>
       <c r="H94" s="7"/>
@@ -5813,17 +5770,17 @@
         <v>46215.0</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E95" s="7"/>
       <c r="F95" s="5" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H95" s="7"/>
       <c r="I95" s="6"/>
@@ -5838,14 +5795,14 @@
         <v>46215.0</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E96" s="7"/>
       <c r="F96" s="5" t="s">
-        <v>304</v>
+        <v>146</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
@@ -5861,14 +5818,14 @@
         <v>46215.0</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E97" s="7"/>
       <c r="F97" s="5" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
@@ -5884,17 +5841,17 @@
         <v>46216.0</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D98" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E98" s="7"/>
       <c r="F98" s="5" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H98" s="7"/>
       <c r="I98" s="6"/>
@@ -5909,17 +5866,17 @@
         <v>46216.0</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D99" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E99" s="7"/>
       <c r="F99" s="5" t="s">
-        <v>236</v>
+        <v>305</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H99" s="7"/>
       <c r="I99" s="6"/>
@@ -5934,15 +5891,13 @@
         <v>46216.0</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D100" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E100" s="7"/>
-      <c r="F100" s="5" t="s">
-        <v>267</v>
-      </c>
+      <c r="F100" s="7"/>
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
       <c r="I100" s="6"/>
@@ -5957,17 +5912,17 @@
         <v>46216.0</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D101" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E101" s="7"/>
       <c r="F101" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H101" s="7"/>
       <c r="I101" s="6"/>
@@ -5982,14 +5937,14 @@
         <v>46216.0</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E102" s="7"/>
       <c r="F102" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G102" s="7"/>
       <c r="H102" s="7"/>
@@ -6005,17 +5960,17 @@
         <v>46216.0</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E103" s="7"/>
       <c r="F103" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="H103" s="7"/>
       <c r="I103" s="6"/>
@@ -6030,14 +5985,14 @@
         <v>46216.0</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E104" s="7"/>
       <c r="F104" s="5" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="G104" s="7"/>
       <c r="H104" s="7"/>
@@ -6053,14 +6008,14 @@
         <v>46216.0</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E105" s="7"/>
       <c r="F105" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
@@ -6076,17 +6031,17 @@
         <v>46217.0</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D106" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E106" s="7"/>
       <c r="F106" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H106" s="7"/>
       <c r="I106" s="6"/>
@@ -6101,17 +6056,17 @@
         <v>46217.0</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E107" s="7"/>
       <c r="F107" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H107" s="7"/>
       <c r="I107" s="6"/>
@@ -6126,15 +6081,13 @@
         <v>46217.0</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D108" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E108" s="7"/>
-      <c r="F108" s="5" t="s">
-        <v>101</v>
-      </c>
+      <c r="F108" s="7"/>
       <c r="G108" s="7"/>
       <c r="H108" s="7"/>
       <c r="I108" s="6"/>
@@ -6149,17 +6102,17 @@
         <v>46217.0</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E109" s="7"/>
       <c r="F109" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H109" s="7"/>
       <c r="I109" s="6"/>
@@ -6174,14 +6127,14 @@
         <v>46217.0</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E110" s="7"/>
       <c r="F110" s="5" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="G110" s="7"/>
       <c r="H110" s="7"/>
@@ -6197,17 +6150,17 @@
         <v>46217.0</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E111" s="7"/>
       <c r="F111" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H111" s="7"/>
       <c r="I111" s="6"/>
@@ -6222,14 +6175,14 @@
         <v>46217.0</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E112" s="7"/>
       <c r="F112" s="5" t="s">
-        <v>141</v>
+        <v>238</v>
       </c>
       <c r="G112" s="7"/>
       <c r="H112" s="7"/>
@@ -6245,14 +6198,14 @@
         <v>46217.0</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E113" s="7"/>
       <c r="F113" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G113" s="7"/>
       <c r="H113" s="7"/>
@@ -6275,10 +6228,10 @@
       </c>
       <c r="E114" s="7"/>
       <c r="F114" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H114" s="7"/>
       <c r="I114" s="6"/>
@@ -6300,10 +6253,10 @@
       </c>
       <c r="E115" s="7"/>
       <c r="F115" s="5" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H115" s="7"/>
       <c r="I115" s="6"/>
@@ -6324,9 +6277,7 @@
         <v>100</v>
       </c>
       <c r="E116" s="7"/>
-      <c r="F116" s="5" t="s">
-        <v>217</v>
-      </c>
+      <c r="F116" s="7"/>
       <c r="G116" s="7"/>
       <c r="H116" s="7"/>
       <c r="I116" s="6"/>
@@ -6348,10 +6299,10 @@
       </c>
       <c r="E117" s="7"/>
       <c r="F117" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="G117" s="5" t="s">
         <v>323</v>
-      </c>
-      <c r="G117" s="5" t="s">
-        <v>324</v>
       </c>
       <c r="H117" s="7"/>
       <c r="I117" s="6"/>
@@ -6369,11 +6320,11 @@
         <v>92</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E118" s="7"/>
       <c r="F118" s="5" t="s">
-        <v>178</v>
+        <v>252</v>
       </c>
       <c r="G118" s="7"/>
       <c r="H118" s="7"/>
@@ -6392,14 +6343,14 @@
         <v>92</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E119" s="7"/>
       <c r="F119" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="G119" s="5" t="s">
         <v>325</v>
-      </c>
-      <c r="G119" s="5" t="s">
-        <v>326</v>
       </c>
       <c r="H119" s="7"/>
       <c r="I119" s="6"/>
@@ -6417,7 +6368,7 @@
         <v>92</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E120" s="7"/>
       <c r="F120" s="5" t="s">
@@ -6440,11 +6391,11 @@
         <v>92</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E121" s="7"/>
       <c r="F121" s="5" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="G121" s="7"/>
       <c r="H121" s="7"/>
@@ -6460,17 +6411,17 @@
         <v>46219.0</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E122" s="7"/>
       <c r="F122" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="G122" s="5" t="s">
         <v>327</v>
-      </c>
-      <c r="G122" s="5" t="s">
-        <v>328</v>
       </c>
       <c r="H122" s="7"/>
       <c r="I122" s="6"/>
@@ -6485,17 +6436,17 @@
         <v>46219.0</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E123" s="7"/>
       <c r="F123" s="5" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H123" s="7"/>
       <c r="I123" s="6"/>
@@ -6510,15 +6461,13 @@
         <v>46219.0</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D124" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E124" s="7"/>
-      <c r="F124" s="5" t="s">
-        <v>101</v>
-      </c>
+      <c r="F124" s="7"/>
       <c r="G124" s="7"/>
       <c r="H124" s="7"/>
       <c r="I124" s="6"/>
@@ -6533,17 +6482,17 @@
         <v>46219.0</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E125" s="7"/>
       <c r="F125" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="G125" s="5" t="s">
         <v>330</v>
-      </c>
-      <c r="G125" s="5" t="s">
-        <v>331</v>
       </c>
       <c r="H125" s="7"/>
       <c r="I125" s="6"/>
@@ -6558,14 +6507,14 @@
         <v>46219.0</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E126" s="7"/>
       <c r="F126" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G126" s="7"/>
       <c r="H126" s="7"/>
@@ -6581,17 +6530,17 @@
         <v>46219.0</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E127" s="7"/>
       <c r="F127" s="5" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H127" s="7"/>
       <c r="I127" s="6"/>
@@ -6606,14 +6555,14 @@
         <v>46219.0</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E128" s="7"/>
       <c r="F128" s="5" t="s">
-        <v>160</v>
+        <v>270</v>
       </c>
       <c r="G128" s="7"/>
       <c r="H128" s="7"/>
@@ -6629,14 +6578,14 @@
         <v>46219.0</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E129" s="7"/>
       <c r="F129" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G129" s="7"/>
       <c r="H129" s="7"/>
@@ -6652,17 +6601,17 @@
         <v>46220.0</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D130" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E130" s="7"/>
       <c r="F130" s="5" t="s">
-        <v>248</v>
+        <v>318</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H130" s="7"/>
       <c r="I130" s="6"/>
@@ -6677,14 +6626,14 @@
         <v>46220.0</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E131" s="7"/>
       <c r="F131" s="5" t="s">
-        <v>233</v>
+        <v>334</v>
       </c>
       <c r="G131" s="5" t="s">
         <v>335</v>
@@ -6702,15 +6651,13 @@
         <v>46220.0</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D132" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E132" s="7"/>
-      <c r="F132" s="5" t="s">
-        <v>251</v>
-      </c>
+      <c r="F132" s="7"/>
       <c r="G132" s="7"/>
       <c r="H132" s="7"/>
       <c r="I132" s="6"/>
@@ -6725,7 +6672,7 @@
         <v>46220.0</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>45</v>
@@ -6750,10 +6697,10 @@
         <v>46220.0</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E134" s="7"/>
       <c r="F134" s="5" t="s">
@@ -6773,10 +6720,10 @@
         <v>46220.0</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E135" s="7"/>
       <c r="F135" s="5" t="s">
@@ -6798,14 +6745,14 @@
         <v>46220.0</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E136" s="7"/>
       <c r="F136" s="5" t="s">
-        <v>341</v>
+        <v>105</v>
       </c>
       <c r="G136" s="7"/>
       <c r="H136" s="7"/>
@@ -6821,14 +6768,14 @@
         <v>46220.0</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E137" s="7"/>
       <c r="F137" s="5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G137" s="7"/>
       <c r="H137" s="7"/>
@@ -6844,17 +6791,17 @@
         <v>46221.0</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D138" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E138" s="7"/>
       <c r="F138" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="G138" s="5" t="s">
         <v>343</v>
-      </c>
-      <c r="G138" s="5" t="s">
-        <v>344</v>
       </c>
       <c r="H138" s="7"/>
       <c r="I138" s="6"/>
@@ -6869,17 +6816,17 @@
         <v>46221.0</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E139" s="7"/>
       <c r="F139" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="G139" s="5" t="s">
         <v>345</v>
-      </c>
-      <c r="G139" s="5" t="s">
-        <v>346</v>
       </c>
       <c r="H139" s="7"/>
       <c r="I139" s="6"/>
@@ -6894,15 +6841,13 @@
         <v>46221.0</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D140" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E140" s="7"/>
-      <c r="F140" s="5" t="s">
-        <v>347</v>
-      </c>
+      <c r="F140" s="7"/>
       <c r="G140" s="7"/>
       <c r="H140" s="7"/>
       <c r="I140" s="6"/>
@@ -6917,17 +6862,17 @@
         <v>46221.0</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E141" s="7"/>
       <c r="F141" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H141" s="7"/>
       <c r="I141" s="6"/>
@@ -6942,14 +6887,14 @@
         <v>46221.0</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E142" s="7"/>
       <c r="F142" s="5" t="s">
-        <v>139</v>
+        <v>252</v>
       </c>
       <c r="G142" s="7"/>
       <c r="H142" s="7"/>
@@ -6965,17 +6910,17 @@
         <v>46221.0</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E143" s="7"/>
       <c r="F143" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H143" s="7"/>
       <c r="I143" s="6"/>
@@ -6990,14 +6935,14 @@
         <v>46221.0</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E144" s="7"/>
       <c r="F144" s="5" t="s">
-        <v>304</v>
+        <v>142</v>
       </c>
       <c r="G144" s="7"/>
       <c r="H144" s="7"/>
@@ -7013,14 +6958,14 @@
         <v>46221.0</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E145" s="7"/>
       <c r="F145" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G145" s="7"/>
       <c r="H145" s="7"/>
@@ -7036,17 +6981,17 @@
         <v>46222.0</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E146" s="7"/>
       <c r="F146" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H146" s="7"/>
       <c r="I146" s="6"/>
@@ -7061,17 +7006,17 @@
         <v>46222.0</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E147" s="7"/>
       <c r="F147" s="5" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H147" s="7"/>
       <c r="I147" s="6"/>
@@ -7086,15 +7031,13 @@
         <v>46222.0</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D148" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E148" s="7"/>
-      <c r="F148" s="5" t="s">
-        <v>355</v>
-      </c>
+      <c r="F148" s="7"/>
       <c r="G148" s="7"/>
       <c r="H148" s="7"/>
       <c r="I148" s="6"/>
@@ -7109,17 +7052,17 @@
         <v>46222.0</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E149" s="7"/>
       <c r="F149" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="H149" s="7"/>
       <c r="I149" s="6"/>
@@ -7134,14 +7077,12 @@
         <v>46222.0</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D150" s="5" t="s">
-        <v>105</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="D150" s="7"/>
       <c r="E150" s="7"/>
       <c r="F150" s="5" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="G150" s="7"/>
       <c r="H150" s="7"/>
@@ -7157,17 +7098,17 @@
         <v>46222.0</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E151" s="7"/>
       <c r="F151" s="5" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="H151" s="7"/>
       <c r="I151" s="6"/>
@@ -7182,14 +7123,14 @@
         <v>46222.0</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E152" s="7"/>
       <c r="F152" s="5" t="s">
-        <v>160</v>
+        <v>270</v>
       </c>
       <c r="G152" s="7"/>
       <c r="H152" s="7"/>
@@ -7205,14 +7146,14 @@
         <v>46222.0</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E153" s="7"/>
       <c r="F153" s="5" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="G153" s="7"/>
       <c r="H153" s="7"/>
@@ -7228,17 +7169,17 @@
         <v>46223.0</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D154" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E154" s="7"/>
       <c r="F154" s="5" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="H154" s="7"/>
       <c r="I154" s="6"/>
@@ -7253,17 +7194,17 @@
         <v>46223.0</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D155" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E155" s="7"/>
       <c r="F155" s="5" t="s">
-        <v>157</v>
+        <v>275</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="H155" s="7"/>
       <c r="I155" s="6"/>
@@ -7278,15 +7219,13 @@
         <v>46223.0</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D156" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E156" s="7"/>
-      <c r="F156" s="5" t="s">
-        <v>217</v>
-      </c>
+      <c r="F156" s="7"/>
       <c r="G156" s="7"/>
       <c r="H156" s="7"/>
       <c r="I156" s="6"/>
@@ -7301,17 +7240,17 @@
         <v>46223.0</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D157" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E157" s="7"/>
       <c r="F157" s="5" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="H157" s="7"/>
       <c r="I157" s="6"/>
@@ -7326,14 +7265,14 @@
         <v>46223.0</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E158" s="7"/>
       <c r="F158" s="5" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="G158" s="7"/>
       <c r="H158" s="7"/>
@@ -7349,17 +7288,17 @@
         <v>46223.0</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E159" s="7"/>
       <c r="F159" s="5" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="G159" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="H159" s="7"/>
       <c r="I159" s="6"/>
@@ -7374,14 +7313,14 @@
         <v>46223.0</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E160" s="7"/>
       <c r="F160" s="5" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="G160" s="7"/>
       <c r="H160" s="7"/>
@@ -7397,14 +7336,14 @@
         <v>46223.0</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E161" s="7"/>
       <c r="F161" s="5" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="G161" s="7"/>
       <c r="H161" s="7"/>
@@ -7420,17 +7359,17 @@
         <v>46224.0</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D162" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E162" s="7"/>
       <c r="F162" s="5" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H162" s="7"/>
       <c r="I162" s="6"/>
@@ -7445,17 +7384,17 @@
         <v>46224.0</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D163" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E163" s="7"/>
       <c r="F163" s="5" t="s">
-        <v>178</v>
+        <v>252</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="H163" s="7"/>
       <c r="I163" s="6"/>
@@ -7470,15 +7409,13 @@
         <v>46224.0</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D164" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E164" s="7"/>
-      <c r="F164" s="5" t="s">
-        <v>372</v>
-      </c>
+      <c r="F164" s="7"/>
       <c r="G164" s="7"/>
       <c r="H164" s="7"/>
       <c r="I164" s="6"/>
@@ -7493,17 +7430,17 @@
         <v>46224.0</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D165" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E165" s="7"/>
       <c r="F165" s="5" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="H165" s="7"/>
       <c r="I165" s="6"/>
@@ -7518,14 +7455,14 @@
         <v>46224.0</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E166" s="7"/>
       <c r="F166" s="5" t="s">
-        <v>149</v>
+        <v>371</v>
       </c>
       <c r="G166" s="7"/>
       <c r="H166" s="7"/>
@@ -7541,17 +7478,17 @@
         <v>46224.0</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E167" s="7"/>
       <c r="F167" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="H167" s="7"/>
       <c r="I167" s="6"/>
@@ -7566,14 +7503,14 @@
         <v>46224.0</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E168" s="7"/>
       <c r="F168" s="5" t="s">
-        <v>183</v>
+        <v>142</v>
       </c>
       <c r="G168" s="7"/>
       <c r="H168" s="7"/>
@@ -7589,14 +7526,14 @@
         <v>46224.0</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E169" s="7"/>
       <c r="F169" s="5" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="G169" s="7"/>
       <c r="H169" s="7"/>
@@ -7619,10 +7556,10 @@
       </c>
       <c r="E170" s="7"/>
       <c r="F170" s="5" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="H170" s="7"/>
       <c r="I170" s="6"/>
@@ -7644,10 +7581,10 @@
       </c>
       <c r="E171" s="7"/>
       <c r="F171" s="5" t="s">
-        <v>287</v>
+        <v>159</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="H171" s="7"/>
       <c r="I171" s="6"/>
@@ -7668,9 +7605,7 @@
         <v>100</v>
       </c>
       <c r="E172" s="7"/>
-      <c r="F172" s="5" t="s">
-        <v>101</v>
-      </c>
+      <c r="F172" s="7"/>
       <c r="G172" s="7"/>
       <c r="H172" s="7"/>
       <c r="I172" s="6"/>
@@ -7692,10 +7627,10 @@
       </c>
       <c r="E173" s="7"/>
       <c r="F173" s="5" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="H173" s="7"/>
       <c r="I173" s="6"/>
@@ -7713,11 +7648,11 @@
         <v>92</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E174" s="7"/>
       <c r="F174" s="5" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G174" s="7"/>
       <c r="H174" s="7"/>
@@ -7736,14 +7671,14 @@
         <v>92</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E175" s="7"/>
       <c r="F175" s="5" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H175" s="7"/>
       <c r="I175" s="6"/>
@@ -7761,11 +7696,11 @@
         <v>92</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E176" s="7"/>
       <c r="F176" s="5" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="G176" s="7"/>
       <c r="H176" s="7"/>
@@ -7784,11 +7719,11 @@
         <v>92</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E177" s="7"/>
       <c r="F177" s="5" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="G177" s="7"/>
       <c r="H177" s="7"/>
@@ -7804,17 +7739,17 @@
         <v>46226.0</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D178" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E178" s="7"/>
       <c r="F178" s="5" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="G178" s="5" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="H178" s="7"/>
       <c r="I178" s="6"/>
@@ -7829,17 +7764,17 @@
         <v>46226.0</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D179" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E179" s="7"/>
       <c r="F179" s="5" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="H179" s="7"/>
       <c r="I179" s="6"/>
@@ -7854,15 +7789,13 @@
         <v>46226.0</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D180" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E180" s="7"/>
-      <c r="F180" s="5" t="s">
-        <v>372</v>
-      </c>
+      <c r="F180" s="7"/>
       <c r="G180" s="7"/>
       <c r="H180" s="7"/>
       <c r="I180" s="6"/>
@@ -7877,17 +7810,17 @@
         <v>46226.0</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D181" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E181" s="7"/>
       <c r="F181" s="5" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="G181" s="5" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="H181" s="7"/>
       <c r="I181" s="6"/>
@@ -7902,14 +7835,14 @@
         <v>46226.0</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E182" s="7"/>
       <c r="F182" s="5" t="s">
-        <v>393</v>
+        <v>289</v>
       </c>
       <c r="G182" s="7"/>
       <c r="H182" s="7"/>
@@ -7925,17 +7858,17 @@
         <v>46226.0</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E183" s="7"/>
       <c r="F183" s="5" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="G183" s="5" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="H183" s="7"/>
       <c r="I183" s="6"/>
@@ -7950,14 +7883,14 @@
         <v>46226.0</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E184" s="7"/>
       <c r="F184" s="5" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="G184" s="7"/>
       <c r="H184" s="7"/>
@@ -7973,14 +7906,14 @@
         <v>46226.0</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E185" s="7"/>
       <c r="F185" s="5" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="G185" s="7"/>
       <c r="H185" s="7"/>
@@ -7996,17 +7929,17 @@
         <v>46227.0</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D186" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E186" s="7"/>
       <c r="F186" s="5" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="G186" s="5" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="H186" s="7"/>
       <c r="I186" s="6"/>
@@ -8021,17 +7954,17 @@
         <v>46227.0</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D187" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E187" s="7"/>
       <c r="F187" s="5" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="G187" s="5" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="H187" s="7"/>
       <c r="I187" s="6"/>
@@ -8046,15 +7979,13 @@
         <v>46227.0</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D188" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E188" s="7"/>
-      <c r="F188" s="5" t="s">
-        <v>222</v>
-      </c>
+      <c r="F188" s="7"/>
       <c r="G188" s="7"/>
       <c r="H188" s="7"/>
       <c r="I188" s="6"/>
@@ -8069,17 +8000,17 @@
         <v>46227.0</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D189" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E189" s="7"/>
       <c r="F189" s="5" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="G189" s="5" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="H189" s="7"/>
       <c r="I189" s="6"/>
@@ -8094,14 +8025,14 @@
         <v>46227.0</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E190" s="7"/>
       <c r="F190" s="5" t="s">
-        <v>341</v>
+        <v>399</v>
       </c>
       <c r="G190" s="7"/>
       <c r="H190" s="7"/>
@@ -8117,17 +8048,17 @@
         <v>46227.0</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E191" s="7"/>
       <c r="F191" s="5" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="G191" s="5" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="H191" s="7"/>
       <c r="I191" s="6"/>
@@ -8142,14 +8073,14 @@
         <v>46227.0</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E192" s="7"/>
       <c r="F192" s="5" t="s">
-        <v>287</v>
+        <v>228</v>
       </c>
       <c r="G192" s="7"/>
       <c r="H192" s="7"/>
@@ -8165,14 +8096,14 @@
         <v>46227.0</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E193" s="7"/>
       <c r="F193" s="5" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G193" s="7"/>
       <c r="H193" s="7"/>
@@ -8188,17 +8119,17 @@
         <v>46228.0</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D194" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E194" s="7"/>
       <c r="F194" s="5" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G194" s="5" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="H194" s="7"/>
       <c r="I194" s="6"/>
@@ -8213,17 +8144,17 @@
         <v>46228.0</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D195" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E195" s="7"/>
       <c r="F195" s="5" t="s">
-        <v>372</v>
+        <v>404</v>
       </c>
       <c r="G195" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H195" s="7"/>
       <c r="I195" s="6"/>
@@ -8238,15 +8169,13 @@
         <v>46228.0</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D196" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E196" s="7"/>
-      <c r="F196" s="5" t="s">
-        <v>226</v>
-      </c>
+      <c r="F196" s="7"/>
       <c r="G196" s="7"/>
       <c r="H196" s="7"/>
       <c r="I196" s="6"/>
@@ -8261,17 +8190,17 @@
         <v>46228.0</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D197" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E197" s="7"/>
       <c r="F197" s="5" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="G197" s="5" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H197" s="7"/>
       <c r="I197" s="6"/>
@@ -8286,14 +8215,14 @@
         <v>46228.0</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E198" s="7"/>
       <c r="F198" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G198" s="7"/>
       <c r="H198" s="7"/>
@@ -8309,17 +8238,17 @@
         <v>46228.0</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E199" s="7"/>
       <c r="F199" s="5" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="G199" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H199" s="7"/>
       <c r="I199" s="6"/>
@@ -8334,14 +8263,14 @@
         <v>46228.0</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E200" s="7"/>
       <c r="F200" s="5" t="s">
-        <v>121</v>
+        <v>163</v>
       </c>
       <c r="G200" s="7"/>
       <c r="H200" s="7"/>
@@ -8357,14 +8286,14 @@
         <v>46228.0</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E201" s="7"/>
       <c r="F201" s="5" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="G201" s="7"/>
       <c r="H201" s="7"/>
@@ -8380,17 +8309,17 @@
         <v>46229.0</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D202" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E202" s="7"/>
       <c r="F202" s="5" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="G202" s="5" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H202" s="7"/>
       <c r="I202" s="6"/>
@@ -8405,17 +8334,17 @@
         <v>46229.0</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D203" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E203" s="7"/>
       <c r="F203" s="5" t="s">
-        <v>341</v>
+        <v>413</v>
       </c>
       <c r="G203" s="5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H203" s="7"/>
       <c r="I203" s="6"/>
@@ -8430,15 +8359,13 @@
         <v>46229.0</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D204" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E204" s="7"/>
-      <c r="F204" s="5" t="s">
-        <v>217</v>
-      </c>
+      <c r="F204" s="7"/>
       <c r="G204" s="7"/>
       <c r="H204" s="7"/>
       <c r="I204" s="6"/>
@@ -8453,17 +8380,17 @@
         <v>46229.0</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D205" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E205" s="7"/>
       <c r="F205" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="G205" s="5" t="s">
         <v>416</v>
-      </c>
-      <c r="G205" s="5" t="s">
-        <v>417</v>
       </c>
       <c r="H205" s="7"/>
       <c r="I205" s="6"/>
@@ -8478,14 +8405,14 @@
         <v>46229.0</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E206" s="7"/>
       <c r="F206" s="5" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="G206" s="7"/>
       <c r="H206" s="7"/>
@@ -8501,17 +8428,17 @@
         <v>46229.0</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E207" s="7"/>
       <c r="F207" s="5" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G207" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H207" s="7"/>
       <c r="I207" s="6"/>
@@ -8526,14 +8453,14 @@
         <v>46229.0</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E208" s="7"/>
       <c r="F208" s="5" t="s">
-        <v>145</v>
+        <v>338</v>
       </c>
       <c r="G208" s="7"/>
       <c r="H208" s="7"/>
@@ -8549,14 +8476,14 @@
         <v>46229.0</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E209" s="7"/>
       <c r="F209" s="5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G209" s="7"/>
       <c r="H209" s="7"/>
@@ -8572,17 +8499,17 @@
         <v>46230.0</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D210" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E210" s="7"/>
       <c r="F210" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="G210" s="5" t="s">
         <v>420</v>
-      </c>
-      <c r="G210" s="5" t="s">
-        <v>421</v>
       </c>
       <c r="H210" s="7"/>
       <c r="I210" s="6"/>
@@ -8597,17 +8524,17 @@
         <v>46230.0</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D211" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E211" s="7"/>
       <c r="F211" s="5" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G211" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H211" s="7"/>
       <c r="I211" s="6"/>
@@ -8622,15 +8549,13 @@
         <v>46230.0</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D212" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E212" s="7"/>
-      <c r="F212" s="5" t="s">
-        <v>287</v>
-      </c>
+      <c r="F212" s="7"/>
       <c r="G212" s="7"/>
       <c r="H212" s="7"/>
       <c r="I212" s="6"/>
@@ -8645,17 +8570,17 @@
         <v>46230.0</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D213" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E213" s="7"/>
       <c r="F213" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="G213" s="5" t="s">
         <v>423</v>
-      </c>
-      <c r="G213" s="5" t="s">
-        <v>424</v>
       </c>
       <c r="H213" s="7"/>
       <c r="I213" s="6"/>
@@ -8670,14 +8595,14 @@
         <v>46230.0</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E214" s="7"/>
       <c r="F214" s="5" t="s">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="G214" s="7"/>
       <c r="H214" s="7"/>
@@ -8693,10 +8618,10 @@
         <v>46230.0</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E215" s="7"/>
       <c r="F215" s="5" t="s">
@@ -8718,14 +8643,14 @@
         <v>46230.0</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E216" s="7"/>
       <c r="F216" s="5" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="G216" s="7"/>
       <c r="H216" s="7"/>
@@ -8741,14 +8666,14 @@
         <v>46230.0</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E217" s="7"/>
       <c r="F217" s="5" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="G217" s="7"/>
       <c r="H217" s="7"/>
@@ -8764,7 +8689,7 @@
         <v>46231.0</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D218" s="5" t="s">
         <v>93</v>
@@ -8789,14 +8714,14 @@
         <v>46231.0</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D219" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E219" s="7"/>
       <c r="F219" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G219" s="5" t="s">
         <v>429</v>
@@ -8814,15 +8739,13 @@
         <v>46231.0</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D220" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E220" s="7"/>
-      <c r="F220" s="5" t="s">
-        <v>217</v>
-      </c>
+      <c r="F220" s="7"/>
       <c r="G220" s="7"/>
       <c r="H220" s="7"/>
       <c r="I220" s="6"/>
@@ -8837,7 +8760,7 @@
         <v>46231.0</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D221" s="5" t="s">
         <v>45</v>
@@ -8862,14 +8785,14 @@
         <v>46231.0</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E222" s="7"/>
       <c r="F222" s="5" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="G222" s="7"/>
       <c r="H222" s="7"/>
@@ -8885,17 +8808,17 @@
         <v>46231.0</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E223" s="7"/>
       <c r="F223" s="5" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G223" s="5" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H223" s="7"/>
       <c r="I223" s="6"/>
@@ -8910,14 +8833,14 @@
         <v>46231.0</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E224" s="7"/>
       <c r="F224" s="5" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G224" s="7"/>
       <c r="H224" s="7"/>
@@ -8933,14 +8856,14 @@
         <v>46231.0</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E225" s="7"/>
       <c r="F225" s="5" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G225" s="7"/>
       <c r="H225" s="7"/>
@@ -8963,10 +8886,10 @@
       </c>
       <c r="E226" s="7"/>
       <c r="F226" s="5" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G226" s="5" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H226" s="7"/>
       <c r="I226" s="6"/>
@@ -8988,10 +8911,10 @@
       </c>
       <c r="E227" s="7"/>
       <c r="F227" s="5" t="s">
-        <v>160</v>
+        <v>270</v>
       </c>
       <c r="G227" s="5" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="H227" s="7"/>
       <c r="I227" s="6"/>
@@ -9012,9 +8935,7 @@
         <v>100</v>
       </c>
       <c r="E228" s="7"/>
-      <c r="F228" s="5" t="s">
-        <v>101</v>
-      </c>
+      <c r="F228" s="7"/>
       <c r="G228" s="7"/>
       <c r="H228" s="7"/>
       <c r="I228" s="6"/>
@@ -9036,10 +8957,10 @@
       </c>
       <c r="E229" s="7"/>
       <c r="F229" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G229" s="5" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H229" s="7"/>
       <c r="I229" s="6"/>
@@ -9057,11 +8978,11 @@
         <v>92</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E230" s="7"/>
       <c r="F230" s="5" t="s">
-        <v>141</v>
+        <v>238</v>
       </c>
       <c r="G230" s="7"/>
       <c r="H230" s="7"/>
@@ -9080,14 +9001,14 @@
         <v>92</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E231" s="7"/>
       <c r="F231" s="5" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G231" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="H231" s="7"/>
       <c r="I231" s="6"/>
@@ -9105,11 +9026,11 @@
         <v>92</v>
       </c>
       <c r="D232" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E232" s="7"/>
       <c r="F232" s="5" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="G232" s="7"/>
       <c r="H232" s="7"/>
@@ -9128,11 +9049,11 @@
         <v>92</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E233" s="7"/>
       <c r="F233" s="5" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G233" s="7"/>
       <c r="H233" s="7"/>
@@ -9148,17 +9069,17 @@
         <v>46233.0</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D234" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E234" s="7"/>
       <c r="F234" s="5" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G234" s="5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H234" s="7"/>
       <c r="I234" s="6"/>
@@ -9173,17 +9094,17 @@
         <v>46233.0</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D235" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E235" s="7"/>
       <c r="F235" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G235" s="5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H235" s="7"/>
       <c r="I235" s="6"/>
@@ -9198,15 +9119,13 @@
         <v>46233.0</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D236" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E236" s="7"/>
-      <c r="F236" s="5" t="s">
-        <v>217</v>
-      </c>
+      <c r="F236" s="7"/>
       <c r="G236" s="7"/>
       <c r="H236" s="7"/>
       <c r="I236" s="6"/>
@@ -9221,17 +9140,17 @@
         <v>46233.0</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D237" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E237" s="7"/>
       <c r="F237" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G237" s="5" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H237" s="7"/>
       <c r="I237" s="6"/>
@@ -9246,14 +9165,14 @@
         <v>46233.0</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D238" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E238" s="7"/>
       <c r="F238" s="5" t="s">
-        <v>347</v>
+        <v>399</v>
       </c>
       <c r="G238" s="7"/>
       <c r="H238" s="7"/>
@@ -9269,17 +9188,17 @@
         <v>46233.0</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E239" s="7"/>
       <c r="F239" s="5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G239" s="5" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H239" s="7"/>
       <c r="I239" s="6"/>
@@ -9294,14 +9213,14 @@
         <v>46233.0</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D240" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E240" s="7"/>
       <c r="F240" s="5" t="s">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="G240" s="7"/>
       <c r="H240" s="7"/>
@@ -9317,14 +9236,14 @@
         <v>46233.0</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E241" s="7"/>
       <c r="F241" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G241" s="7"/>
       <c r="H241" s="7"/>
@@ -9340,17 +9259,17 @@
         <v>46234.0</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D242" s="5" t="s">
         <v>93</v>
       </c>
       <c r="E242" s="7"/>
       <c r="F242" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G242" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H242" s="7"/>
       <c r="I242" s="6"/>
@@ -9365,17 +9284,17 @@
         <v>46234.0</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D243" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E243" s="7"/>
       <c r="F243" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G243" s="5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H243" s="7"/>
       <c r="I243" s="6"/>
@@ -9390,15 +9309,13 @@
         <v>46234.0</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D244" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E244" s="7"/>
-      <c r="F244" s="5" t="s">
-        <v>250</v>
-      </c>
+      <c r="F244" s="7"/>
       <c r="G244" s="7"/>
       <c r="H244" s="7"/>
       <c r="I244" s="6"/>
@@ -9413,17 +9330,17 @@
         <v>46234.0</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D245" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E245" s="7"/>
       <c r="F245" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G245" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H245" s="7"/>
       <c r="I245" s="6"/>
@@ -9438,14 +9355,14 @@
         <v>46234.0</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D246" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E246" s="7"/>
       <c r="F246" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G246" s="7"/>
       <c r="H246" s="7"/>
@@ -9461,17 +9378,17 @@
         <v>46234.0</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E247" s="7"/>
       <c r="F247" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G247" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H247" s="7"/>
       <c r="I247" s="6"/>
@@ -9486,14 +9403,14 @@
         <v>46234.0</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D248" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E248" s="7"/>
       <c r="F248" s="5" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="G248" s="7"/>
       <c r="H248" s="7"/>
@@ -9509,14 +9426,14 @@
         <v>46234.0</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E249" s="7"/>
-      <c r="F249" s="5" t="s">
-        <v>458</v>
+      <c r="F249" s="9" t="s">
+        <v>459</v>
       </c>
       <c r="G249" s="7"/>
       <c r="H249" s="7"/>
@@ -9526,7 +9443,7 @@
     </row>
     <row r="250" ht="14.25" customHeight="1">
       <c r="A250" s="3"/>
-      <c r="B250" s="9"/>
+      <c r="B250" s="10"/>
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
@@ -9539,7 +9456,7 @@
     </row>
     <row r="251" ht="14.25" customHeight="1">
       <c r="A251" s="6"/>
-      <c r="B251" s="10"/>
+      <c r="B251" s="11"/>
       <c r="C251" s="6"/>
       <c r="D251" s="6"/>
       <c r="E251" s="6"/>
@@ -9552,7 +9469,7 @@
     </row>
     <row r="252" ht="14.25" customHeight="1">
       <c r="A252" s="6"/>
-      <c r="B252" s="10"/>
+      <c r="B252" s="11"/>
       <c r="C252" s="6"/>
       <c r="D252" s="6"/>
       <c r="E252" s="6"/>
@@ -9565,7 +9482,7 @@
     </row>
     <row r="253" ht="14.25" customHeight="1">
       <c r="A253" s="6"/>
-      <c r="B253" s="10"/>
+      <c r="B253" s="11"/>
       <c r="C253" s="6"/>
       <c r="D253" s="6"/>
       <c r="E253" s="6"/>
@@ -9600,39 +9517,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B5" s="3">
         <v>2026.0</v>
@@ -9640,7 +9557,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B6" s="3">
         <v>9.63931444898E11</v>
@@ -9648,10 +9565,10 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8">

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="471">
   <si>
     <t>الفرز</t>
   </si>
@@ -46,7 +46,7 @@
 د عبدالرحمن حج طه</t>
   </si>
   <si>
-    <t>علي عبدالرزاق - رنیم ضبیط - روان بطل</t>
+    <t>علي عبدالرزاق - رنیم ضبیط - روان بطل - فاطمة سليمان</t>
   </si>
   <si>
     <t>عائشة عبدالخالق - تسنیم الخال - علا الیوسف</t>
@@ -106,7 +106,7 @@
     <t>د. غنى الصاري</t>
   </si>
   <si>
-    <t>بیان قبسیز - براءة أحمد - نور علاف</t>
+    <t>بیان قبسیز - براءة أحمد - نور علاف - حلا السعيد</t>
   </si>
   <si>
     <t>آیة خلوف - بتول شیاح - رشا عویر</t>
@@ -148,13 +148,13 @@
     <t>رؤى عابدین - زین بركات - سنا طاھر - غرام سلطان - علا بكري - مریم عموري</t>
   </si>
   <si>
-    <t>شامیران بازار - جودي بلال - شھد مخللات</t>
+    <t>راما سيد علي - آية مركن - راما زين الدين - أروى حاج موسى - آية مكانسي - بيان قطنجي</t>
   </si>
   <si>
     <t>الحواضن</t>
   </si>
   <si>
-    <t>أسماء قلعھ جي - رفیدة فرمان - فاضلة شیخ محمد - ریم حمادة - سنا مسلاتي - راما مشلح - رامي سلیمان - أمامة الخلیفة</t>
+    <t>أسماء قلعه جي - رفیدة فرمان - فاضلة شیخ محمد - ریم حمادة - سنا مسلاتي - راما مشلح - رامي سلیمان - أمامة الخلیفة - تسنيم بخصو</t>
   </si>
   <si>
     <t>جود فرواتي - جودي مھندس - سارة زیدان - میسم بطحیش - نور أشرفي - ھمسة مطر - ریم مكیس - رغد محي الدین</t>
@@ -166,7 +166,7 @@
     <t>مشفى التوليد الجامعي</t>
   </si>
   <si>
-    <t>نور قلعھ جي - ھیفا محمد - فاطمة قلعیة - بانة شحرور - محمد حج ابراھیم - روان جنیدي - روان عبس</t>
+    <t>نور قلعه جي - ھیفا محمد - فاطمة قلعیة - بانة شحرور - محمد حج ابراھیم - روان جنیدي - روان عبس - روليان مصطفى - تسنيم فاضل</t>
   </si>
   <si>
     <t>حسن الحسن - خالد رزوق - عدن أقرع - ریم ماضي - راما عتیق - یمنى كیروان - براءة آغا</t>
@@ -208,12 +208,6 @@
     <t>اسلام اسراج - عبالرحمن منصور - یوسف فرحات - أنس غریب - عبدالرحمن نجار - أمل رحال - سنا رشواني</t>
   </si>
   <si>
-    <t>ھاجر صیادي - محمد نبیل صالح
-حسان الأحمد - مھا عیسى
-تسنیم باكیر - آیة حایك
-مجیدة عویجة - حور عنفلی</t>
-  </si>
-  <si>
     <t>القبولات + الاستشارات</t>
   </si>
   <si>
@@ -226,7 +220,7 @@
     <t>عيادات 1</t>
   </si>
   <si>
-    <t>حسین جمعة - شھد الموسى</t>
+    <t>حسین جمعة - شھد الموسى - خديجة بكار</t>
   </si>
   <si>
     <t>دلیفان بطال</t>
@@ -235,7 +229,7 @@
     <t>عيادات 2</t>
   </si>
   <si>
-    <t>سوسن بھلول</t>
+    <t>سوسن بھلول - غفران جزار</t>
   </si>
   <si>
     <t>رغد بازركان - بانة كاتب</t>
@@ -1432,7 +1426,7 @@
     <t>اسم_المطور</t>
   </si>
   <si>
-    <t>علاء العلي </t>
+    <t>علاء العلي 💚</t>
   </si>
 </sst>
 </file>
@@ -1498,14 +1492,14 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2213,9 +2207,7 @@
       <c r="C16" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>64</v>
-      </c>
+      <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -2226,13 +2218,13 @@
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -2245,13 +2237,13 @@
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -2264,13 +2256,13 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -2283,14 +2275,14 @@
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="4"/>
@@ -2302,12 +2294,12 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="4"/>
@@ -2319,13 +2311,13 @@
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -2338,10 +2330,10 @@
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -3378,28 +3370,28 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
@@ -3413,19 +3405,19 @@
         <v>46204.0</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>96</v>
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="6"/>
@@ -3440,17 +3432,17 @@
         <v>46204.0</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>99</v>
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="6"/>
@@ -3465,10 +3457,10 @@
         <v>46204.0</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
@@ -3486,19 +3478,19 @@
         <v>46204.0</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>103</v>
       </c>
       <c r="H5" s="7"/>
       <c r="I5" s="6"/>
@@ -3513,14 +3505,14 @@
         <v>46204.0</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
@@ -3536,19 +3528,19 @@
         <v>46204.0</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>109</v>
       </c>
       <c r="H7" s="7"/>
       <c r="I7" s="6"/>
@@ -3563,14 +3555,14 @@
         <v>46204.0</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
@@ -3586,16 +3578,16 @@
         <v>46204.0</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>114</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
@@ -3611,19 +3603,19 @@
         <v>46205.0</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>118</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="6"/>
@@ -3638,19 +3630,19 @@
         <v>46205.0</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E11" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="G11" s="5" t="s">
         <v>120</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>121</v>
       </c>
       <c r="H11" s="7"/>
       <c r="I11" s="6"/>
@@ -3665,10 +3657,10 @@
         <v>46205.0</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -3686,19 +3678,19 @@
         <v>46205.0</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E13" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>124</v>
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="6"/>
@@ -3713,14 +3705,14 @@
         <v>46205.0</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
@@ -3736,19 +3728,19 @@
         <v>46205.0</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E15" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="6"/>
@@ -3763,14 +3755,14 @@
         <v>46205.0</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -3786,16 +3778,16 @@
         <v>46205.0</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E17" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>130</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>131</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -3811,19 +3803,19 @@
         <v>46206.0</v>
       </c>
       <c r="C18" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E18" s="5" t="s">
+      <c r="F18" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="G18" s="5" t="s">
         <v>134</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>135</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="6"/>
@@ -3838,19 +3830,19 @@
         <v>46206.0</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E19" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>138</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="6"/>
@@ -3865,10 +3857,10 @@
         <v>46206.0</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
@@ -3886,19 +3878,19 @@
         <v>46206.0</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E21" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="G21" s="5" t="s">
         <v>140</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>141</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="6"/>
@@ -3913,14 +3905,14 @@
         <v>46206.0</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E22" s="7"/>
       <c r="F22" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
@@ -3936,19 +3928,19 @@
         <v>46206.0</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E23" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F23" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="G23" s="5" t="s">
         <v>144</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>145</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="6"/>
@@ -3963,14 +3955,14 @@
         <v>46206.0</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
@@ -3986,16 +3978,16 @@
         <v>46206.0</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E25" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>147</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>148</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
@@ -4011,19 +4003,19 @@
         <v>46207.0</v>
       </c>
       <c r="C26" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E26" s="5" t="s">
+      <c r="F26" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="G26" s="5" t="s">
         <v>151</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>152</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="6"/>
@@ -4038,19 +4030,19 @@
         <v>46207.0</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E27" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F27" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="G27" s="5" t="s">
         <v>154</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>155</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="6"/>
@@ -4065,10 +4057,10 @@
         <v>46207.0</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
@@ -4086,19 +4078,19 @@
         <v>46207.0</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E29" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F29" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="G29" s="5" t="s">
         <v>157</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>158</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="6"/>
@@ -4113,14 +4105,14 @@
         <v>46207.0</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
@@ -4136,19 +4128,19 @@
         <v>46207.0</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E31" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="G31" s="5" t="s">
         <v>161</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>162</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="6"/>
@@ -4163,14 +4155,14 @@
         <v>46207.0</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
@@ -4186,16 +4178,16 @@
         <v>46207.0</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E33" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F33" s="5" t="s">
         <v>164</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>165</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
@@ -4211,19 +4203,19 @@
         <v>46208.0</v>
       </c>
       <c r="C34" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E34" s="5" t="s">
+      <c r="F34" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="G34" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>169</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="6"/>
@@ -4238,19 +4230,19 @@
         <v>46208.0</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E35" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F35" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="G35" s="5" t="s">
         <v>171</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>172</v>
       </c>
       <c r="H35" s="7"/>
       <c r="I35" s="6"/>
@@ -4265,10 +4257,10 @@
         <v>46208.0</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
@@ -4286,19 +4278,19 @@
         <v>46208.0</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E37" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="F37" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="G37" s="5" t="s">
         <v>174</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>175</v>
       </c>
       <c r="H37" s="7"/>
       <c r="I37" s="6"/>
@@ -4313,16 +4305,16 @@
         <v>46208.0</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
@@ -4338,19 +4330,19 @@
         <v>46208.0</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E39" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F39" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="G39" s="5" t="s">
         <v>178</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>179</v>
       </c>
       <c r="H39" s="7"/>
       <c r="I39" s="6"/>
@@ -4365,16 +4357,16 @@
         <v>46208.0</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E40" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F40" s="5" t="s">
         <v>180</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>181</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
@@ -4390,16 +4382,16 @@
         <v>46208.0</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E41" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="F41" s="5" t="s">
         <v>182</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>183</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
@@ -4415,19 +4407,19 @@
         <v>46209.0</v>
       </c>
       <c r="C42" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E42" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="D42" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E42" s="5" t="s">
+      <c r="F42" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="G42" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>187</v>
       </c>
       <c r="H42" s="7"/>
       <c r="I42" s="6"/>
@@ -4442,19 +4434,19 @@
         <v>46209.0</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E43" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="F43" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="G43" s="5" t="s">
         <v>189</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>190</v>
       </c>
       <c r="H43" s="7"/>
       <c r="I43" s="6"/>
@@ -4469,13 +4461,13 @@
         <v>46209.0</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
@@ -4492,19 +4484,19 @@
         <v>46209.0</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E45" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F45" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="G45" s="5" t="s">
         <v>193</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>194</v>
       </c>
       <c r="H45" s="7"/>
       <c r="I45" s="6"/>
@@ -4519,16 +4511,16 @@
         <v>46209.0</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E46" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F46" s="5" t="s">
         <v>195</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>196</v>
       </c>
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
@@ -4544,19 +4536,19 @@
         <v>46209.0</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E47" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F47" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="G47" s="5" t="s">
         <v>198</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>199</v>
       </c>
       <c r="H47" s="7"/>
       <c r="I47" s="6"/>
@@ -4571,16 +4563,16 @@
         <v>46209.0</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E48" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F48" s="5" t="s">
         <v>200</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>201</v>
       </c>
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
@@ -4596,16 +4588,16 @@
         <v>46209.0</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E49" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="F49" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>203</v>
       </c>
       <c r="G49" s="7"/>
       <c r="H49" s="7"/>
@@ -4621,19 +4613,19 @@
         <v>46210.0</v>
       </c>
       <c r="C50" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E50" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="D50" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E50" s="5" t="s">
+      <c r="F50" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="F50" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="G50" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H50" s="7"/>
       <c r="I50" s="6"/>
@@ -4648,19 +4640,19 @@
         <v>46210.0</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E51" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F51" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F51" s="5" t="s">
+      <c r="G51" s="5" t="s">
         <v>208</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>209</v>
       </c>
       <c r="H51" s="7"/>
       <c r="I51" s="6"/>
@@ -4675,13 +4667,13 @@
         <v>46210.0</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
@@ -4698,19 +4690,19 @@
         <v>46210.0</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E53" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F53" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="F53" s="5" t="s">
+      <c r="G53" s="5" t="s">
         <v>212</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>213</v>
       </c>
       <c r="H53" s="7"/>
       <c r="I53" s="6"/>
@@ -4725,16 +4717,16 @@
         <v>46210.0</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E54" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F54" s="5" t="s">
         <v>214</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>215</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
@@ -4750,19 +4742,19 @@
         <v>46210.0</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E55" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="F55" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="F55" s="5" t="s">
+      <c r="G55" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="H55" s="7"/>
       <c r="I55" s="6"/>
@@ -4777,16 +4769,16 @@
         <v>46210.0</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E56" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F56" s="5" t="s">
         <v>219</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>220</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
@@ -4802,16 +4794,16 @@
         <v>46210.0</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E57" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="F57" s="5" t="s">
         <v>221</v>
-      </c>
-      <c r="F57" s="5" t="s">
-        <v>222</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
@@ -4827,19 +4819,19 @@
         <v>46211.0</v>
       </c>
       <c r="C58" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D58" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D58" s="5" t="s">
-        <v>93</v>
-      </c>
       <c r="E58" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F58" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="F58" s="5" t="s">
+      <c r="G58" s="5" t="s">
         <v>224</v>
-      </c>
-      <c r="G58" s="5" t="s">
-        <v>225</v>
       </c>
       <c r="H58" s="7"/>
       <c r="I58" s="6"/>
@@ -4854,19 +4846,19 @@
         <v>46211.0</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E59" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F59" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="G59" s="5" t="s">
         <v>227</v>
-      </c>
-      <c r="G59" s="5" t="s">
-        <v>228</v>
       </c>
       <c r="H59" s="7"/>
       <c r="I59" s="6"/>
@@ -4881,13 +4873,13 @@
         <v>46211.0</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="7"/>
@@ -4904,19 +4896,19 @@
         <v>46211.0</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E61" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F61" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="F61" s="5" t="s">
+      <c r="G61" s="5" t="s">
         <v>231</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>232</v>
       </c>
       <c r="H61" s="7"/>
       <c r="I61" s="6"/>
@@ -4931,16 +4923,16 @@
         <v>46211.0</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
@@ -4956,19 +4948,19 @@
         <v>46211.0</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E63" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="F63" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="F63" s="5" t="s">
+      <c r="G63" s="5" t="s">
         <v>235</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>236</v>
       </c>
       <c r="H63" s="7"/>
       <c r="I63" s="6"/>
@@ -4983,16 +4975,16 @@
         <v>46211.0</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E64" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F64" s="5" t="s">
         <v>237</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>238</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
@@ -5008,16 +5000,16 @@
         <v>46211.0</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E65" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F65" s="5" t="s">
         <v>239</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>240</v>
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
@@ -5033,19 +5025,19 @@
         <v>46212.0</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E66" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F66" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="F66" s="5" t="s">
+      <c r="G66" s="5" t="s">
         <v>242</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>243</v>
       </c>
       <c r="H66" s="7"/>
       <c r="I66" s="6"/>
@@ -5060,19 +5052,19 @@
         <v>46212.0</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E67" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="F67" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="F67" s="5" t="s">
+      <c r="G67" s="5" t="s">
         <v>245</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>246</v>
       </c>
       <c r="H67" s="7"/>
       <c r="I67" s="6"/>
@@ -5087,13 +5079,13 @@
         <v>46212.0</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F68" s="7"/>
       <c r="G68" s="7"/>
@@ -5110,19 +5102,19 @@
         <v>46212.0</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E69" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="F69" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="F69" s="5" t="s">
+      <c r="G69" s="5" t="s">
         <v>249</v>
-      </c>
-      <c r="G69" s="5" t="s">
-        <v>250</v>
       </c>
       <c r="H69" s="7"/>
       <c r="I69" s="6"/>
@@ -5137,16 +5129,16 @@
         <v>46212.0</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E70" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="F70" s="5" t="s">
         <v>251</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>252</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
@@ -5162,19 +5154,19 @@
         <v>46212.0</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E71" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="F71" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="F71" s="5" t="s">
+      <c r="G71" s="5" t="s">
         <v>254</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>255</v>
       </c>
       <c r="H71" s="7"/>
       <c r="I71" s="6"/>
@@ -5189,16 +5181,16 @@
         <v>46212.0</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
@@ -5214,16 +5206,16 @@
         <v>46212.0</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E73" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="F73" s="5" t="s">
         <v>257</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>258</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="7"/>
@@ -5239,19 +5231,19 @@
         <v>46213.0</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E74" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F74" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="F74" s="5" t="s">
+      <c r="G74" s="5" t="s">
         <v>260</v>
-      </c>
-      <c r="G74" s="5" t="s">
-        <v>261</v>
       </c>
       <c r="H74" s="7"/>
       <c r="I74" s="6"/>
@@ -5266,19 +5258,19 @@
         <v>46213.0</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E75" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="F75" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="F75" s="5" t="s">
+      <c r="G75" s="5" t="s">
         <v>263</v>
-      </c>
-      <c r="G75" s="5" t="s">
-        <v>264</v>
       </c>
       <c r="H75" s="7"/>
       <c r="I75" s="6"/>
@@ -5293,13 +5285,13 @@
         <v>46213.0</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F76" s="7"/>
       <c r="G76" s="7"/>
@@ -5316,19 +5308,19 @@
         <v>46213.0</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E77" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="F77" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="F77" s="5" t="s">
+      <c r="G77" s="5" t="s">
         <v>267</v>
-      </c>
-      <c r="G77" s="5" t="s">
-        <v>268</v>
       </c>
       <c r="H77" s="7"/>
       <c r="I77" s="6"/>
@@ -5343,16 +5335,16 @@
         <v>46213.0</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E78" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="F78" s="5" t="s">
         <v>269</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>270</v>
       </c>
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
@@ -5368,19 +5360,19 @@
         <v>46213.0</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E79" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="F79" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="F79" s="5" t="s">
+      <c r="G79" s="5" t="s">
         <v>272</v>
-      </c>
-      <c r="G79" s="5" t="s">
-        <v>273</v>
       </c>
       <c r="H79" s="7"/>
       <c r="I79" s="6"/>
@@ -5395,16 +5387,16 @@
         <v>46213.0</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E80" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="F80" s="5" t="s">
         <v>274</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>275</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
@@ -5420,16 +5412,16 @@
         <v>46213.0</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E81" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="F81" s="5" t="s">
         <v>276</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>277</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
@@ -5445,19 +5437,19 @@
         <v>46214.0</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E82" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="F82" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="F82" s="5" t="s">
+      <c r="G82" s="5" t="s">
         <v>279</v>
-      </c>
-      <c r="G82" s="5" t="s">
-        <v>280</v>
       </c>
       <c r="H82" s="7"/>
       <c r="I82" s="6"/>
@@ -5472,19 +5464,19 @@
         <v>46214.0</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E83" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="F83" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="F83" s="5" t="s">
+      <c r="G83" s="5" t="s">
         <v>282</v>
-      </c>
-      <c r="G83" s="5" t="s">
-        <v>283</v>
       </c>
       <c r="H83" s="7"/>
       <c r="I83" s="6"/>
@@ -5499,13 +5491,13 @@
         <v>46214.0</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F84" s="7"/>
       <c r="G84" s="7"/>
@@ -5522,19 +5514,19 @@
         <v>46214.0</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E85" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="F85" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="F85" s="5" t="s">
+      <c r="G85" s="5" t="s">
         <v>286</v>
-      </c>
-      <c r="G85" s="5" t="s">
-        <v>287</v>
       </c>
       <c r="H85" s="7"/>
       <c r="I85" s="6"/>
@@ -5549,16 +5541,16 @@
         <v>46214.0</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E86" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="F86" s="5" t="s">
         <v>288</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>289</v>
       </c>
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
@@ -5574,19 +5566,19 @@
         <v>46214.0</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E87" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="F87" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="F87" s="5" t="s">
+      <c r="G87" s="5" t="s">
         <v>291</v>
-      </c>
-      <c r="G87" s="5" t="s">
-        <v>292</v>
       </c>
       <c r="H87" s="7"/>
       <c r="I87" s="6"/>
@@ -5601,16 +5593,16 @@
         <v>46214.0</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
@@ -5626,16 +5618,16 @@
         <v>46214.0</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E89" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="F89" s="5" t="s">
         <v>294</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>295</v>
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
@@ -5651,17 +5643,17 @@
         <v>46215.0</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E90" s="7"/>
       <c r="F90" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="G90" s="5" t="s">
         <v>296</v>
-      </c>
-      <c r="G90" s="5" t="s">
-        <v>297</v>
       </c>
       <c r="H90" s="7"/>
       <c r="I90" s="6"/>
@@ -5676,17 +5668,17 @@
         <v>46215.0</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E91" s="7"/>
       <c r="F91" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H91" s="7"/>
       <c r="I91" s="6"/>
@@ -5701,10 +5693,10 @@
         <v>46215.0</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E92" s="7"/>
       <c r="F92" s="7"/>
@@ -5722,17 +5714,17 @@
         <v>46215.0</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E93" s="7"/>
       <c r="F93" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="G93" s="5" t="s">
         <v>299</v>
-      </c>
-      <c r="G93" s="5" t="s">
-        <v>300</v>
       </c>
       <c r="H93" s="7"/>
       <c r="I93" s="6"/>
@@ -5747,14 +5739,14 @@
         <v>46215.0</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E94" s="7"/>
       <c r="F94" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G94" s="7"/>
       <c r="H94" s="7"/>
@@ -5770,17 +5762,17 @@
         <v>46215.0</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E95" s="7"/>
       <c r="F95" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H95" s="7"/>
       <c r="I95" s="6"/>
@@ -5795,14 +5787,14 @@
         <v>46215.0</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E96" s="7"/>
       <c r="F96" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
@@ -5818,14 +5810,14 @@
         <v>46215.0</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E97" s="7"/>
       <c r="F97" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
@@ -5841,17 +5833,17 @@
         <v>46216.0</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E98" s="7"/>
       <c r="F98" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="G98" s="5" t="s">
         <v>303</v>
-      </c>
-      <c r="G98" s="5" t="s">
-        <v>304</v>
       </c>
       <c r="H98" s="7"/>
       <c r="I98" s="6"/>
@@ -5866,17 +5858,17 @@
         <v>46216.0</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E99" s="7"/>
       <c r="F99" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="G99" s="5" t="s">
         <v>305</v>
-      </c>
-      <c r="G99" s="5" t="s">
-        <v>306</v>
       </c>
       <c r="H99" s="7"/>
       <c r="I99" s="6"/>
@@ -5891,10 +5883,10 @@
         <v>46216.0</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E100" s="7"/>
       <c r="F100" s="7"/>
@@ -5912,17 +5904,17 @@
         <v>46216.0</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D101" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E101" s="7"/>
       <c r="F101" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="G101" s="5" t="s">
         <v>307</v>
-      </c>
-      <c r="G101" s="5" t="s">
-        <v>308</v>
       </c>
       <c r="H101" s="7"/>
       <c r="I101" s="6"/>
@@ -5937,14 +5929,14 @@
         <v>46216.0</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E102" s="7"/>
       <c r="F102" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G102" s="7"/>
       <c r="H102" s="7"/>
@@ -5960,17 +5952,17 @@
         <v>46216.0</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E103" s="7"/>
       <c r="F103" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H103" s="7"/>
       <c r="I103" s="6"/>
@@ -5985,14 +5977,14 @@
         <v>46216.0</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E104" s="7"/>
       <c r="F104" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G104" s="7"/>
       <c r="H104" s="7"/>
@@ -6008,14 +6000,14 @@
         <v>46216.0</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E105" s="7"/>
       <c r="F105" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
@@ -6031,17 +6023,17 @@
         <v>46217.0</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E106" s="7"/>
       <c r="F106" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="G106" s="5" t="s">
         <v>311</v>
-      </c>
-      <c r="G106" s="5" t="s">
-        <v>312</v>
       </c>
       <c r="H106" s="7"/>
       <c r="I106" s="6"/>
@@ -6056,17 +6048,17 @@
         <v>46217.0</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E107" s="7"/>
       <c r="F107" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H107" s="7"/>
       <c r="I107" s="6"/>
@@ -6081,10 +6073,10 @@
         <v>46217.0</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E108" s="7"/>
       <c r="F108" s="7"/>
@@ -6102,17 +6094,17 @@
         <v>46217.0</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E109" s="7"/>
       <c r="F109" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="G109" s="5" t="s">
         <v>314</v>
-      </c>
-      <c r="G109" s="5" t="s">
-        <v>315</v>
       </c>
       <c r="H109" s="7"/>
       <c r="I109" s="6"/>
@@ -6127,14 +6119,14 @@
         <v>46217.0</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E110" s="7"/>
       <c r="F110" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G110" s="7"/>
       <c r="H110" s="7"/>
@@ -6150,17 +6142,17 @@
         <v>46217.0</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E111" s="7"/>
       <c r="F111" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H111" s="7"/>
       <c r="I111" s="6"/>
@@ -6175,14 +6167,14 @@
         <v>46217.0</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E112" s="7"/>
       <c r="F112" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G112" s="7"/>
       <c r="H112" s="7"/>
@@ -6198,14 +6190,14 @@
         <v>46217.0</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E113" s="7"/>
       <c r="F113" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G113" s="7"/>
       <c r="H113" s="7"/>
@@ -6221,17 +6213,17 @@
         <v>46218.0</v>
       </c>
       <c r="C114" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D114" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>93</v>
       </c>
       <c r="E114" s="7"/>
       <c r="F114" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="G114" s="5" t="s">
         <v>318</v>
-      </c>
-      <c r="G114" s="5" t="s">
-        <v>319</v>
       </c>
       <c r="H114" s="7"/>
       <c r="I114" s="6"/>
@@ -6246,17 +6238,17 @@
         <v>46218.0</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E115" s="7"/>
       <c r="F115" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G115" s="5" t="s">
         <v>320</v>
-      </c>
-      <c r="G115" s="5" t="s">
-        <v>321</v>
       </c>
       <c r="H115" s="7"/>
       <c r="I115" s="6"/>
@@ -6271,10 +6263,10 @@
         <v>46218.0</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E116" s="7"/>
       <c r="F116" s="7"/>
@@ -6292,17 +6284,17 @@
         <v>46218.0</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E117" s="7"/>
       <c r="F117" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="G117" s="5" t="s">
         <v>322</v>
-      </c>
-      <c r="G117" s="5" t="s">
-        <v>323</v>
       </c>
       <c r="H117" s="7"/>
       <c r="I117" s="6"/>
@@ -6317,14 +6309,14 @@
         <v>46218.0</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E118" s="7"/>
       <c r="F118" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G118" s="7"/>
       <c r="H118" s="7"/>
@@ -6340,17 +6332,17 @@
         <v>46218.0</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E119" s="7"/>
       <c r="F119" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="G119" s="5" t="s">
         <v>324</v>
-      </c>
-      <c r="G119" s="5" t="s">
-        <v>325</v>
       </c>
       <c r="H119" s="7"/>
       <c r="I119" s="6"/>
@@ -6365,14 +6357,14 @@
         <v>46218.0</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E120" s="7"/>
       <c r="F120" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G120" s="7"/>
       <c r="H120" s="7"/>
@@ -6388,14 +6380,14 @@
         <v>46218.0</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E121" s="7"/>
       <c r="F121" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G121" s="7"/>
       <c r="H121" s="7"/>
@@ -6411,17 +6403,17 @@
         <v>46219.0</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E122" s="7"/>
       <c r="F122" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="G122" s="5" t="s">
         <v>326</v>
-      </c>
-      <c r="G122" s="5" t="s">
-        <v>327</v>
       </c>
       <c r="H122" s="7"/>
       <c r="I122" s="6"/>
@@ -6436,17 +6428,17 @@
         <v>46219.0</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E123" s="7"/>
       <c r="F123" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H123" s="7"/>
       <c r="I123" s="6"/>
@@ -6461,10 +6453,10 @@
         <v>46219.0</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E124" s="7"/>
       <c r="F124" s="7"/>
@@ -6482,17 +6474,17 @@
         <v>46219.0</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E125" s="7"/>
       <c r="F125" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="G125" s="5" t="s">
         <v>329</v>
-      </c>
-      <c r="G125" s="5" t="s">
-        <v>330</v>
       </c>
       <c r="H125" s="7"/>
       <c r="I125" s="6"/>
@@ -6507,14 +6499,14 @@
         <v>46219.0</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E126" s="7"/>
       <c r="F126" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G126" s="7"/>
       <c r="H126" s="7"/>
@@ -6530,17 +6522,17 @@
         <v>46219.0</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E127" s="7"/>
       <c r="F127" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H127" s="7"/>
       <c r="I127" s="6"/>
@@ -6555,14 +6547,14 @@
         <v>46219.0</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E128" s="7"/>
       <c r="F128" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G128" s="7"/>
       <c r="H128" s="7"/>
@@ -6578,14 +6570,14 @@
         <v>46219.0</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E129" s="7"/>
       <c r="F129" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G129" s="7"/>
       <c r="H129" s="7"/>
@@ -6601,17 +6593,17 @@
         <v>46220.0</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E130" s="7"/>
       <c r="F130" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H130" s="7"/>
       <c r="I130" s="6"/>
@@ -6626,17 +6618,17 @@
         <v>46220.0</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E131" s="7"/>
       <c r="F131" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="G131" s="5" t="s">
         <v>334</v>
-      </c>
-      <c r="G131" s="5" t="s">
-        <v>335</v>
       </c>
       <c r="H131" s="7"/>
       <c r="I131" s="6"/>
@@ -6651,10 +6643,10 @@
         <v>46220.0</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E132" s="7"/>
       <c r="F132" s="7"/>
@@ -6672,17 +6664,17 @@
         <v>46220.0</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E133" s="7"/>
       <c r="F133" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="G133" s="5" t="s">
         <v>336</v>
-      </c>
-      <c r="G133" s="5" t="s">
-        <v>337</v>
       </c>
       <c r="H133" s="7"/>
       <c r="I133" s="6"/>
@@ -6697,14 +6689,14 @@
         <v>46220.0</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E134" s="7"/>
       <c r="F134" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G134" s="7"/>
       <c r="H134" s="7"/>
@@ -6720,17 +6712,17 @@
         <v>46220.0</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E135" s="7"/>
       <c r="F135" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="G135" s="5" t="s">
         <v>339</v>
-      </c>
-      <c r="G135" s="5" t="s">
-        <v>340</v>
       </c>
       <c r="H135" s="7"/>
       <c r="I135" s="6"/>
@@ -6745,14 +6737,14 @@
         <v>46220.0</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E136" s="7"/>
       <c r="F136" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G136" s="7"/>
       <c r="H136" s="7"/>
@@ -6768,14 +6760,14 @@
         <v>46220.0</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E137" s="7"/>
       <c r="F137" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G137" s="7"/>
       <c r="H137" s="7"/>
@@ -6791,17 +6783,17 @@
         <v>46221.0</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E138" s="7"/>
       <c r="F138" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="G138" s="5" t="s">
         <v>342</v>
-      </c>
-      <c r="G138" s="5" t="s">
-        <v>343</v>
       </c>
       <c r="H138" s="7"/>
       <c r="I138" s="6"/>
@@ -6816,17 +6808,17 @@
         <v>46221.0</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E139" s="7"/>
       <c r="F139" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="G139" s="5" t="s">
         <v>344</v>
-      </c>
-      <c r="G139" s="5" t="s">
-        <v>345</v>
       </c>
       <c r="H139" s="7"/>
       <c r="I139" s="6"/>
@@ -6841,10 +6833,10 @@
         <v>46221.0</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E140" s="7"/>
       <c r="F140" s="7"/>
@@ -6862,17 +6854,17 @@
         <v>46221.0</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E141" s="7"/>
       <c r="F141" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="G141" s="5" t="s">
         <v>346</v>
-      </c>
-      <c r="G141" s="5" t="s">
-        <v>347</v>
       </c>
       <c r="H141" s="7"/>
       <c r="I141" s="6"/>
@@ -6887,14 +6879,14 @@
         <v>46221.0</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E142" s="7"/>
       <c r="F142" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G142" s="7"/>
       <c r="H142" s="7"/>
@@ -6910,17 +6902,17 @@
         <v>46221.0</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E143" s="7"/>
       <c r="F143" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="G143" s="5" t="s">
         <v>348</v>
-      </c>
-      <c r="G143" s="5" t="s">
-        <v>349</v>
       </c>
       <c r="H143" s="7"/>
       <c r="I143" s="6"/>
@@ -6935,14 +6927,14 @@
         <v>46221.0</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E144" s="7"/>
       <c r="F144" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G144" s="7"/>
       <c r="H144" s="7"/>
@@ -6958,14 +6950,14 @@
         <v>46221.0</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E145" s="7"/>
       <c r="F145" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G145" s="7"/>
       <c r="H145" s="7"/>
@@ -6981,17 +6973,17 @@
         <v>46222.0</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E146" s="7"/>
       <c r="F146" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H146" s="7"/>
       <c r="I146" s="6"/>
@@ -7006,17 +6998,17 @@
         <v>46222.0</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E147" s="7"/>
       <c r="F147" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H147" s="7"/>
       <c r="I147" s="6"/>
@@ -7031,10 +7023,10 @@
         <v>46222.0</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E148" s="7"/>
       <c r="F148" s="7"/>
@@ -7052,17 +7044,17 @@
         <v>46222.0</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E149" s="7"/>
       <c r="F149" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="G149" s="5" t="s">
         <v>353</v>
-      </c>
-      <c r="G149" s="5" t="s">
-        <v>354</v>
       </c>
       <c r="H149" s="7"/>
       <c r="I149" s="6"/>
@@ -7077,12 +7069,12 @@
         <v>46222.0</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D150" s="7"/>
       <c r="E150" s="7"/>
       <c r="F150" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G150" s="7"/>
       <c r="H150" s="7"/>
@@ -7098,17 +7090,17 @@
         <v>46222.0</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E151" s="7"/>
       <c r="F151" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="G151" s="5" t="s">
         <v>355</v>
-      </c>
-      <c r="G151" s="5" t="s">
-        <v>356</v>
       </c>
       <c r="H151" s="7"/>
       <c r="I151" s="6"/>
@@ -7123,14 +7115,14 @@
         <v>46222.0</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E152" s="7"/>
       <c r="F152" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G152" s="7"/>
       <c r="H152" s="7"/>
@@ -7146,14 +7138,14 @@
         <v>46222.0</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E153" s="7"/>
       <c r="F153" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G153" s="7"/>
       <c r="H153" s="7"/>
@@ -7169,17 +7161,17 @@
         <v>46223.0</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E154" s="7"/>
       <c r="F154" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="G154" s="5" t="s">
         <v>358</v>
-      </c>
-      <c r="G154" s="5" t="s">
-        <v>359</v>
       </c>
       <c r="H154" s="7"/>
       <c r="I154" s="6"/>
@@ -7194,17 +7186,17 @@
         <v>46223.0</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E155" s="7"/>
       <c r="F155" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H155" s="7"/>
       <c r="I155" s="6"/>
@@ -7219,10 +7211,10 @@
         <v>46223.0</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E156" s="7"/>
       <c r="F156" s="7"/>
@@ -7240,17 +7232,17 @@
         <v>46223.0</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D157" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E157" s="7"/>
       <c r="F157" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="G157" s="5" t="s">
         <v>361</v>
-      </c>
-      <c r="G157" s="5" t="s">
-        <v>362</v>
       </c>
       <c r="H157" s="7"/>
       <c r="I157" s="6"/>
@@ -7265,14 +7257,14 @@
         <v>46223.0</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E158" s="7"/>
       <c r="F158" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G158" s="7"/>
       <c r="H158" s="7"/>
@@ -7288,17 +7280,17 @@
         <v>46223.0</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E159" s="7"/>
       <c r="F159" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="G159" s="5" t="s">
         <v>363</v>
-      </c>
-      <c r="G159" s="5" t="s">
-        <v>364</v>
       </c>
       <c r="H159" s="7"/>
       <c r="I159" s="6"/>
@@ -7313,14 +7305,14 @@
         <v>46223.0</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E160" s="7"/>
       <c r="F160" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G160" s="7"/>
       <c r="H160" s="7"/>
@@ -7336,14 +7328,14 @@
         <v>46223.0</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E161" s="7"/>
       <c r="F161" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G161" s="7"/>
       <c r="H161" s="7"/>
@@ -7359,17 +7351,17 @@
         <v>46224.0</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E162" s="7"/>
       <c r="F162" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="G162" s="5" t="s">
         <v>366</v>
-      </c>
-      <c r="G162" s="5" t="s">
-        <v>367</v>
       </c>
       <c r="H162" s="7"/>
       <c r="I162" s="6"/>
@@ -7384,17 +7376,17 @@
         <v>46224.0</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E163" s="7"/>
       <c r="F163" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H163" s="7"/>
       <c r="I163" s="6"/>
@@ -7409,10 +7401,10 @@
         <v>46224.0</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E164" s="7"/>
       <c r="F164" s="7"/>
@@ -7430,17 +7422,17 @@
         <v>46224.0</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D165" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E165" s="7"/>
       <c r="F165" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="G165" s="5" t="s">
         <v>369</v>
-      </c>
-      <c r="G165" s="5" t="s">
-        <v>370</v>
       </c>
       <c r="H165" s="7"/>
       <c r="I165" s="6"/>
@@ -7455,14 +7447,14 @@
         <v>46224.0</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E166" s="7"/>
       <c r="F166" s="5" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G166" s="7"/>
       <c r="H166" s="7"/>
@@ -7478,17 +7470,17 @@
         <v>46224.0</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E167" s="7"/>
       <c r="F167" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="G167" s="5" t="s">
         <v>372</v>
-      </c>
-      <c r="G167" s="5" t="s">
-        <v>373</v>
       </c>
       <c r="H167" s="7"/>
       <c r="I167" s="6"/>
@@ -7503,14 +7495,14 @@
         <v>46224.0</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E168" s="7"/>
       <c r="F168" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G168" s="7"/>
       <c r="H168" s="7"/>
@@ -7526,14 +7518,14 @@
         <v>46224.0</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E169" s="7"/>
       <c r="F169" s="5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G169" s="7"/>
       <c r="H169" s="7"/>
@@ -7549,17 +7541,17 @@
         <v>46225.0</v>
       </c>
       <c r="C170" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D170" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="D170" s="5" t="s">
-        <v>93</v>
       </c>
       <c r="E170" s="7"/>
       <c r="F170" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="G170" s="5" t="s">
         <v>375</v>
-      </c>
-      <c r="G170" s="5" t="s">
-        <v>376</v>
       </c>
       <c r="H170" s="7"/>
       <c r="I170" s="6"/>
@@ -7574,17 +7566,17 @@
         <v>46225.0</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E171" s="7"/>
       <c r="F171" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H171" s="7"/>
       <c r="I171" s="6"/>
@@ -7599,10 +7591,10 @@
         <v>46225.0</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E172" s="7"/>
       <c r="F172" s="7"/>
@@ -7620,17 +7612,17 @@
         <v>46225.0</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D173" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E173" s="7"/>
       <c r="F173" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="G173" s="5" t="s">
         <v>378</v>
-      </c>
-      <c r="G173" s="5" t="s">
-        <v>379</v>
       </c>
       <c r="H173" s="7"/>
       <c r="I173" s="6"/>
@@ -7645,14 +7637,14 @@
         <v>46225.0</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E174" s="7"/>
       <c r="F174" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G174" s="7"/>
       <c r="H174" s="7"/>
@@ -7668,17 +7660,17 @@
         <v>46225.0</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E175" s="7"/>
       <c r="F175" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H175" s="7"/>
       <c r="I175" s="6"/>
@@ -7693,14 +7685,14 @@
         <v>46225.0</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E176" s="7"/>
       <c r="F176" s="5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G176" s="7"/>
       <c r="H176" s="7"/>
@@ -7716,14 +7708,14 @@
         <v>46225.0</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E177" s="7"/>
       <c r="F177" s="5" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G177" s="7"/>
       <c r="H177" s="7"/>
@@ -7739,17 +7731,17 @@
         <v>46226.0</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E178" s="7"/>
       <c r="F178" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="G178" s="5" t="s">
         <v>384</v>
-      </c>
-      <c r="G178" s="5" t="s">
-        <v>385</v>
       </c>
       <c r="H178" s="7"/>
       <c r="I178" s="6"/>
@@ -7764,17 +7756,17 @@
         <v>46226.0</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E179" s="7"/>
       <c r="F179" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="G179" s="5" t="s">
         <v>386</v>
-      </c>
-      <c r="G179" s="5" t="s">
-        <v>387</v>
       </c>
       <c r="H179" s="7"/>
       <c r="I179" s="6"/>
@@ -7789,10 +7781,10 @@
         <v>46226.0</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E180" s="7"/>
       <c r="F180" s="7"/>
@@ -7810,17 +7802,17 @@
         <v>46226.0</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D181" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E181" s="7"/>
       <c r="F181" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="G181" s="5" t="s">
         <v>388</v>
-      </c>
-      <c r="G181" s="5" t="s">
-        <v>389</v>
       </c>
       <c r="H181" s="7"/>
       <c r="I181" s="6"/>
@@ -7835,14 +7827,14 @@
         <v>46226.0</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E182" s="7"/>
       <c r="F182" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G182" s="7"/>
       <c r="H182" s="7"/>
@@ -7858,17 +7850,17 @@
         <v>46226.0</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E183" s="7"/>
       <c r="F183" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="G183" s="5" t="s">
         <v>390</v>
-      </c>
-      <c r="G183" s="5" t="s">
-        <v>391</v>
       </c>
       <c r="H183" s="7"/>
       <c r="I183" s="6"/>
@@ -7883,14 +7875,14 @@
         <v>46226.0</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E184" s="7"/>
       <c r="F184" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G184" s="7"/>
       <c r="H184" s="7"/>
@@ -7906,14 +7898,14 @@
         <v>46226.0</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E185" s="7"/>
       <c r="F185" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G185" s="7"/>
       <c r="H185" s="7"/>
@@ -7929,17 +7921,17 @@
         <v>46227.0</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E186" s="7"/>
       <c r="F186" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="G186" s="5" t="s">
         <v>393</v>
-      </c>
-      <c r="G186" s="5" t="s">
-        <v>394</v>
       </c>
       <c r="H186" s="7"/>
       <c r="I186" s="6"/>
@@ -7954,17 +7946,17 @@
         <v>46227.0</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E187" s="7"/>
       <c r="F187" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="G187" s="5" t="s">
         <v>395</v>
-      </c>
-      <c r="G187" s="5" t="s">
-        <v>396</v>
       </c>
       <c r="H187" s="7"/>
       <c r="I187" s="6"/>
@@ -7979,10 +7971,10 @@
         <v>46227.0</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E188" s="7"/>
       <c r="F188" s="7"/>
@@ -8000,17 +7992,17 @@
         <v>46227.0</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D189" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E189" s="7"/>
       <c r="F189" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="G189" s="5" t="s">
         <v>397</v>
-      </c>
-      <c r="G189" s="5" t="s">
-        <v>398</v>
       </c>
       <c r="H189" s="7"/>
       <c r="I189" s="6"/>
@@ -8025,14 +8017,14 @@
         <v>46227.0</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E190" s="7"/>
       <c r="F190" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G190" s="7"/>
       <c r="H190" s="7"/>
@@ -8048,17 +8040,17 @@
         <v>46227.0</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E191" s="7"/>
       <c r="F191" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="G191" s="5" t="s">
         <v>400</v>
-      </c>
-      <c r="G191" s="5" t="s">
-        <v>401</v>
       </c>
       <c r="H191" s="7"/>
       <c r="I191" s="6"/>
@@ -8073,14 +8065,14 @@
         <v>46227.0</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E192" s="7"/>
       <c r="F192" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G192" s="7"/>
       <c r="H192" s="7"/>
@@ -8096,14 +8088,14 @@
         <v>46227.0</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E193" s="7"/>
       <c r="F193" s="5" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G193" s="7"/>
       <c r="H193" s="7"/>
@@ -8119,17 +8111,17 @@
         <v>46228.0</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E194" s="7"/>
       <c r="F194" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G194" s="5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H194" s="7"/>
       <c r="I194" s="6"/>
@@ -8144,17 +8136,17 @@
         <v>46228.0</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E195" s="7"/>
       <c r="F195" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="G195" s="5" t="s">
         <v>404</v>
-      </c>
-      <c r="G195" s="5" t="s">
-        <v>405</v>
       </c>
       <c r="H195" s="7"/>
       <c r="I195" s="6"/>
@@ -8169,10 +8161,10 @@
         <v>46228.0</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E196" s="7"/>
       <c r="F196" s="7"/>
@@ -8190,17 +8182,17 @@
         <v>46228.0</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D197" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E197" s="7"/>
       <c r="F197" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="G197" s="5" t="s">
         <v>406</v>
-      </c>
-      <c r="G197" s="5" t="s">
-        <v>407</v>
       </c>
       <c r="H197" s="7"/>
       <c r="I197" s="6"/>
@@ -8215,14 +8207,14 @@
         <v>46228.0</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E198" s="7"/>
       <c r="F198" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G198" s="7"/>
       <c r="H198" s="7"/>
@@ -8238,17 +8230,17 @@
         <v>46228.0</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E199" s="7"/>
       <c r="F199" s="5" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G199" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H199" s="7"/>
       <c r="I199" s="6"/>
@@ -8263,14 +8255,14 @@
         <v>46228.0</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E200" s="7"/>
       <c r="F200" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G200" s="7"/>
       <c r="H200" s="7"/>
@@ -8286,14 +8278,14 @@
         <v>46228.0</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E201" s="7"/>
       <c r="F201" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G201" s="7"/>
       <c r="H201" s="7"/>
@@ -8309,17 +8301,17 @@
         <v>46229.0</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E202" s="7"/>
       <c r="F202" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="G202" s="5" t="s">
         <v>411</v>
-      </c>
-      <c r="G202" s="5" t="s">
-        <v>412</v>
       </c>
       <c r="H202" s="7"/>
       <c r="I202" s="6"/>
@@ -8334,17 +8326,17 @@
         <v>46229.0</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E203" s="7"/>
       <c r="F203" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="G203" s="5" t="s">
         <v>413</v>
-      </c>
-      <c r="G203" s="5" t="s">
-        <v>414</v>
       </c>
       <c r="H203" s="7"/>
       <c r="I203" s="6"/>
@@ -8359,10 +8351,10 @@
         <v>46229.0</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E204" s="7"/>
       <c r="F204" s="7"/>
@@ -8380,17 +8372,17 @@
         <v>46229.0</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D205" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E205" s="7"/>
       <c r="F205" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="G205" s="5" t="s">
         <v>415</v>
-      </c>
-      <c r="G205" s="5" t="s">
-        <v>416</v>
       </c>
       <c r="H205" s="7"/>
       <c r="I205" s="6"/>
@@ -8405,14 +8397,14 @@
         <v>46229.0</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E206" s="7"/>
       <c r="F206" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G206" s="7"/>
       <c r="H206" s="7"/>
@@ -8428,17 +8420,17 @@
         <v>46229.0</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E207" s="7"/>
       <c r="F207" s="5" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G207" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H207" s="7"/>
       <c r="I207" s="6"/>
@@ -8453,14 +8445,14 @@
         <v>46229.0</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E208" s="7"/>
       <c r="F208" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G208" s="7"/>
       <c r="H208" s="7"/>
@@ -8476,14 +8468,14 @@
         <v>46229.0</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E209" s="7"/>
       <c r="F209" s="5" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G209" s="7"/>
       <c r="H209" s="7"/>
@@ -8499,17 +8491,17 @@
         <v>46230.0</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E210" s="7"/>
       <c r="F210" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="G210" s="5" t="s">
         <v>419</v>
-      </c>
-      <c r="G210" s="5" t="s">
-        <v>420</v>
       </c>
       <c r="H210" s="7"/>
       <c r="I210" s="6"/>
@@ -8524,17 +8516,17 @@
         <v>46230.0</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E211" s="7"/>
       <c r="F211" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G211" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H211" s="7"/>
       <c r="I211" s="6"/>
@@ -8549,10 +8541,10 @@
         <v>46230.0</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D212" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E212" s="7"/>
       <c r="F212" s="7"/>
@@ -8570,17 +8562,17 @@
         <v>46230.0</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D213" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E213" s="7"/>
       <c r="F213" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="G213" s="5" t="s">
         <v>422</v>
-      </c>
-      <c r="G213" s="5" t="s">
-        <v>423</v>
       </c>
       <c r="H213" s="7"/>
       <c r="I213" s="6"/>
@@ -8595,14 +8587,14 @@
         <v>46230.0</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E214" s="7"/>
       <c r="F214" s="5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G214" s="7"/>
       <c r="H214" s="7"/>
@@ -8618,17 +8610,17 @@
         <v>46230.0</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E215" s="7"/>
       <c r="F215" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="G215" s="5" t="s">
         <v>425</v>
-      </c>
-      <c r="G215" s="5" t="s">
-        <v>426</v>
       </c>
       <c r="H215" s="7"/>
       <c r="I215" s="6"/>
@@ -8643,14 +8635,14 @@
         <v>46230.0</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E216" s="7"/>
       <c r="F216" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G216" s="7"/>
       <c r="H216" s="7"/>
@@ -8666,14 +8658,14 @@
         <v>46230.0</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E217" s="7"/>
       <c r="F217" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G217" s="7"/>
       <c r="H217" s="7"/>
@@ -8689,17 +8681,17 @@
         <v>46231.0</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E218" s="7"/>
       <c r="F218" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="G218" s="5" t="s">
         <v>427</v>
-      </c>
-      <c r="G218" s="5" t="s">
-        <v>428</v>
       </c>
       <c r="H218" s="7"/>
       <c r="I218" s="6"/>
@@ -8714,17 +8706,17 @@
         <v>46231.0</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E219" s="7"/>
       <c r="F219" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G219" s="5" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H219" s="7"/>
       <c r="I219" s="6"/>
@@ -8739,10 +8731,10 @@
         <v>46231.0</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E220" s="7"/>
       <c r="F220" s="7"/>
@@ -8760,17 +8752,17 @@
         <v>46231.0</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D221" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E221" s="7"/>
       <c r="F221" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="G221" s="5" t="s">
         <v>430</v>
-      </c>
-      <c r="G221" s="5" t="s">
-        <v>431</v>
       </c>
       <c r="H221" s="7"/>
       <c r="I221" s="6"/>
@@ -8785,14 +8777,14 @@
         <v>46231.0</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E222" s="7"/>
       <c r="F222" s="5" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G222" s="7"/>
       <c r="H222" s="7"/>
@@ -8808,17 +8800,17 @@
         <v>46231.0</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E223" s="7"/>
       <c r="F223" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="G223" s="5" t="s">
         <v>433</v>
-      </c>
-      <c r="G223" s="5" t="s">
-        <v>434</v>
       </c>
       <c r="H223" s="7"/>
       <c r="I223" s="6"/>
@@ -8833,14 +8825,14 @@
         <v>46231.0</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E224" s="7"/>
       <c r="F224" s="5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G224" s="7"/>
       <c r="H224" s="7"/>
@@ -8856,14 +8848,14 @@
         <v>46231.0</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E225" s="7"/>
       <c r="F225" s="5" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G225" s="7"/>
       <c r="H225" s="7"/>
@@ -8879,17 +8871,17 @@
         <v>46232.0</v>
       </c>
       <c r="C226" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D226" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="D226" s="5" t="s">
-        <v>93</v>
       </c>
       <c r="E226" s="7"/>
       <c r="F226" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="G226" s="5" t="s">
         <v>437</v>
-      </c>
-      <c r="G226" s="5" t="s">
-        <v>438</v>
       </c>
       <c r="H226" s="7"/>
       <c r="I226" s="6"/>
@@ -8904,17 +8896,17 @@
         <v>46232.0</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E227" s="7"/>
       <c r="F227" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G227" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H227" s="7"/>
       <c r="I227" s="6"/>
@@ -8929,10 +8921,10 @@
         <v>46232.0</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E228" s="7"/>
       <c r="F228" s="7"/>
@@ -8950,17 +8942,17 @@
         <v>46232.0</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D229" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E229" s="7"/>
       <c r="F229" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="G229" s="5" t="s">
         <v>439</v>
-      </c>
-      <c r="G229" s="5" t="s">
-        <v>440</v>
       </c>
       <c r="H229" s="7"/>
       <c r="I229" s="6"/>
@@ -8975,14 +8967,14 @@
         <v>46232.0</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E230" s="7"/>
       <c r="F230" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G230" s="7"/>
       <c r="H230" s="7"/>
@@ -8998,17 +8990,17 @@
         <v>46232.0</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E231" s="7"/>
       <c r="F231" s="5" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G231" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H231" s="7"/>
       <c r="I231" s="6"/>
@@ -9023,14 +9015,14 @@
         <v>46232.0</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D232" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E232" s="7"/>
       <c r="F232" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G232" s="7"/>
       <c r="H232" s="7"/>
@@ -9046,14 +9038,14 @@
         <v>46232.0</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E233" s="7"/>
       <c r="F233" s="5" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G233" s="7"/>
       <c r="H233" s="7"/>
@@ -9069,17 +9061,17 @@
         <v>46233.0</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D234" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E234" s="7"/>
       <c r="F234" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="G234" s="5" t="s">
         <v>442</v>
-      </c>
-      <c r="G234" s="5" t="s">
-        <v>443</v>
       </c>
       <c r="H234" s="7"/>
       <c r="I234" s="6"/>
@@ -9094,17 +9086,17 @@
         <v>46233.0</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E235" s="7"/>
       <c r="F235" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G235" s="5" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H235" s="7"/>
       <c r="I235" s="6"/>
@@ -9119,10 +9111,10 @@
         <v>46233.0</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D236" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E236" s="7"/>
       <c r="F236" s="7"/>
@@ -9140,17 +9132,17 @@
         <v>46233.0</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D237" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E237" s="7"/>
       <c r="F237" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="G237" s="5" t="s">
         <v>445</v>
-      </c>
-      <c r="G237" s="5" t="s">
-        <v>446</v>
       </c>
       <c r="H237" s="7"/>
       <c r="I237" s="6"/>
@@ -9165,14 +9157,14 @@
         <v>46233.0</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D238" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E238" s="7"/>
       <c r="F238" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G238" s="7"/>
       <c r="H238" s="7"/>
@@ -9188,17 +9180,17 @@
         <v>46233.0</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E239" s="7"/>
       <c r="F239" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="G239" s="5" t="s">
         <v>447</v>
-      </c>
-      <c r="G239" s="5" t="s">
-        <v>448</v>
       </c>
       <c r="H239" s="7"/>
       <c r="I239" s="6"/>
@@ -9213,14 +9205,14 @@
         <v>46233.0</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D240" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E240" s="7"/>
       <c r="F240" s="5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G240" s="7"/>
       <c r="H240" s="7"/>
@@ -9236,14 +9228,14 @@
         <v>46233.0</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E241" s="7"/>
       <c r="F241" s="5" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G241" s="7"/>
       <c r="H241" s="7"/>
@@ -9259,17 +9251,17 @@
         <v>46234.0</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D242" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E242" s="7"/>
       <c r="F242" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="G242" s="5" t="s">
         <v>450</v>
-      </c>
-      <c r="G242" s="5" t="s">
-        <v>451</v>
       </c>
       <c r="H242" s="7"/>
       <c r="I242" s="6"/>
@@ -9284,17 +9276,17 @@
         <v>46234.0</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E243" s="7"/>
       <c r="F243" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="G243" s="5" t="s">
         <v>452</v>
-      </c>
-      <c r="G243" s="5" t="s">
-        <v>453</v>
       </c>
       <c r="H243" s="7"/>
       <c r="I243" s="6"/>
@@ -9309,10 +9301,10 @@
         <v>46234.0</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D244" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E244" s="7"/>
       <c r="F244" s="7"/>
@@ -9330,17 +9322,17 @@
         <v>46234.0</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D245" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E245" s="7"/>
       <c r="F245" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="G245" s="5" t="s">
         <v>454</v>
-      </c>
-      <c r="G245" s="5" t="s">
-        <v>455</v>
       </c>
       <c r="H245" s="7"/>
       <c r="I245" s="6"/>
@@ -9355,14 +9347,14 @@
         <v>46234.0</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D246" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E246" s="7"/>
       <c r="F246" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G246" s="7"/>
       <c r="H246" s="7"/>
@@ -9378,17 +9370,17 @@
         <v>46234.0</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E247" s="7"/>
       <c r="F247" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="G247" s="5" t="s">
         <v>457</v>
-      </c>
-      <c r="G247" s="5" t="s">
-        <v>458</v>
       </c>
       <c r="H247" s="7"/>
       <c r="I247" s="6"/>
@@ -9403,14 +9395,14 @@
         <v>46234.0</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D248" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E248" s="7"/>
       <c r="F248" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G248" s="7"/>
       <c r="H248" s="7"/>
@@ -9426,14 +9418,14 @@
         <v>46234.0</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E249" s="7"/>
-      <c r="F249" s="9" t="s">
-        <v>459</v>
+      <c r="F249" s="5" t="s">
+        <v>458</v>
       </c>
       <c r="G249" s="7"/>
       <c r="H249" s="7"/>
@@ -9443,7 +9435,7 @@
     </row>
     <row r="250" ht="14.25" customHeight="1">
       <c r="A250" s="3"/>
-      <c r="B250" s="10"/>
+      <c r="B250" s="9"/>
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
@@ -9456,7 +9448,7 @@
     </row>
     <row r="251" ht="14.25" customHeight="1">
       <c r="A251" s="6"/>
-      <c r="B251" s="11"/>
+      <c r="B251" s="10"/>
       <c r="C251" s="6"/>
       <c r="D251" s="6"/>
       <c r="E251" s="6"/>
@@ -9469,7 +9461,7 @@
     </row>
     <row r="252" ht="14.25" customHeight="1">
       <c r="A252" s="6"/>
-      <c r="B252" s="11"/>
+      <c r="B252" s="10"/>
       <c r="C252" s="6"/>
       <c r="D252" s="6"/>
       <c r="E252" s="6"/>
@@ -9482,7 +9474,7 @@
     </row>
     <row r="253" ht="14.25" customHeight="1">
       <c r="A253" s="6"/>
-      <c r="B253" s="11"/>
+      <c r="B253" s="10"/>
       <c r="C253" s="6"/>
       <c r="D253" s="6"/>
       <c r="E253" s="6"/>
@@ -9517,39 +9509,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>462</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B5" s="3">
         <v>2026.0</v>
@@ -9557,7 +9549,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B6" s="3">
         <v>9.63931444898E11</v>
@@ -9565,10 +9557,10 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>470</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="8">

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="509">
   <si>
     <t>الفرز</t>
   </si>
@@ -901,112 +901,226 @@
     <t>رشواني - بازركان - رؤى - علا اليوسف</t>
   </si>
   <si>
+    <t>مها عيسى - اسراء جاويش - نور كجيل - كريمش</t>
+  </si>
+  <si>
     <t>مريم - تسنيم - بتول</t>
   </si>
   <si>
     <t>سدرة - زين الدين</t>
   </si>
   <si>
+    <t>نور علاف - لانا صباغ</t>
+  </si>
+  <si>
     <t>حريري</t>
   </si>
   <si>
+    <t>علاء</t>
+  </si>
+  <si>
+    <t>رامي - راما مشلح - تسنيم بخصو - روان جنيدي - فاطمة قلعية - غفران</t>
+  </si>
+  <si>
     <t>علا خلوف - هيا - همسة - أشرفي - قمر</t>
   </si>
   <si>
     <t>ديمة - شيماء - إيلاف</t>
   </si>
   <si>
+    <t>نور قلعة جي</t>
+  </si>
+  <si>
+    <t>زيلان - جودي بلال - جودي بوشي - فاطمة سليمان</t>
+  </si>
+  <si>
     <t>جودي - روشان</t>
   </si>
   <si>
+    <t>بيان بيطار</t>
+  </si>
+  <si>
+    <t>حسان - تسنيم باكير - زهيدة - براءة - شهد دباغ</t>
+  </si>
+  <si>
     <t>ليندا - براءة - يمنى - سالي</t>
   </si>
   <si>
+    <t>حلا سعيد - تسنيم فاضل - مجيدة عويجة - فدى قصاص</t>
+  </si>
+  <si>
     <t>شهد - زين - طاهر</t>
   </si>
   <si>
     <t>ساكت - فاتن</t>
   </si>
   <si>
+    <t xml:space="preserve">لارا النعسان - بتول شكوا </t>
+  </si>
+  <si>
     <t>مهندس</t>
   </si>
   <si>
     <t>دندل</t>
   </si>
   <si>
+    <t>سنا مسلاتي - أمامة - رفيدة - سلام - روان بطل - روليان</t>
+  </si>
+  <si>
     <t>عبدالله - كردية - كجان - نجار - مكيس</t>
   </si>
   <si>
     <t>كبب - سلمان - قاسم</t>
   </si>
   <si>
+    <t>سنا ديب</t>
+  </si>
+  <si>
+    <t>تسنيم ترك - رؤى النبشة - ميسم طاحوش - رند كيالي</t>
+  </si>
+  <si>
     <t>سلام عرب - نتالي - آية خلوف</t>
   </si>
   <si>
+    <t>ماريا</t>
+  </si>
+  <si>
+    <t>وتين كسارة - رغد الأفندي - محمد حج ابراهيم - سارة عرابي - سارة سعيد</t>
+  </si>
+  <si>
     <t>عدن - راما - ريم ماضي - عائشة</t>
   </si>
   <si>
+    <t>علي - هديل قناعة - آية حايك - حور</t>
+  </si>
+  <si>
     <t>بازركان - رؤى - علا بكري</t>
   </si>
   <si>
     <t>علا - تمو</t>
   </si>
   <si>
+    <t>بيان قبسيز - آية فتال</t>
+  </si>
+  <si>
     <t>غزال</t>
   </si>
   <si>
+    <t xml:space="preserve">جودي بوشي </t>
+  </si>
+  <si>
+    <t>أسماء قلعة جي - ريم حمادة - فاضلة - روان عبس - شهد مخللاتي - راما أبري</t>
+  </si>
+  <si>
     <t>فرواتي - محي الدين - سالي - رشا - أنس</t>
   </si>
   <si>
     <t>منار - إسماعيل - حمادية</t>
   </si>
   <si>
+    <t>أمنية عدلة</t>
+  </si>
+  <si>
+    <t>شاميران - بتول هنداوي - روضة - سهام وعري</t>
+  </si>
+  <si>
     <t>ليندا - لانا - جميلي</t>
   </si>
   <si>
+    <t>ندوى</t>
+  </si>
+  <si>
+    <t>محمد الصالح - حسين - بانة شحرور - محمد نور - مصطفى</t>
+  </si>
+  <si>
     <t>حسن - خالد - قمر - ايمان</t>
   </si>
   <si>
+    <t>نور قلعة جي - سمر سرماني - لانا صباغ - هاجر</t>
+  </si>
+  <si>
     <t>مريم - تسنيم - هيا</t>
   </si>
   <si>
     <t>رفاعي - سفانة</t>
   </si>
   <si>
+    <t xml:space="preserve">هيفا محمد - خديجة بكار </t>
+  </si>
+  <si>
     <t>علا خلوف</t>
   </si>
   <si>
     <t>روان</t>
   </si>
   <si>
+    <t xml:space="preserve">راما مشلح - رامي - تسنيم بخصو - حسان - مها عيسى - سنا ديب </t>
+  </si>
+  <si>
     <t>سارة - ميسم - همسة - يمنى - براءة</t>
   </si>
   <si>
     <t>لين - كوثر - فرح</t>
   </si>
   <si>
+    <t xml:space="preserve">جودي بلال </t>
+  </si>
+  <si>
+    <t>زهيدة - اسراء جاويش - نور علاف - رؤى عطار</t>
+  </si>
+  <si>
     <t>نجار - رشواني - غرام</t>
   </si>
   <si>
     <t>بركات - روابي</t>
   </si>
   <si>
+    <t>روان جندي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رنيم ضبيط - شهد حمدان - بلال - أحمد - شهد دباغ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">رند كيالي - علاء - سارة عرابي - محمد حج ابراهيم </t>
+  </si>
+  <si>
     <t>ريم ماضي - راما - أمل</t>
   </si>
   <si>
     <t>أريج - عبدالو</t>
   </si>
   <si>
+    <t xml:space="preserve">تسنيم باكير - وتين كسارة </t>
+  </si>
+  <si>
     <t>إنجي</t>
   </si>
   <si>
+    <t xml:space="preserve">رؤى النبشة </t>
+  </si>
+  <si>
+    <t xml:space="preserve">أمامة - ريم حمادة - سنا مسلاتي - سوسن - لارا النعسان - تسنيم ترك </t>
+  </si>
+  <si>
     <t>فرواتي - مهندس - أشرفي - بتول - آية خلوف</t>
   </si>
   <si>
     <t>سيد علي - دياب - كابرييل</t>
   </si>
   <si>
+    <t>براءة</t>
+  </si>
+  <si>
+    <t>حلا سعيد - خالد - مجيدة عويجة - محمد نور</t>
+  </si>
+  <si>
     <t>أماني - أحمد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سارة سعيد </t>
+  </si>
+  <si>
+    <t xml:space="preserve">رفيدة - فاطمة قلعة جي - سلام - فاطمة سليمان - روان بطل </t>
   </si>
   <si>
     <t>عبدالله - كردية - كجان - أنس</t>
@@ -1492,14 +1606,14 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5648,12 +5762,14 @@
       <c r="D90" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E90" s="7"/>
+      <c r="E90" s="9" t="s">
+        <v>295</v>
+      </c>
       <c r="F90" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H90" s="7"/>
       <c r="I90" s="6"/>
@@ -5673,12 +5789,14 @@
       <c r="D91" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E91" s="7"/>
+      <c r="E91" s="9" t="s">
+        <v>298</v>
+      </c>
       <c r="F91" s="5" t="s">
         <v>251</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H91" s="7"/>
       <c r="I91" s="6"/>
@@ -5698,7 +5816,9 @@
       <c r="D92" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E92" s="7"/>
+      <c r="E92" s="9" t="s">
+        <v>300</v>
+      </c>
       <c r="F92" s="7"/>
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
@@ -5719,12 +5839,14 @@
       <c r="D93" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E93" s="7"/>
+      <c r="E93" s="9" t="s">
+        <v>301</v>
+      </c>
       <c r="F93" s="5" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="H93" s="7"/>
       <c r="I93" s="6"/>
@@ -5744,7 +5866,9 @@
       <c r="D94" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E94" s="7"/>
+      <c r="E94" s="9" t="s">
+        <v>304</v>
+      </c>
       <c r="F94" s="5" t="s">
         <v>274</v>
       </c>
@@ -5767,12 +5891,14 @@
       <c r="D95" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E95" s="7"/>
+      <c r="E95" s="9" t="s">
+        <v>305</v>
+      </c>
       <c r="F95" s="5" t="s">
         <v>241</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="H95" s="7"/>
       <c r="I95" s="6"/>
@@ -5792,7 +5918,9 @@
       <c r="D96" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E96" s="7"/>
+      <c r="E96" s="9" t="s">
+        <v>307</v>
+      </c>
       <c r="F96" s="5" t="s">
         <v>145</v>
       </c>
@@ -5815,9 +5943,11 @@
       <c r="D97" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E97" s="7"/>
+      <c r="E97" s="9" t="s">
+        <v>308</v>
+      </c>
       <c r="F97" s="5" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
@@ -5838,12 +5968,14 @@
       <c r="D98" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E98" s="7"/>
+      <c r="E98" s="9" t="s">
+        <v>310</v>
+      </c>
       <c r="F98" s="5" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="H98" s="7"/>
       <c r="I98" s="6"/>
@@ -5863,12 +5995,14 @@
       <c r="D99" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E99" s="7"/>
+      <c r="E99" s="9" t="s">
+        <v>313</v>
+      </c>
       <c r="F99" s="5" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="H99" s="7"/>
       <c r="I99" s="6"/>
@@ -5888,7 +6022,9 @@
       <c r="D100" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E100" s="7"/>
+      <c r="E100" s="9" t="s">
+        <v>244</v>
+      </c>
       <c r="F100" s="7"/>
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
@@ -5909,12 +6045,14 @@
       <c r="D101" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E101" s="7"/>
+      <c r="E101" s="9" t="s">
+        <v>316</v>
+      </c>
       <c r="F101" s="5" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="H101" s="7"/>
       <c r="I101" s="6"/>
@@ -5934,7 +6072,9 @@
       <c r="D102" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E102" s="7"/>
+      <c r="E102" s="9" t="s">
+        <v>319</v>
+      </c>
       <c r="F102" s="5" t="s">
         <v>124</v>
       </c>
@@ -5957,9 +6097,11 @@
       <c r="D103" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E103" s="7"/>
+      <c r="E103" s="9" t="s">
+        <v>320</v>
+      </c>
       <c r="F103" s="5" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="G103" s="5" t="s">
         <v>161</v>
@@ -5982,7 +6124,9 @@
       <c r="D104" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E104" s="7"/>
+      <c r="E104" s="9" t="s">
+        <v>322</v>
+      </c>
       <c r="F104" s="5" t="s">
         <v>214</v>
       </c>
@@ -6005,9 +6149,11 @@
       <c r="D105" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E105" s="7"/>
+      <c r="E105" s="9" t="s">
+        <v>323</v>
+      </c>
       <c r="F105" s="5" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
@@ -6028,12 +6174,14 @@
       <c r="D106" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E106" s="7"/>
+      <c r="E106" s="9" t="s">
+        <v>325</v>
+      </c>
       <c r="F106" s="5" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="H106" s="7"/>
       <c r="I106" s="6"/>
@@ -6053,12 +6201,14 @@
       <c r="D107" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E107" s="7"/>
+      <c r="E107" s="9" t="s">
+        <v>328</v>
+      </c>
       <c r="F107" s="5" t="s">
         <v>128</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="H107" s="7"/>
       <c r="I107" s="6"/>
@@ -6078,7 +6228,9 @@
       <c r="D108" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E108" s="7"/>
+      <c r="E108" s="9" t="s">
+        <v>330</v>
+      </c>
       <c r="F108" s="7"/>
       <c r="G108" s="7"/>
       <c r="H108" s="7"/>
@@ -6099,12 +6251,14 @@
       <c r="D109" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E109" s="7"/>
+      <c r="E109" s="9" t="s">
+        <v>331</v>
+      </c>
       <c r="F109" s="5" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="H109" s="7"/>
       <c r="I109" s="6"/>
@@ -6124,7 +6278,9 @@
       <c r="D110" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E110" s="7"/>
+      <c r="E110" s="9" t="s">
+        <v>334</v>
+      </c>
       <c r="F110" s="5" t="s">
         <v>207</v>
       </c>
@@ -6147,9 +6303,11 @@
       <c r="D111" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E111" s="7"/>
+      <c r="E111" s="9" t="s">
+        <v>335</v>
+      </c>
       <c r="F111" s="5" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="G111" s="5" t="s">
         <v>144</v>
@@ -6172,7 +6330,9 @@
       <c r="D112" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E112" s="7"/>
+      <c r="E112" s="9" t="s">
+        <v>337</v>
+      </c>
       <c r="F112" s="5" t="s">
         <v>237</v>
       </c>
@@ -6195,9 +6355,11 @@
       <c r="D113" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E113" s="7"/>
+      <c r="E113" s="9" t="s">
+        <v>338</v>
+      </c>
       <c r="F113" s="5" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="G113" s="7"/>
       <c r="H113" s="7"/>
@@ -6218,12 +6380,14 @@
       <c r="D114" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E114" s="7"/>
+      <c r="E114" s="9" t="s">
+        <v>340</v>
+      </c>
       <c r="F114" s="5" t="s">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>318</v>
+        <v>342</v>
       </c>
       <c r="H114" s="7"/>
       <c r="I114" s="6"/>
@@ -6243,12 +6407,14 @@
       <c r="D115" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E115" s="7"/>
+      <c r="E115" s="9" t="s">
+        <v>343</v>
+      </c>
       <c r="F115" s="5" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="H115" s="7"/>
       <c r="I115" s="6"/>
@@ -6268,7 +6434,9 @@
       <c r="D116" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E116" s="7"/>
+      <c r="E116" s="9" t="s">
+        <v>175</v>
+      </c>
       <c r="F116" s="7"/>
       <c r="G116" s="7"/>
       <c r="H116" s="7"/>
@@ -6289,12 +6457,14 @@
       <c r="D117" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E117" s="7"/>
+      <c r="E117" s="9" t="s">
+        <v>346</v>
+      </c>
       <c r="F117" s="5" t="s">
-        <v>321</v>
+        <v>347</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>322</v>
+        <v>348</v>
       </c>
       <c r="H117" s="7"/>
       <c r="I117" s="6"/>
@@ -6314,7 +6484,9 @@
       <c r="D118" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E118" s="7"/>
+      <c r="E118" s="9" t="s">
+        <v>349</v>
+      </c>
       <c r="F118" s="5" t="s">
         <v>251</v>
       </c>
@@ -6337,12 +6509,14 @@
       <c r="D119" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E119" s="7"/>
+      <c r="E119" s="9" t="s">
+        <v>350</v>
+      </c>
       <c r="F119" s="5" t="s">
-        <v>323</v>
+        <v>351</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>324</v>
+        <v>352</v>
       </c>
       <c r="H119" s="7"/>
       <c r="I119" s="6"/>
@@ -6362,7 +6536,9 @@
       <c r="D120" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E120" s="7"/>
+      <c r="E120" s="9" t="s">
+        <v>353</v>
+      </c>
       <c r="F120" s="5" t="s">
         <v>97</v>
       </c>
@@ -6385,7 +6561,9 @@
       <c r="D121" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E121" s="7"/>
+      <c r="E121" s="9" t="s">
+        <v>354</v>
+      </c>
       <c r="F121" s="5" t="s">
         <v>202</v>
       </c>
@@ -6408,12 +6586,14 @@
       <c r="D122" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E122" s="7"/>
+      <c r="E122" s="9" t="s">
+        <v>355</v>
+      </c>
       <c r="F122" s="5" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="H122" s="7"/>
       <c r="I122" s="6"/>
@@ -6433,12 +6613,14 @@
       <c r="D123" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E123" s="7"/>
+      <c r="E123" s="9" t="s">
+        <v>358</v>
+      </c>
       <c r="F123" s="5" t="s">
         <v>207</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="H123" s="7"/>
       <c r="I123" s="6"/>
@@ -6458,7 +6640,9 @@
       <c r="D124" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E124" s="7"/>
+      <c r="E124" s="9" t="s">
+        <v>360</v>
+      </c>
       <c r="F124" s="7"/>
       <c r="G124" s="7"/>
       <c r="H124" s="7"/>
@@ -6479,12 +6663,14 @@
       <c r="D125" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E125" s="7"/>
+      <c r="E125" s="9" t="s">
+        <v>361</v>
+      </c>
       <c r="F125" s="5" t="s">
-        <v>328</v>
+        <v>362</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>329</v>
+        <v>363</v>
       </c>
       <c r="H125" s="7"/>
       <c r="I125" s="6"/>
@@ -6504,7 +6690,9 @@
       <c r="D126" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E126" s="7"/>
+      <c r="E126" s="9" t="s">
+        <v>364</v>
+      </c>
       <c r="F126" s="5" t="s">
         <v>119</v>
       </c>
@@ -6527,12 +6715,14 @@
       <c r="D127" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E127" s="7"/>
+      <c r="E127" s="9" t="s">
+        <v>365</v>
+      </c>
       <c r="F127" s="5" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="H127" s="7"/>
       <c r="I127" s="6"/>
@@ -6552,7 +6742,9 @@
       <c r="D128" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E128" s="7"/>
+      <c r="E128" s="9" t="s">
+        <v>367</v>
+      </c>
       <c r="F128" s="5" t="s">
         <v>269</v>
       </c>
@@ -6575,9 +6767,11 @@
       <c r="D129" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E129" s="7"/>
+      <c r="E129" s="9" t="s">
+        <v>368</v>
+      </c>
       <c r="F129" s="5" t="s">
-        <v>331</v>
+        <v>369</v>
       </c>
       <c r="G129" s="7"/>
       <c r="H129" s="7"/>
@@ -6600,10 +6794,10 @@
       </c>
       <c r="E130" s="7"/>
       <c r="F130" s="5" t="s">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>332</v>
+        <v>370</v>
       </c>
       <c r="H130" s="7"/>
       <c r="I130" s="6"/>
@@ -6625,10 +6819,10 @@
       </c>
       <c r="E131" s="7"/>
       <c r="F131" s="5" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>334</v>
+        <v>372</v>
       </c>
       <c r="H131" s="7"/>
       <c r="I131" s="6"/>
@@ -6671,10 +6865,10 @@
       </c>
       <c r="E133" s="7"/>
       <c r="F133" s="5" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>336</v>
+        <v>374</v>
       </c>
       <c r="H133" s="7"/>
       <c r="I133" s="6"/>
@@ -6696,7 +6890,7 @@
       </c>
       <c r="E134" s="7"/>
       <c r="F134" s="5" t="s">
-        <v>337</v>
+        <v>375</v>
       </c>
       <c r="G134" s="7"/>
       <c r="H134" s="7"/>
@@ -6719,10 +6913,10 @@
       </c>
       <c r="E135" s="7"/>
       <c r="F135" s="5" t="s">
-        <v>338</v>
+        <v>376</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>339</v>
+        <v>377</v>
       </c>
       <c r="H135" s="7"/>
       <c r="I135" s="6"/>
@@ -6767,7 +6961,7 @@
       </c>
       <c r="E137" s="7"/>
       <c r="F137" s="5" t="s">
-        <v>340</v>
+        <v>378</v>
       </c>
       <c r="G137" s="7"/>
       <c r="H137" s="7"/>
@@ -6790,10 +6984,10 @@
       </c>
       <c r="E138" s="7"/>
       <c r="F138" s="5" t="s">
-        <v>341</v>
+        <v>379</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>342</v>
+        <v>380</v>
       </c>
       <c r="H138" s="7"/>
       <c r="I138" s="6"/>
@@ -6815,10 +7009,10 @@
       </c>
       <c r="E139" s="7"/>
       <c r="F139" s="5" t="s">
-        <v>343</v>
+        <v>381</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>344</v>
+        <v>382</v>
       </c>
       <c r="H139" s="7"/>
       <c r="I139" s="6"/>
@@ -6861,10 +7055,10 @@
       </c>
       <c r="E141" s="7"/>
       <c r="F141" s="5" t="s">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>346</v>
+        <v>384</v>
       </c>
       <c r="H141" s="7"/>
       <c r="I141" s="6"/>
@@ -6909,10 +7103,10 @@
       </c>
       <c r="E143" s="7"/>
       <c r="F143" s="5" t="s">
-        <v>347</v>
+        <v>385</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>348</v>
+        <v>386</v>
       </c>
       <c r="H143" s="7"/>
       <c r="I143" s="6"/>
@@ -6957,7 +7151,7 @@
       </c>
       <c r="E145" s="7"/>
       <c r="F145" s="5" t="s">
-        <v>349</v>
+        <v>387</v>
       </c>
       <c r="G145" s="7"/>
       <c r="H145" s="7"/>
@@ -6980,7 +7174,7 @@
       </c>
       <c r="E146" s="7"/>
       <c r="F146" s="5" t="s">
-        <v>350</v>
+        <v>388</v>
       </c>
       <c r="G146" s="5" t="s">
         <v>291</v>
@@ -7008,7 +7202,7 @@
         <v>227</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>351</v>
+        <v>389</v>
       </c>
       <c r="H147" s="7"/>
       <c r="I147" s="6"/>
@@ -7051,10 +7245,10 @@
       </c>
       <c r="E149" s="7"/>
       <c r="F149" s="5" t="s">
-        <v>352</v>
+        <v>390</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>353</v>
+        <v>391</v>
       </c>
       <c r="H149" s="7"/>
       <c r="I149" s="6"/>
@@ -7097,10 +7291,10 @@
       </c>
       <c r="E151" s="7"/>
       <c r="F151" s="5" t="s">
-        <v>354</v>
+        <v>392</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="H151" s="7"/>
       <c r="I151" s="6"/>
@@ -7145,7 +7339,7 @@
       </c>
       <c r="E153" s="7"/>
       <c r="F153" s="5" t="s">
-        <v>356</v>
+        <v>394</v>
       </c>
       <c r="G153" s="7"/>
       <c r="H153" s="7"/>
@@ -7168,10 +7362,10 @@
       </c>
       <c r="E154" s="7"/>
       <c r="F154" s="5" t="s">
-        <v>357</v>
+        <v>395</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>358</v>
+        <v>396</v>
       </c>
       <c r="H154" s="7"/>
       <c r="I154" s="6"/>
@@ -7196,7 +7390,7 @@
         <v>274</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>359</v>
+        <v>397</v>
       </c>
       <c r="H155" s="7"/>
       <c r="I155" s="6"/>
@@ -7239,10 +7433,10 @@
       </c>
       <c r="E157" s="7"/>
       <c r="F157" s="5" t="s">
-        <v>360</v>
+        <v>398</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>361</v>
+        <v>399</v>
       </c>
       <c r="H157" s="7"/>
       <c r="I157" s="6"/>
@@ -7287,10 +7481,10 @@
       </c>
       <c r="E159" s="7"/>
       <c r="F159" s="5" t="s">
-        <v>362</v>
+        <v>400</v>
       </c>
       <c r="G159" s="5" t="s">
-        <v>363</v>
+        <v>401</v>
       </c>
       <c r="H159" s="7"/>
       <c r="I159" s="6"/>
@@ -7335,7 +7529,7 @@
       </c>
       <c r="E161" s="7"/>
       <c r="F161" s="5" t="s">
-        <v>364</v>
+        <v>402</v>
       </c>
       <c r="G161" s="7"/>
       <c r="H161" s="7"/>
@@ -7358,10 +7552,10 @@
       </c>
       <c r="E162" s="7"/>
       <c r="F162" s="5" t="s">
-        <v>365</v>
+        <v>403</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>366</v>
+        <v>404</v>
       </c>
       <c r="H162" s="7"/>
       <c r="I162" s="6"/>
@@ -7386,7 +7580,7 @@
         <v>251</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>367</v>
+        <v>405</v>
       </c>
       <c r="H163" s="7"/>
       <c r="I163" s="6"/>
@@ -7429,10 +7623,10 @@
       </c>
       <c r="E165" s="7"/>
       <c r="F165" s="5" t="s">
-        <v>368</v>
+        <v>406</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>369</v>
+        <v>407</v>
       </c>
       <c r="H165" s="7"/>
       <c r="I165" s="6"/>
@@ -7454,7 +7648,7 @@
       </c>
       <c r="E166" s="7"/>
       <c r="F166" s="5" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="G166" s="7"/>
       <c r="H166" s="7"/>
@@ -7477,10 +7671,10 @@
       </c>
       <c r="E167" s="7"/>
       <c r="F167" s="5" t="s">
-        <v>371</v>
+        <v>409</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>372</v>
+        <v>410</v>
       </c>
       <c r="H167" s="7"/>
       <c r="I167" s="6"/>
@@ -7525,7 +7719,7 @@
       </c>
       <c r="E169" s="7"/>
       <c r="F169" s="5" t="s">
-        <v>373</v>
+        <v>411</v>
       </c>
       <c r="G169" s="7"/>
       <c r="H169" s="7"/>
@@ -7548,10 +7742,10 @@
       </c>
       <c r="E170" s="7"/>
       <c r="F170" s="5" t="s">
-        <v>374</v>
+        <v>412</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>375</v>
+        <v>413</v>
       </c>
       <c r="H170" s="7"/>
       <c r="I170" s="6"/>
@@ -7576,7 +7770,7 @@
         <v>158</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>376</v>
+        <v>414</v>
       </c>
       <c r="H171" s="7"/>
       <c r="I171" s="6"/>
@@ -7619,10 +7813,10 @@
       </c>
       <c r="E173" s="7"/>
       <c r="F173" s="5" t="s">
-        <v>377</v>
+        <v>415</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>378</v>
+        <v>416</v>
       </c>
       <c r="H173" s="7"/>
       <c r="I173" s="6"/>
@@ -7644,7 +7838,7 @@
       </c>
       <c r="E174" s="7"/>
       <c r="F174" s="5" t="s">
-        <v>379</v>
+        <v>417</v>
       </c>
       <c r="G174" s="7"/>
       <c r="H174" s="7"/>
@@ -7667,10 +7861,10 @@
       </c>
       <c r="E175" s="7"/>
       <c r="F175" s="5" t="s">
-        <v>380</v>
+        <v>418</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>332</v>
+        <v>370</v>
       </c>
       <c r="H175" s="7"/>
       <c r="I175" s="6"/>
@@ -7692,7 +7886,7 @@
       </c>
       <c r="E176" s="7"/>
       <c r="F176" s="5" t="s">
-        <v>381</v>
+        <v>419</v>
       </c>
       <c r="G176" s="7"/>
       <c r="H176" s="7"/>
@@ -7715,7 +7909,7 @@
       </c>
       <c r="E177" s="7"/>
       <c r="F177" s="5" t="s">
-        <v>382</v>
+        <v>420</v>
       </c>
       <c r="G177" s="7"/>
       <c r="H177" s="7"/>
@@ -7738,10 +7932,10 @@
       </c>
       <c r="E178" s="7"/>
       <c r="F178" s="5" t="s">
-        <v>383</v>
+        <v>421</v>
       </c>
       <c r="G178" s="5" t="s">
-        <v>384</v>
+        <v>422</v>
       </c>
       <c r="H178" s="7"/>
       <c r="I178" s="6"/>
@@ -7763,10 +7957,10 @@
       </c>
       <c r="E179" s="7"/>
       <c r="F179" s="5" t="s">
-        <v>385</v>
+        <v>423</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>386</v>
+        <v>424</v>
       </c>
       <c r="H179" s="7"/>
       <c r="I179" s="6"/>
@@ -7809,10 +8003,10 @@
       </c>
       <c r="E181" s="7"/>
       <c r="F181" s="5" t="s">
-        <v>387</v>
+        <v>425</v>
       </c>
       <c r="G181" s="5" t="s">
-        <v>388</v>
+        <v>426</v>
       </c>
       <c r="H181" s="7"/>
       <c r="I181" s="6"/>
@@ -7857,10 +8051,10 @@
       </c>
       <c r="E183" s="7"/>
       <c r="F183" s="5" t="s">
-        <v>389</v>
+        <v>427</v>
       </c>
       <c r="G183" s="5" t="s">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="H183" s="7"/>
       <c r="I183" s="6"/>
@@ -7905,7 +8099,7 @@
       </c>
       <c r="E185" s="7"/>
       <c r="F185" s="5" t="s">
-        <v>391</v>
+        <v>429</v>
       </c>
       <c r="G185" s="7"/>
       <c r="H185" s="7"/>
@@ -7928,10 +8122,10 @@
       </c>
       <c r="E186" s="7"/>
       <c r="F186" s="5" t="s">
-        <v>392</v>
+        <v>430</v>
       </c>
       <c r="G186" s="5" t="s">
-        <v>393</v>
+        <v>431</v>
       </c>
       <c r="H186" s="7"/>
       <c r="I186" s="6"/>
@@ -7953,10 +8147,10 @@
       </c>
       <c r="E187" s="7"/>
       <c r="F187" s="5" t="s">
-        <v>394</v>
+        <v>432</v>
       </c>
       <c r="G187" s="5" t="s">
-        <v>395</v>
+        <v>433</v>
       </c>
       <c r="H187" s="7"/>
       <c r="I187" s="6"/>
@@ -7999,10 +8193,10 @@
       </c>
       <c r="E189" s="7"/>
       <c r="F189" s="5" t="s">
-        <v>396</v>
+        <v>434</v>
       </c>
       <c r="G189" s="5" t="s">
-        <v>397</v>
+        <v>435</v>
       </c>
       <c r="H189" s="7"/>
       <c r="I189" s="6"/>
@@ -8024,7 +8218,7 @@
       </c>
       <c r="E190" s="7"/>
       <c r="F190" s="5" t="s">
-        <v>398</v>
+        <v>436</v>
       </c>
       <c r="G190" s="7"/>
       <c r="H190" s="7"/>
@@ -8047,10 +8241,10 @@
       </c>
       <c r="E191" s="7"/>
       <c r="F191" s="5" t="s">
-        <v>399</v>
+        <v>437</v>
       </c>
       <c r="G191" s="5" t="s">
-        <v>400</v>
+        <v>438</v>
       </c>
       <c r="H191" s="7"/>
       <c r="I191" s="6"/>
@@ -8095,7 +8289,7 @@
       </c>
       <c r="E193" s="7"/>
       <c r="F193" s="5" t="s">
-        <v>401</v>
+        <v>439</v>
       </c>
       <c r="G193" s="7"/>
       <c r="H193" s="7"/>
@@ -8118,10 +8312,10 @@
       </c>
       <c r="E194" s="7"/>
       <c r="F194" s="5" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="G194" s="5" t="s">
-        <v>402</v>
+        <v>440</v>
       </c>
       <c r="H194" s="7"/>
       <c r="I194" s="6"/>
@@ -8143,10 +8337,10 @@
       </c>
       <c r="E195" s="7"/>
       <c r="F195" s="5" t="s">
-        <v>403</v>
+        <v>441</v>
       </c>
       <c r="G195" s="5" t="s">
-        <v>404</v>
+        <v>442</v>
       </c>
       <c r="H195" s="7"/>
       <c r="I195" s="6"/>
@@ -8189,10 +8383,10 @@
       </c>
       <c r="E197" s="7"/>
       <c r="F197" s="5" t="s">
-        <v>405</v>
+        <v>443</v>
       </c>
       <c r="G197" s="5" t="s">
-        <v>406</v>
+        <v>444</v>
       </c>
       <c r="H197" s="7"/>
       <c r="I197" s="6"/>
@@ -8214,7 +8408,7 @@
       </c>
       <c r="E198" s="7"/>
       <c r="F198" s="5" t="s">
-        <v>407</v>
+        <v>445</v>
       </c>
       <c r="G198" s="7"/>
       <c r="H198" s="7"/>
@@ -8237,10 +8431,10 @@
       </c>
       <c r="E199" s="7"/>
       <c r="F199" s="5" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="G199" s="5" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="H199" s="7"/>
       <c r="I199" s="6"/>
@@ -8285,7 +8479,7 @@
       </c>
       <c r="E201" s="7"/>
       <c r="F201" s="5" t="s">
-        <v>409</v>
+        <v>447</v>
       </c>
       <c r="G201" s="7"/>
       <c r="H201" s="7"/>
@@ -8308,10 +8502,10 @@
       </c>
       <c r="E202" s="7"/>
       <c r="F202" s="5" t="s">
-        <v>410</v>
+        <v>448</v>
       </c>
       <c r="G202" s="5" t="s">
-        <v>411</v>
+        <v>449</v>
       </c>
       <c r="H202" s="7"/>
       <c r="I202" s="6"/>
@@ -8333,10 +8527,10 @@
       </c>
       <c r="E203" s="7"/>
       <c r="F203" s="5" t="s">
-        <v>412</v>
+        <v>450</v>
       </c>
       <c r="G203" s="5" t="s">
-        <v>413</v>
+        <v>451</v>
       </c>
       <c r="H203" s="7"/>
       <c r="I203" s="6"/>
@@ -8379,10 +8573,10 @@
       </c>
       <c r="E205" s="7"/>
       <c r="F205" s="5" t="s">
-        <v>414</v>
+        <v>452</v>
       </c>
       <c r="G205" s="5" t="s">
-        <v>415</v>
+        <v>453</v>
       </c>
       <c r="H205" s="7"/>
       <c r="I205" s="6"/>
@@ -8427,7 +8621,7 @@
       </c>
       <c r="E207" s="7"/>
       <c r="F207" s="5" t="s">
-        <v>416</v>
+        <v>454</v>
       </c>
       <c r="G207" s="5" t="s">
         <v>108</v>
@@ -8452,7 +8646,7 @@
       </c>
       <c r="E208" s="7"/>
       <c r="F208" s="5" t="s">
-        <v>337</v>
+        <v>375</v>
       </c>
       <c r="G208" s="7"/>
       <c r="H208" s="7"/>
@@ -8475,7 +8669,7 @@
       </c>
       <c r="E209" s="7"/>
       <c r="F209" s="5" t="s">
-        <v>417</v>
+        <v>455</v>
       </c>
       <c r="G209" s="7"/>
       <c r="H209" s="7"/>
@@ -8498,10 +8692,10 @@
       </c>
       <c r="E210" s="7"/>
       <c r="F210" s="5" t="s">
-        <v>418</v>
+        <v>456</v>
       </c>
       <c r="G210" s="5" t="s">
-        <v>419</v>
+        <v>457</v>
       </c>
       <c r="H210" s="7"/>
       <c r="I210" s="6"/>
@@ -8523,10 +8717,10 @@
       </c>
       <c r="E211" s="7"/>
       <c r="F211" s="5" t="s">
-        <v>379</v>
+        <v>417</v>
       </c>
       <c r="G211" s="5" t="s">
-        <v>420</v>
+        <v>458</v>
       </c>
       <c r="H211" s="7"/>
       <c r="I211" s="6"/>
@@ -8569,10 +8763,10 @@
       </c>
       <c r="E213" s="7"/>
       <c r="F213" s="5" t="s">
-        <v>421</v>
+        <v>459</v>
       </c>
       <c r="G213" s="5" t="s">
-        <v>422</v>
+        <v>460</v>
       </c>
       <c r="H213" s="7"/>
       <c r="I213" s="6"/>
@@ -8594,7 +8788,7 @@
       </c>
       <c r="E214" s="7"/>
       <c r="F214" s="5" t="s">
-        <v>423</v>
+        <v>461</v>
       </c>
       <c r="G214" s="7"/>
       <c r="H214" s="7"/>
@@ -8617,10 +8811,10 @@
       </c>
       <c r="E215" s="7"/>
       <c r="F215" s="5" t="s">
-        <v>424</v>
+        <v>462</v>
       </c>
       <c r="G215" s="5" t="s">
-        <v>425</v>
+        <v>463</v>
       </c>
       <c r="H215" s="7"/>
       <c r="I215" s="6"/>
@@ -8688,10 +8882,10 @@
       </c>
       <c r="E218" s="7"/>
       <c r="F218" s="5" t="s">
-        <v>426</v>
+        <v>464</v>
       </c>
       <c r="G218" s="5" t="s">
-        <v>427</v>
+        <v>465</v>
       </c>
       <c r="H218" s="7"/>
       <c r="I218" s="6"/>
@@ -8716,7 +8910,7 @@
         <v>124</v>
       </c>
       <c r="G219" s="5" t="s">
-        <v>428</v>
+        <v>466</v>
       </c>
       <c r="H219" s="7"/>
       <c r="I219" s="6"/>
@@ -8759,10 +8953,10 @@
       </c>
       <c r="E221" s="7"/>
       <c r="F221" s="5" t="s">
-        <v>429</v>
+        <v>467</v>
       </c>
       <c r="G221" s="5" t="s">
-        <v>430</v>
+        <v>468</v>
       </c>
       <c r="H221" s="7"/>
       <c r="I221" s="6"/>
@@ -8784,7 +8978,7 @@
       </c>
       <c r="E222" s="7"/>
       <c r="F222" s="5" t="s">
-        <v>431</v>
+        <v>469</v>
       </c>
       <c r="G222" s="7"/>
       <c r="H222" s="7"/>
@@ -8807,10 +9001,10 @@
       </c>
       <c r="E223" s="7"/>
       <c r="F223" s="5" t="s">
-        <v>432</v>
+        <v>470</v>
       </c>
       <c r="G223" s="5" t="s">
-        <v>433</v>
+        <v>471</v>
       </c>
       <c r="H223" s="7"/>
       <c r="I223" s="6"/>
@@ -8832,7 +9026,7 @@
       </c>
       <c r="E224" s="7"/>
       <c r="F224" s="5" t="s">
-        <v>434</v>
+        <v>472</v>
       </c>
       <c r="G224" s="7"/>
       <c r="H224" s="7"/>
@@ -8855,7 +9049,7 @@
       </c>
       <c r="E225" s="7"/>
       <c r="F225" s="5" t="s">
-        <v>435</v>
+        <v>473</v>
       </c>
       <c r="G225" s="7"/>
       <c r="H225" s="7"/>
@@ -8878,10 +9072,10 @@
       </c>
       <c r="E226" s="7"/>
       <c r="F226" s="5" t="s">
-        <v>436</v>
+        <v>474</v>
       </c>
       <c r="G226" s="5" t="s">
-        <v>437</v>
+        <v>475</v>
       </c>
       <c r="H226" s="7"/>
       <c r="I226" s="6"/>
@@ -8906,7 +9100,7 @@
         <v>269</v>
       </c>
       <c r="G227" s="5" t="s">
-        <v>376</v>
+        <v>414</v>
       </c>
       <c r="H227" s="7"/>
       <c r="I227" s="6"/>
@@ -8949,10 +9143,10 @@
       </c>
       <c r="E229" s="7"/>
       <c r="F229" s="5" t="s">
-        <v>438</v>
+        <v>476</v>
       </c>
       <c r="G229" s="5" t="s">
-        <v>439</v>
+        <v>477</v>
       </c>
       <c r="H229" s="7"/>
       <c r="I229" s="6"/>
@@ -8997,7 +9191,7 @@
       </c>
       <c r="E231" s="7"/>
       <c r="F231" s="5" t="s">
-        <v>416</v>
+        <v>454</v>
       </c>
       <c r="G231" s="5" t="s">
         <v>161</v>
@@ -9045,7 +9239,7 @@
       </c>
       <c r="E233" s="7"/>
       <c r="F233" s="5" t="s">
-        <v>440</v>
+        <v>478</v>
       </c>
       <c r="G233" s="7"/>
       <c r="H233" s="7"/>
@@ -9068,10 +9262,10 @@
       </c>
       <c r="E234" s="7"/>
       <c r="F234" s="5" t="s">
-        <v>441</v>
+        <v>479</v>
       </c>
       <c r="G234" s="5" t="s">
-        <v>442</v>
+        <v>480</v>
       </c>
       <c r="H234" s="7"/>
       <c r="I234" s="6"/>
@@ -9096,7 +9290,7 @@
         <v>124</v>
       </c>
       <c r="G235" s="5" t="s">
-        <v>443</v>
+        <v>481</v>
       </c>
       <c r="H235" s="7"/>
       <c r="I235" s="6"/>
@@ -9139,10 +9333,10 @@
       </c>
       <c r="E237" s="7"/>
       <c r="F237" s="5" t="s">
-        <v>444</v>
+        <v>482</v>
       </c>
       <c r="G237" s="5" t="s">
-        <v>445</v>
+        <v>483</v>
       </c>
       <c r="H237" s="7"/>
       <c r="I237" s="6"/>
@@ -9164,7 +9358,7 @@
       </c>
       <c r="E238" s="7"/>
       <c r="F238" s="5" t="s">
-        <v>398</v>
+        <v>436</v>
       </c>
       <c r="G238" s="7"/>
       <c r="H238" s="7"/>
@@ -9187,10 +9381,10 @@
       </c>
       <c r="E239" s="7"/>
       <c r="F239" s="5" t="s">
-        <v>446</v>
+        <v>484</v>
       </c>
       <c r="G239" s="5" t="s">
-        <v>447</v>
+        <v>485</v>
       </c>
       <c r="H239" s="7"/>
       <c r="I239" s="6"/>
@@ -9212,7 +9406,7 @@
       </c>
       <c r="E240" s="7"/>
       <c r="F240" s="5" t="s">
-        <v>423</v>
+        <v>461</v>
       </c>
       <c r="G240" s="7"/>
       <c r="H240" s="7"/>
@@ -9235,7 +9429,7 @@
       </c>
       <c r="E241" s="7"/>
       <c r="F241" s="5" t="s">
-        <v>448</v>
+        <v>486</v>
       </c>
       <c r="G241" s="7"/>
       <c r="H241" s="7"/>
@@ -9258,10 +9452,10 @@
       </c>
       <c r="E242" s="7"/>
       <c r="F242" s="5" t="s">
-        <v>449</v>
+        <v>487</v>
       </c>
       <c r="G242" s="5" t="s">
-        <v>450</v>
+        <v>488</v>
       </c>
       <c r="H242" s="7"/>
       <c r="I242" s="6"/>
@@ -9283,10 +9477,10 @@
       </c>
       <c r="E243" s="7"/>
       <c r="F243" s="5" t="s">
-        <v>451</v>
+        <v>489</v>
       </c>
       <c r="G243" s="5" t="s">
-        <v>452</v>
+        <v>490</v>
       </c>
       <c r="H243" s="7"/>
       <c r="I243" s="6"/>
@@ -9329,10 +9523,10 @@
       </c>
       <c r="E245" s="7"/>
       <c r="F245" s="5" t="s">
-        <v>453</v>
+        <v>491</v>
       </c>
       <c r="G245" s="5" t="s">
-        <v>454</v>
+        <v>492</v>
       </c>
       <c r="H245" s="7"/>
       <c r="I245" s="6"/>
@@ -9354,7 +9548,7 @@
       </c>
       <c r="E246" s="7"/>
       <c r="F246" s="5" t="s">
-        <v>455</v>
+        <v>493</v>
       </c>
       <c r="G246" s="7"/>
       <c r="H246" s="7"/>
@@ -9377,10 +9571,10 @@
       </c>
       <c r="E247" s="7"/>
       <c r="F247" s="5" t="s">
-        <v>456</v>
+        <v>494</v>
       </c>
       <c r="G247" s="5" t="s">
-        <v>457</v>
+        <v>495</v>
       </c>
       <c r="H247" s="7"/>
       <c r="I247" s="6"/>
@@ -9425,7 +9619,7 @@
       </c>
       <c r="E249" s="7"/>
       <c r="F249" s="5" t="s">
-        <v>458</v>
+        <v>496</v>
       </c>
       <c r="G249" s="7"/>
       <c r="H249" s="7"/>
@@ -9435,7 +9629,7 @@
     </row>
     <row r="250" ht="14.25" customHeight="1">
       <c r="A250" s="3"/>
-      <c r="B250" s="9"/>
+      <c r="B250" s="10"/>
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
@@ -9448,7 +9642,7 @@
     </row>
     <row r="251" ht="14.25" customHeight="1">
       <c r="A251" s="6"/>
-      <c r="B251" s="10"/>
+      <c r="B251" s="11"/>
       <c r="C251" s="6"/>
       <c r="D251" s="6"/>
       <c r="E251" s="6"/>
@@ -9461,7 +9655,7 @@
     </row>
     <row r="252" ht="14.25" customHeight="1">
       <c r="A252" s="6"/>
-      <c r="B252" s="10"/>
+      <c r="B252" s="11"/>
       <c r="C252" s="6"/>
       <c r="D252" s="6"/>
       <c r="E252" s="6"/>
@@ -9474,7 +9668,7 @@
     </row>
     <row r="253" ht="14.25" customHeight="1">
       <c r="A253" s="6"/>
-      <c r="B253" s="10"/>
+      <c r="B253" s="11"/>
       <c r="C253" s="6"/>
       <c r="D253" s="6"/>
       <c r="E253" s="6"/>
@@ -9509,39 +9703,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>459</v>
+        <v>497</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>460</v>
+        <v>498</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>461</v>
+        <v>499</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>462</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>463</v>
+        <v>501</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>464</v>
+        <v>502</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>465</v>
+        <v>503</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>466</v>
+        <v>504</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>467</v>
+        <v>505</v>
       </c>
       <c r="B5" s="3">
         <v>2026.0</v>
@@ -9549,7 +9743,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>468</v>
+        <v>506</v>
       </c>
       <c r="B6" s="3">
         <v>9.63931444898E11</v>
@@ -9557,10 +9751,10 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>470</v>
+        <v>507</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="8">

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Desktop\جداول المناوبات\جداول شهر 8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43328090-9D65-4C71-BD23-A30427DC3D92}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1864C1D-E3C2-4D64-900F-299C9F3721C7}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mn1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="838">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2182" uniqueCount="838">
   <si>
     <t>اليوم</t>
   </si>
@@ -6340,35 +6340,12 @@
     <t>رؤى عطار - روان عبس - هاجر الصيادي - مجيدة عويجة</t>
   </si>
   <si>
-    <t>شهد دباغ - شهد حمدان - خالد العيسى - فاطمة سليمان
-بتول  شكوا - سارة سعيد - بلال صبحان
-سوسن بهلول - سمر سرماني - سلام شيخ قدور</t>
-  </si>
-  <si>
-    <t>بيان  بيطار - رغد الافندي - زيلان علي - منير ريحاوي
-سارة عرابي - سهام عرابي - لانا صباغ - جودي حمام
-فدى قصاص - غفران جزار - براءة أحمد</t>
-  </si>
-  <si>
-    <t>تسنيم بخصو - سنا ديب - شاميران بازار - خديجة بكار
-وتين كسار - حلا سعيد - نور علاف - شمس حايك
-أمنية عدلة - رند كيالي - مصطفى جورية</t>
-  </si>
-  <si>
     <t>بيان قبسيز - روضة صباغ - زبيدة خرمندة - رنيم ضبيط</t>
   </si>
   <si>
     <t>تغريد جعفر - علي عبدالرزاق - محمد نور ونس</t>
   </si>
   <si>
-    <t>أريج الخطيب - أحمد محمد - راما بوشي - سدرة صقر
-روان بطل - روان عبدالكريم - ناديا جمعة - لجين عجمي
-هديل قناعة - هند فستق - لارا النعسان</t>
-  </si>
-  <si>
-    <t>بتول هنداوي - تسنيم فاضل -جودي بوشي- فاضلة شيخ محمد</t>
-  </si>
-  <si>
     <t>بانة شحرور - رامي سليمان - ماريا آغا</t>
   </si>
   <si>
@@ -6405,100 +6382,102 @@
     <t>همسة مطر - آمنة هندية - نور حرح</t>
   </si>
   <si>
-    <t xml:space="preserve">
-ريما زهرة - رحاب ملحم - خديجة السعيد
-عبدالله أزرق - محمد كجان - أحمد كردية
+    <t>سارة زيدان - ميسم بطحيش - ريم مكيس</t>
+  </si>
+  <si>
+    <t>آية وتي - قمر بودقجي</t>
+  </si>
+  <si>
+    <t>بتول شياح - آية خلوف - علا خلوف</t>
+  </si>
+  <si>
+    <t>رؤى عابدين - سدرة أرمنازي</t>
+  </si>
+  <si>
+    <t>رشا العوير - سلام عرب</t>
+  </si>
+  <si>
+    <t>ليندا خانجي - دليفان بطال</t>
+  </si>
+  <si>
+    <t>فاطمة أسود</t>
+  </si>
+  <si>
+    <t>راما زين الدين - بيان قطنه جي - سلوى تمو</t>
+  </si>
+  <si>
+    <t>رشا سلمان - نور قاسم - شيماء هلال</t>
+  </si>
+  <si>
+    <t>انجي تفنكجي - ايمان عبدالو - راما كبب</t>
+  </si>
+  <si>
+    <t>أريج جوجو - ايمان غزال - هبة سراج</t>
+  </si>
+  <si>
+    <t>آية مركن - آية مكانسي</t>
+  </si>
+  <si>
+    <t>سفانة كريم - روابي - سنا حمو - شهد بركات</t>
+  </si>
+  <si>
+    <t>تسنيم عسلية - بيان شامية</t>
+  </si>
+  <si>
+    <t>ديمة الناصر - آيلاف وادي - روشان حسو</t>
+  </si>
+  <si>
+    <t>راما سيد علي - رفاه عثمان - أروى حاج موسى</t>
+  </si>
+  <si>
+    <t>فاطمة المنار عبدربه - كابرئيل صومي</t>
+  </si>
+  <si>
+    <t>لين سلطان - فاتن المصطفى - روان جابي</t>
+  </si>
+  <si>
+    <t>فاطمة اسماعيل - شهد حمادية - دياب الذياب</t>
+  </si>
+  <si>
+    <t>آب - شهر 8 -</t>
+  </si>
+  <si>
+    <t>شهد دباغ - شهد حمدان - خالد العيسى - فاطمة سليمان - بتول  شكوا - سارة سعيد - بلال صبحان - سوسن بهلول - سمر سرماني - سلام شيخ قدور</t>
+  </si>
+  <si>
+    <t>بيان  بيطار - رغد الافندي - زيلان علي - منير ريحاوي - سارة عرابي - سهام عرابي - لانا صباغ - جودي حمام - فدى قصاص - غفران جزار - براءة أحمد</t>
+  </si>
+  <si>
+    <t>تسنيم بخصو - سنا ديب - شاميران بازار - خديجة بكار - وتين كسار - حلا سعيد - نور علاف - شمس حايك - أمنية عدلة - رند كيالي - مصطفى جورية</t>
+  </si>
+  <si>
+    <t>أريج الخطيب - أحمد محمد - راما بوشي - سدرة صقر - روان بطل - روان عبدالكريم - ناديا جمعة - لجين عجمي - هديل قناعة - هند فستق - لارا النعسان</t>
+  </si>
+  <si>
+    <t>بتول هنداوي - تسنيم فاضل - جودي بوشي - فاضلة شيخ محمد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ريما زهرة - رحاب ملحم - خديجة السعيد - عبدالله أزرق - محمد كجان - أحمد كردية
 </t>
   </si>
   <si>
-    <t xml:space="preserve">آلاء جميلي - نتالي نجار - علي العباس
-بانة كاتب - ايمان لبابيدي - سنا رشواني
-عدن أقرع - علا بكري </t>
-  </si>
-  <si>
-    <t>سنا طاهر - زين بركات - نور أشرفي
-علا اليوسف - عائشة عبدالخالق
-مريم عموري - تسنيم الخال</t>
-  </si>
-  <si>
-    <t>سارة زيدان - ميسم بطحيش - ريم مكيس</t>
-  </si>
-  <si>
-    <t>آية وتي - قمر بودقجي</t>
-  </si>
-  <si>
-    <t>حسن الحسن - خالد رزوق - رغد الشهابي
-شهد مراد - سالي عجمية - هيا جمول
-محمد السعيد</t>
-  </si>
-  <si>
-    <t>بتول شياح - آية خلوف - علا خلوف</t>
-  </si>
-  <si>
-    <t>رؤى عابدين - سدرة أرمنازي</t>
-  </si>
-  <si>
-    <t>رشا العوير - سلام عرب</t>
-  </si>
-  <si>
-    <t>ليندا خانجي - دليفان بطال</t>
-  </si>
-  <si>
-    <t>فاطمة أسود</t>
-  </si>
-  <si>
-    <t>راما زين الدين - بيان قطنه جي - سلوى تمو</t>
-  </si>
-  <si>
-    <t>رشا سلمان - نور قاسم - شيماء هلال</t>
-  </si>
-  <si>
-    <t>انجي تفنكجي - ايمان عبدالو - راما كبب</t>
-  </si>
-  <si>
-    <t>أريج جوجو - ايمان غزال - هبة سراج</t>
-  </si>
-  <si>
-    <t>آية مركن - آية مكانسي</t>
-  </si>
-  <si>
-    <t>سفانة كريم - روابي - سنا حمو - شهد بركات</t>
-  </si>
-  <si>
-    <t>تسنيم عسلية - بيان شامية</t>
-  </si>
-  <si>
-    <t>ديمة الناصر - آيلاف وادي - روشان حسو</t>
-  </si>
-  <si>
-    <t xml:space="preserve">خديجة مصطفى - رؤى الداغري - هيا مشهدي
-لينا الخطيب - أحمد رسلان - بيان الرفاعي
-أماني باكير
+    <t xml:space="preserve">آلاء جميلي - نتالي نجار - علي العباس - بانة كاتب - ايمان لبابيدي - سنا رشواني - عدن أقرع - علا بكري </t>
+  </si>
+  <si>
+    <t>سنا طاهر - زين بركات - نور أشرفي - علا اليوسف - عائشة عبدالخالق - مريم عموري - تسنيم الخال</t>
+  </si>
+  <si>
+    <t>حسن الحسن - خالد رزوق - رغد الشهابي - شهد مراد - سالي عجمية - هيا جمول - محمد السعيد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خديجة مصطفى - رؤى الداغري - هيا مشهدي - لينا الخطيب - أحمد رسلان - بيان الرفاعي - أماني باكير
 </t>
   </si>
   <si>
-    <t>نور حج علي - شهد ساكت - بيان دندل 
-فاطمة نجار - جودي مؤذن 
-علا ربوع - أمل الخالد</t>
-  </si>
-  <si>
-    <t>سدرة رسلان - سلوى حريري - رشا سلات
-تيماء عبدالغفور - فرح البابا - كوثر العلي</t>
-  </si>
-  <si>
-    <t>راما سيد علي - رفاه عثمان - أروى حاج موسى</t>
-  </si>
-  <si>
-    <t>فاطمة المنار عبدربه - كابرئيل صومي</t>
-  </si>
-  <si>
-    <t>لين سلطان - فاتن المصطفى - روان جابي</t>
-  </si>
-  <si>
-    <t>فاطمة اسماعيل - شهد حمادية - دياب الذياب</t>
-  </si>
-  <si>
-    <t>آب - شهر 8 -</t>
+    <t>نور حج علي - شهد ساكت - بيان دندل  - فاطمة نجار - جودي مؤذن - علا ربوع - أمل الخالد</t>
+  </si>
+  <si>
+    <t>سدرة رسلان - سلوى حريري - رشا سلات - تيماء عبدالغفور - فرح البابا - كوثر العلي</t>
   </si>
 </sst>
 </file>
@@ -11026,7 +11005,7 @@
         <v>46236</v>
       </c>
       <c r="C3" s="6" t="str">
-        <f t="shared" ref="C2:C32" si="0">CHOOSE(WEEKDAY(B3,17),"الأحد","الإثنين","الثلاثاء","الأربعاء","الخميس","الجمعة","السبت")</f>
+        <f t="shared" ref="C3:C32" si="0">CHOOSE(WEEKDAY(B3,17),"الأحد","الإثنين","الثلاثاء","الأربعاء","الخميس","الجمعة","السبت")</f>
         <v>الأحد</v>
       </c>
       <c r="D3" s="17" t="s">
@@ -14949,13 +14928,15 @@
   <dimension ref="A1:K99"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="4" width="14.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="11" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15">
+    <row r="1" spans="1:11" ht="30">
       <c r="A1" s="24" t="s">
         <v>260</v>
       </c>
@@ -14978,7 +14959,7 @@
       <c r="J1" s="27"/>
       <c r="K1" s="27"/>
     </row>
-    <row r="2" spans="1:11" ht="60">
+    <row r="2" spans="1:11" ht="45">
       <c r="A2" s="28" t="s">
         <v>265</v>
       </c>
@@ -14986,10 +14967,10 @@
         <v>784</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="E2" s="30"/>
       <c r="F2" s="31"/>
@@ -14999,7 +14980,7 @@
       <c r="J2" s="31"/>
       <c r="K2" s="31"/>
     </row>
-    <row r="3" spans="1:11" ht="60">
+    <row r="3" spans="1:11" ht="45">
       <c r="A3" s="28" t="s">
         <v>266</v>
       </c>
@@ -15007,10 +14988,10 @@
         <v>785</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>823</v>
+        <v>814</v>
       </c>
       <c r="E3" s="30"/>
       <c r="F3" s="31"/>
@@ -15020,7 +15001,7 @@
       <c r="J3" s="31"/>
       <c r="K3" s="31"/>
     </row>
-    <row r="4" spans="1:11" ht="60">
+    <row r="4" spans="1:11" ht="45">
       <c r="A4" s="28" t="s">
         <v>267</v>
       </c>
@@ -15028,10 +15009,10 @@
         <v>786</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>824</v>
+        <v>815</v>
       </c>
       <c r="E4" s="30"/>
       <c r="F4" s="31"/>
@@ -15041,7 +15022,7 @@
       <c r="J4" s="31"/>
       <c r="K4" s="31"/>
     </row>
-    <row r="5" spans="1:11" ht="60">
+    <row r="5" spans="1:11" ht="45">
       <c r="A5" s="28" t="s">
         <v>268</v>
       </c>
@@ -15049,10 +15030,10 @@
         <v>787</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>825</v>
+        <v>816</v>
       </c>
       <c r="E5" s="30"/>
       <c r="F5" s="31"/>
@@ -15062,7 +15043,7 @@
       <c r="J5" s="31"/>
       <c r="K5" s="31"/>
     </row>
-    <row r="6" spans="1:11" ht="60">
+    <row r="6" spans="1:11" ht="45">
       <c r="A6" s="28" t="s">
         <v>269</v>
       </c>
@@ -15070,10 +15051,10 @@
         <v>788</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>826</v>
+        <v>817</v>
       </c>
       <c r="E6" s="30"/>
       <c r="F6" s="31"/>
@@ -15083,7 +15064,7 @@
       <c r="J6" s="31"/>
       <c r="K6" s="31"/>
     </row>
-    <row r="7" spans="1:11" ht="60">
+    <row r="7" spans="1:11" ht="45">
       <c r="A7" s="28" t="s">
         <v>270</v>
       </c>
@@ -15091,10 +15072,10 @@
         <v>789</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>827</v>
+        <v>818</v>
       </c>
       <c r="E7" s="30"/>
       <c r="F7" s="31"/>
@@ -15112,10 +15093,10 @@
         <v>790</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>828</v>
+        <v>819</v>
       </c>
       <c r="E8" s="30"/>
       <c r="F8" s="31"/>
@@ -15125,7 +15106,7 @@
       <c r="J8" s="31"/>
       <c r="K8" s="31"/>
     </row>
-    <row r="9" spans="1:11" ht="60">
+    <row r="9" spans="1:11" ht="45">
       <c r="A9" s="28" t="s">
         <v>272</v>
       </c>
@@ -15133,10 +15114,10 @@
         <v>791</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>829</v>
+        <v>820</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="31"/>
@@ -15146,18 +15127,18 @@
       <c r="J9" s="31"/>
       <c r="K9" s="31"/>
     </row>
-    <row r="10" spans="1:11" ht="180">
+    <row r="10" spans="1:11" ht="105">
       <c r="A10" s="28" t="s">
         <v>273</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>792</v>
+        <v>826</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>811</v>
+        <v>831</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="E10" s="30"/>
       <c r="F10" s="31"/>
@@ -15167,18 +15148,18 @@
       <c r="J10" s="31"/>
       <c r="K10" s="31"/>
     </row>
-    <row r="11" spans="1:11" ht="195">
+    <row r="11" spans="1:11" ht="120">
       <c r="A11" s="28" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>793</v>
+        <v>827</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>812</v>
+        <v>832</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="E11" s="30"/>
       <c r="F11" s="31"/>
@@ -15188,18 +15169,18 @@
       <c r="J11" s="31"/>
       <c r="K11" s="31"/>
     </row>
-    <row r="12" spans="1:11" ht="195">
+    <row r="12" spans="1:11" ht="120">
       <c r="A12" s="28" t="s">
         <v>274</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>794</v>
+        <v>828</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>813</v>
+        <v>833</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="E12" s="30"/>
       <c r="F12" s="31"/>
@@ -15209,18 +15190,18 @@
       <c r="J12" s="31"/>
       <c r="K12" s="31"/>
     </row>
-    <row r="13" spans="1:11" ht="60">
+    <row r="13" spans="1:11" ht="45">
       <c r="A13" s="28" t="s">
         <v>275</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>833</v>
+        <v>821</v>
       </c>
       <c r="E13" s="30"/>
       <c r="F13" s="31"/>
@@ -15235,13 +15216,13 @@
         <v>276</v>
       </c>
       <c r="B14" s="29" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>834</v>
+        <v>822</v>
       </c>
       <c r="E14" s="30"/>
       <c r="F14" s="31"/>
@@ -15251,15 +15232,15 @@
       <c r="J14" s="31"/>
       <c r="K14" s="31"/>
     </row>
-    <row r="15" spans="1:11" ht="195">
+    <row r="15" spans="1:11" ht="120">
       <c r="A15" s="28" t="s">
         <v>277</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>797</v>
+        <v>829</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>816</v>
+        <v>834</v>
       </c>
       <c r="D15" s="32"/>
       <c r="E15" s="30"/>
@@ -15270,15 +15251,15 @@
       <c r="J15" s="31"/>
       <c r="K15" s="31"/>
     </row>
-    <row r="16" spans="1:11" ht="60">
+    <row r="16" spans="1:11" ht="45">
       <c r="A16" s="28" t="s">
         <v>278</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>798</v>
+        <v>830</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>817</v>
+        <v>808</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="30"/>
@@ -15289,15 +15270,15 @@
       <c r="J16" s="31"/>
       <c r="K16" s="31"/>
     </row>
-    <row r="17" spans="1:11" ht="45">
+    <row r="17" spans="1:11" ht="30">
       <c r="A17" s="28" t="s">
         <v>279</v>
       </c>
       <c r="B17" s="29" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>818</v>
+        <v>809</v>
       </c>
       <c r="D17" s="32"/>
       <c r="E17" s="30"/>
@@ -15313,10 +15294,10 @@
         <v>280</v>
       </c>
       <c r="B18" s="29" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>819</v>
+        <v>810</v>
       </c>
       <c r="D18" s="32"/>
       <c r="E18" s="30"/>
@@ -15327,16 +15308,16 @@
       <c r="J18" s="31"/>
       <c r="K18" s="31"/>
     </row>
-    <row r="19" spans="1:11" ht="45">
+    <row r="19" spans="1:11" ht="30">
       <c r="A19" s="28" t="s">
         <v>281</v>
       </c>
       <c r="B19" s="32"/>
       <c r="C19" s="29" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D19" s="29" t="s">
-        <v>835</v>
+        <v>823</v>
       </c>
       <c r="E19" s="30"/>
       <c r="F19" s="31"/>
@@ -15346,16 +15327,16 @@
       <c r="J19" s="31"/>
       <c r="K19" s="31"/>
     </row>
-    <row r="20" spans="1:11" ht="45">
+    <row r="20" spans="1:11" ht="30">
       <c r="A20" s="28" t="s">
         <v>282</v>
       </c>
       <c r="B20" s="32"/>
       <c r="C20" s="32" t="s">
-        <v>821</v>
+        <v>812</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>836</v>
+        <v>824</v>
       </c>
       <c r="E20" s="30"/>
       <c r="F20" s="31"/>
@@ -15370,7 +15351,7 @@
         <v>283</v>
       </c>
       <c r="B21" s="29" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="C21" s="29" t="s">
         <v>721</v>
@@ -15389,7 +15370,7 @@
         <v>284</v>
       </c>
       <c r="B22" s="29" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="C22" s="32"/>
       <c r="D22" s="32"/>
@@ -20150,7 +20131,7 @@
         <v>590</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
     </row>
     <row r="5" spans="1:2">
